--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1167"/>
+  <dimension ref="A1:L1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56343,10 +56343,8 @@
         </is>
       </c>
       <c r="H1147" t="inlineStr"/>
-      <c r="I1147" t="inlineStr">
-        <is>
-          <t>556193656589</t>
-        </is>
+      <c r="I1147" t="n">
+        <v>556193656589</v>
       </c>
       <c r="J1147" t="inlineStr"/>
       <c r="K1147" t="n">
@@ -56395,10 +56393,8 @@
         </is>
       </c>
       <c r="H1148" t="inlineStr"/>
-      <c r="I1148" t="inlineStr">
-        <is>
-          <t>5561993041166</t>
-        </is>
+      <c r="I1148" t="n">
+        <v>5561993041166</v>
       </c>
       <c r="J1148" t="inlineStr"/>
       <c r="K1148" t="n">
@@ -56543,10 +56539,8 @@
         </is>
       </c>
       <c r="H1151" t="inlineStr"/>
-      <c r="I1151" t="inlineStr">
-        <is>
-          <t>5561984048581</t>
-        </is>
+      <c r="I1151" t="n">
+        <v>5561984048581</v>
       </c>
       <c r="J1151" t="inlineStr"/>
       <c r="K1151" t="n">
@@ -56595,10 +56589,8 @@
         </is>
       </c>
       <c r="H1152" t="inlineStr"/>
-      <c r="I1152" t="inlineStr">
-        <is>
-          <t>5511976396153</t>
-        </is>
+      <c r="I1152" t="n">
+        <v>5511976396153</v>
       </c>
       <c r="J1152" t="inlineStr"/>
       <c r="K1152" t="n">
@@ -56695,10 +56687,8 @@
         </is>
       </c>
       <c r="H1154" t="inlineStr"/>
-      <c r="I1154" t="inlineStr">
-        <is>
-          <t>5521999850091</t>
-        </is>
+      <c r="I1154" t="n">
+        <v>5521999850091</v>
       </c>
       <c r="J1154" t="inlineStr"/>
       <c r="K1154" t="n">
@@ -56747,10 +56737,8 @@
         </is>
       </c>
       <c r="H1155" t="inlineStr"/>
-      <c r="I1155" t="inlineStr">
-        <is>
-          <t>5561992926161</t>
-        </is>
+      <c r="I1155" t="n">
+        <v>5561992926161</v>
       </c>
       <c r="J1155" t="inlineStr"/>
       <c r="K1155" t="n">
@@ -56799,10 +56787,8 @@
         </is>
       </c>
       <c r="H1156" t="inlineStr"/>
-      <c r="I1156" t="inlineStr">
-        <is>
-          <t>556196811386</t>
-        </is>
+      <c r="I1156" t="n">
+        <v>556196811386</v>
       </c>
       <c r="J1156" t="inlineStr"/>
       <c r="K1156" t="n">
@@ -56851,10 +56837,8 @@
         </is>
       </c>
       <c r="H1157" t="inlineStr"/>
-      <c r="I1157" t="inlineStr">
-        <is>
-          <t>5561992541042</t>
-        </is>
+      <c r="I1157" t="n">
+        <v>5561992541042</v>
       </c>
       <c r="J1157" t="inlineStr"/>
       <c r="K1157" t="n">
@@ -56999,10 +56983,8 @@
         </is>
       </c>
       <c r="H1160" t="inlineStr"/>
-      <c r="I1160" t="inlineStr">
-        <is>
-          <t>5562981942470</t>
-        </is>
+      <c r="I1160" t="n">
+        <v>5562981942470</v>
       </c>
       <c r="J1160" t="inlineStr"/>
       <c r="K1160" t="n">
@@ -57147,10 +57129,8 @@
         </is>
       </c>
       <c r="H1163" t="inlineStr"/>
-      <c r="I1163" t="inlineStr">
-        <is>
-          <t>5562982254507</t>
-        </is>
+      <c r="I1163" t="n">
+        <v>5562982254507</v>
       </c>
       <c r="J1163" t="inlineStr"/>
       <c r="K1163" t="n">
@@ -57354,6 +57334,1478 @@
         </is>
       </c>
     </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Clínica Amme</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://grupoammare.com.br</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr"/>
+      <c r="I1168" t="inlineStr"/>
+      <c r="J1168" t="inlineStr"/>
+      <c r="K1168" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1168" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Pronto Atendimento</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://www.hospitalvitoriaapart.com.br</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr"/>
+      <c r="I1169" t="inlineStr"/>
+      <c r="J1169" t="inlineStr"/>
+      <c r="K1169" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1169" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Clínica Kairós</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://clinicakairosvitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr"/>
+      <c r="I1170" t="inlineStr"/>
+      <c r="J1170" t="inlineStr"/>
+      <c r="K1170" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1170" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Conheça Vitória / ES</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://attitudepromo.iweventos.com.br</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr"/>
+      <c r="I1171" t="inlineStr"/>
+      <c r="J1171" t="inlineStr"/>
+      <c r="K1171" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1171" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>FORMAN Medicina</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://formanmedicina.com.br</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr"/>
+      <c r="I1172" t="inlineStr"/>
+      <c r="J1172" t="inlineStr"/>
+      <c r="K1172" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1172" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Psicóloga em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://psicologagiulianadepaula.com.br</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr"/>
+      <c r="I1173" t="inlineStr"/>
+      <c r="J1173" t="inlineStr"/>
+      <c r="K1173" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1173" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Os currículos da Educação Física na educação infantil em ...</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://periodicos.pucpr.br</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr"/>
+      <c r="I1174" t="inlineStr"/>
+      <c r="J1174" t="inlineStr"/>
+      <c r="K1174" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1174" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>EXPERIÊNCIAS NA EDUCAÇÃO INFANTIL DE VITÓRIA/ES</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://portalespiral.cp2.g12.br</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr"/>
+      <c r="I1175" t="inlineStr"/>
+      <c r="J1175" t="inlineStr"/>
+      <c r="K1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1175" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>[PDF] atuação do fisioterapeuta na atenção na básica, na perspectiva ...</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://revista.faesa.br</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr"/>
+      <c r="I1176" t="inlineStr"/>
+      <c r="J1176" t="inlineStr"/>
+      <c r="K1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1176" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Clinica Sagrada Família</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://clinicamedsagradafamilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr"/>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>5531975954885</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr"/>
+      <c r="K1177" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1177" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://www.clinicaaima.com.br</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr"/>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>5531999997188</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr"/>
+      <c r="K1178" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1178" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Clinica Médica São Paulo - Belo Horizonte - MG</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://www.climesp.com.br</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr"/>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>5531999345416</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr"/>
+      <c r="K1179" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1179" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Aspemed</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://aspemed.com.br</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr"/>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>5531973133014</t>
+        </is>
+      </c>
+      <c r="J1180" t="inlineStr"/>
+      <c r="K1180" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1180" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Contato</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://www.clinicamarcosandrade.com</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr"/>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>5531971622529</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr"/>
+      <c r="K1181" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1181" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Clínica de Psicologia PUC Minas</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://www.pucminas.br</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr"/>
+      <c r="I1182" t="inlineStr"/>
+      <c r="J1182" t="inlineStr"/>
+      <c r="K1182" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1182" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>32 treinadores e professores de esporte em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.suasaulasparticulares.com.br</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr"/>
+      <c r="I1183" t="inlineStr"/>
+      <c r="J1183" t="inlineStr"/>
+      <c r="K1183" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1183" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Personal Trainers em Belo Horizonte, MG</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://www.supertrainers.com.br</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr"/>
+      <c r="I1184" t="inlineStr"/>
+      <c r="J1184" t="inlineStr"/>
+      <c r="K1184" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1184" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Top 10 Academias de BH: Onde Treinar na Capital MineiraAcademias em Belo Horizonte, MG, Brasil</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://overallgymbh.com.br</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr"/>
+      <c r="I1185" t="inlineStr"/>
+      <c r="J1185" t="inlineStr"/>
+      <c r="K1185" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1185" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Dental Borges</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://dentalborges.com.br</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr"/>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>552138721919</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr"/>
+      <c r="K1186" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1186" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Revista Científica do CRO-RJ (Rio de Janeiro Dental Journal)</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://revcientifica.cro-rj.org.br</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr"/>
+      <c r="I1187" t="inlineStr"/>
+      <c r="J1187" t="inlineStr"/>
+      <c r="K1187" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1187" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Dentista em Rio de Janeiro com Convênio</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://www.encontreseudentista.com.br</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr"/>
+      <c r="I1188" t="inlineStr"/>
+      <c r="J1188" t="inlineStr"/>
+      <c r="K1188" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1188" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Sorriso Carioca</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://www.victorhugoalmeida.com.br</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr"/>
+      <c r="I1189" t="inlineStr"/>
+      <c r="J1189" t="inlineStr"/>
+      <c r="K1189" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1189" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Odonto Premier: Home</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://clinicaodontopremier.com.br</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr"/>
+      <c r="I1190" t="inlineStr"/>
+      <c r="J1190" t="inlineStr"/>
+      <c r="K1190" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1190" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Nova Odonto</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://novaodontorj.com</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr"/>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>5521984158201</t>
+        </is>
+      </c>
+      <c r="J1191" t="inlineStr"/>
+      <c r="K1191" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1191" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Psicólogos Sem Fronteiras</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://psf.org.br</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr"/>
+      <c r="I1192" t="inlineStr"/>
+      <c r="J1192" t="inlineStr"/>
+      <c r="K1192" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1192" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>SPA Serviços</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://www.psi.puc-rio.br</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr"/>
+      <c r="I1193" t="inlineStr"/>
+      <c r="J1193" t="inlineStr"/>
+      <c r="K1193" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1193" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Psicologia para Adultos</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://terapiascopacabana.com.br</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr"/>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>5521995673175</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr"/>
+      <c r="K1194" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1194" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Cadastro Nacional de Profissionais de Psicologia</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://cadastro.cfp.org.br</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr"/>
+      <c r="I1195" t="inlineStr"/>
+      <c r="J1195" t="inlineStr"/>
+      <c r="K1195" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1195" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Estudos e Pesquisas em Psicologia</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.e-publicacoes.uerj.br</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr"/>
+      <c r="I1196" t="inlineStr"/>
+      <c r="J1196" t="inlineStr"/>
+      <c r="K1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1196" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Encontre seu Terapeuta</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://terapeutasdobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr"/>
+      <c r="I1197" t="inlineStr"/>
+      <c r="J1197" t="inlineStr"/>
+      <c r="K1197" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1197" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1197"/>
+  <dimension ref="A1:L1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57803,10 +57803,8 @@
         </is>
       </c>
       <c r="H1177" t="inlineStr"/>
-      <c r="I1177" t="inlineStr">
-        <is>
-          <t>5531975954885</t>
-        </is>
+      <c r="I1177" t="n">
+        <v>5531975954885</v>
       </c>
       <c r="J1177" t="inlineStr"/>
       <c r="K1177" t="n">
@@ -57855,10 +57853,8 @@
         </is>
       </c>
       <c r="H1178" t="inlineStr"/>
-      <c r="I1178" t="inlineStr">
-        <is>
-          <t>5531999997188</t>
-        </is>
+      <c r="I1178" t="n">
+        <v>5531999997188</v>
       </c>
       <c r="J1178" t="inlineStr"/>
       <c r="K1178" t="n">
@@ -57907,10 +57903,8 @@
         </is>
       </c>
       <c r="H1179" t="inlineStr"/>
-      <c r="I1179" t="inlineStr">
-        <is>
-          <t>5531999345416</t>
-        </is>
+      <c r="I1179" t="n">
+        <v>5531999345416</v>
       </c>
       <c r="J1179" t="inlineStr"/>
       <c r="K1179" t="n">
@@ -57959,10 +57953,8 @@
         </is>
       </c>
       <c r="H1180" t="inlineStr"/>
-      <c r="I1180" t="inlineStr">
-        <is>
-          <t>5531973133014</t>
-        </is>
+      <c r="I1180" t="n">
+        <v>5531973133014</v>
       </c>
       <c r="J1180" t="inlineStr"/>
       <c r="K1180" t="n">
@@ -58011,10 +58003,8 @@
         </is>
       </c>
       <c r="H1181" t="inlineStr"/>
-      <c r="I1181" t="inlineStr">
-        <is>
-          <t>5531971622529</t>
-        </is>
+      <c r="I1181" t="n">
+        <v>5531971622529</v>
       </c>
       <c r="J1181" t="inlineStr"/>
       <c r="K1181" t="n">
@@ -58255,10 +58245,8 @@
         </is>
       </c>
       <c r="H1186" t="inlineStr"/>
-      <c r="I1186" t="inlineStr">
-        <is>
-          <t>552138721919</t>
-        </is>
+      <c r="I1186" t="n">
+        <v>552138721919</v>
       </c>
       <c r="J1186" t="inlineStr"/>
       <c r="K1186" t="n">
@@ -58499,10 +58487,8 @@
         </is>
       </c>
       <c r="H1191" t="inlineStr"/>
-      <c r="I1191" t="inlineStr">
-        <is>
-          <t>5521984158201</t>
-        </is>
+      <c r="I1191" t="n">
+        <v>5521984158201</v>
       </c>
       <c r="J1191" t="inlineStr"/>
       <c r="K1191" t="n">
@@ -58647,10 +58633,8 @@
         </is>
       </c>
       <c r="H1194" t="inlineStr"/>
-      <c r="I1194" t="inlineStr">
-        <is>
-          <t>5521995673175</t>
-        </is>
+      <c r="I1194" t="n">
+        <v>5521995673175</v>
       </c>
       <c r="J1194" t="inlineStr"/>
       <c r="K1194" t="n">
@@ -58806,6 +58790,458 @@
         </is>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Curitiba Clínica Médica Dr. Ivan Paredes</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.ivanparedes.com</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr"/>
+      <c r="I1198" t="inlineStr"/>
+      <c r="J1198" t="inlineStr"/>
+      <c r="K1198" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1198" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Garden Ouro</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://gardenouro.com.br</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr"/>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>5541987870161</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr"/>
+      <c r="K1199" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1199" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Centro Médico Mercês</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.centromedicomerces.com.br</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr"/>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>5541992900778</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr"/>
+      <c r="K1200" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1200" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://ics.curitiba.org.br</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr"/>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>554133306100</t>
+        </is>
+      </c>
+      <c r="J1201" t="inlineStr"/>
+      <c r="K1201" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1201" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Portal CRM-PR</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://crmpr.org.br</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr"/>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>5541985225361</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr"/>
+      <c r="K1202" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1202" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Psicóloga por Bairro em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.elisianesiqueira.com.br</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr"/>
+      <c r="I1203" t="inlineStr"/>
+      <c r="J1203" t="inlineStr"/>
+      <c r="K1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1203" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>projeto psicologia para todos</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.unibrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr"/>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>5541998127721</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr"/>
+      <c r="K1204" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1204" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Psicólogo Online para Todo o Brasil</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://onlinepsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr"/>
+      <c r="I1205" t="inlineStr"/>
+      <c r="J1205" t="inlineStr"/>
+      <c r="K1205" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1205" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.studiofcoach.com</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr"/>
+      <c r="I1206" t="inlineStr"/>
+      <c r="J1206" t="inlineStr"/>
+      <c r="K1206" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1206" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1206"/>
+  <dimension ref="A1:L1210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58875,10 +58875,8 @@
         </is>
       </c>
       <c r="H1199" t="inlineStr"/>
-      <c r="I1199" t="inlineStr">
-        <is>
-          <t>5541987870161</t>
-        </is>
+      <c r="I1199" t="n">
+        <v>5541987870161</v>
       </c>
       <c r="J1199" t="inlineStr"/>
       <c r="K1199" t="n">
@@ -58927,10 +58925,8 @@
         </is>
       </c>
       <c r="H1200" t="inlineStr"/>
-      <c r="I1200" t="inlineStr">
-        <is>
-          <t>5541992900778</t>
-        </is>
+      <c r="I1200" t="n">
+        <v>5541992900778</v>
       </c>
       <c r="J1200" t="inlineStr"/>
       <c r="K1200" t="n">
@@ -58979,10 +58975,8 @@
         </is>
       </c>
       <c r="H1201" t="inlineStr"/>
-      <c r="I1201" t="inlineStr">
-        <is>
-          <t>554133306100</t>
-        </is>
+      <c r="I1201" t="n">
+        <v>554133306100</v>
       </c>
       <c r="J1201" t="inlineStr"/>
       <c r="K1201" t="n">
@@ -59031,10 +59025,8 @@
         </is>
       </c>
       <c r="H1202" t="inlineStr"/>
-      <c r="I1202" t="inlineStr">
-        <is>
-          <t>5541985225361</t>
-        </is>
+      <c r="I1202" t="n">
+        <v>5541985225361</v>
       </c>
       <c r="J1202" t="inlineStr"/>
       <c r="K1202" t="n">
@@ -59131,10 +59123,8 @@
         </is>
       </c>
       <c r="H1204" t="inlineStr"/>
-      <c r="I1204" t="inlineStr">
-        <is>
-          <t>5541998127721</t>
-        </is>
+      <c r="I1204" t="n">
+        <v>5541998127721</v>
       </c>
       <c r="J1204" t="inlineStr"/>
       <c r="K1204" t="n">
@@ -59242,6 +59232,202 @@
         </is>
       </c>
     </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Academia Rio Branco na TotalPass</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://totalpass.com</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr"/>
+      <c r="I1207" t="inlineStr"/>
+      <c r="J1207" t="inlineStr"/>
+      <c r="K1207" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1207" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Lista de Clinica em Macapá</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.boaempresa.com.br</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr"/>
+      <c r="I1208" t="inlineStr"/>
+      <c r="J1208" t="inlineStr"/>
+      <c r="K1208" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1208" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Percepção de professores sobre o ensino de esportes não ...</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://seer.ufrgs.br</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr"/>
+      <c r="I1209" t="inlineStr"/>
+      <c r="J1209" t="inlineStr"/>
+      <c r="K1209" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1209" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Consulta particular em Manaus</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.medicalclin.com.br</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr"/>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>5592994786699</t>
+        </is>
+      </c>
+      <c r="J1210" t="inlineStr"/>
+      <c r="K1210" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1210" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1210"/>
+  <dimension ref="A1:L1221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59413,16 +59413,562 @@
         </is>
       </c>
       <c r="H1210" t="inlineStr"/>
-      <c r="I1210" t="inlineStr">
-        <is>
-          <t>5592994786699</t>
-        </is>
+      <c r="I1210" t="n">
+        <v>5592994786699</v>
       </c>
       <c r="J1210" t="inlineStr"/>
       <c r="K1210" t="n">
         <v>59</v>
       </c>
       <c r="L1210" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>RedeMedicos</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.redemedicos.com.br</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr"/>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>558288942811</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr"/>
+      <c r="K1211" t="n">
+        <v>93</v>
+      </c>
+      <c r="L1211" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Encontre um Dentista</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.uniodontomaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr"/>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>558221233300</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr"/>
+      <c r="K1212" t="n">
+        <v>100</v>
+      </c>
+      <c r="L1212" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Firlan Advogados</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://firlanadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr"/>
+      <c r="I1213" t="inlineStr"/>
+      <c r="J1213" t="inlineStr"/>
+      <c r="K1213" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1213" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Previdência</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://barachoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr"/>
+      <c r="I1214" t="inlineStr"/>
+      <c r="J1214" t="inlineStr"/>
+      <c r="K1214" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1214" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://www.gomespereiraadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr"/>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>5582999179543</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr"/>
+      <c r="K1215" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1215" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://vagas.solides.com.br</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr"/>
+      <c r="I1216" t="inlineStr"/>
+      <c r="J1216" t="inlineStr"/>
+      <c r="K1216" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1216" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Goldclin Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://clinicagoldclin.com.br</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr"/>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>5571992866341</t>
+        </is>
+      </c>
+      <c r="J1217" t="inlineStr"/>
+      <c r="K1217" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1217" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Dentistas em Salvador</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://www.encontrasalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr"/>
+      <c r="I1218" t="inlineStr"/>
+      <c r="J1218" t="inlineStr"/>
+      <c r="K1218" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1218" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Salvador Dentista</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://www.salvadordentista.com.br</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr"/>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>5571989211052</t>
+        </is>
+      </c>
+      <c r="J1219" t="inlineStr"/>
+      <c r="K1219" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1219" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Psicólogos em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://hubmental.com.br</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr"/>
+      <c r="I1220" t="inlineStr"/>
+      <c r="J1220" t="inlineStr"/>
+      <c r="K1220" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1220" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.colegioantoniovieira.com.br</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr"/>
+      <c r="I1221" t="inlineStr"/>
+      <c r="J1221" t="inlineStr"/>
+      <c r="K1221" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1221" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1221"/>
+  <dimension ref="A1:L1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59463,10 +59463,8 @@
         </is>
       </c>
       <c r="H1211" t="inlineStr"/>
-      <c r="I1211" t="inlineStr">
-        <is>
-          <t>558288942811</t>
-        </is>
+      <c r="I1211" t="n">
+        <v>558288942811</v>
       </c>
       <c r="J1211" t="inlineStr"/>
       <c r="K1211" t="n">
@@ -59515,10 +59513,8 @@
         </is>
       </c>
       <c r="H1212" t="inlineStr"/>
-      <c r="I1212" t="inlineStr">
-        <is>
-          <t>558221233300</t>
-        </is>
+      <c r="I1212" t="n">
+        <v>558221233300</v>
       </c>
       <c r="J1212" t="inlineStr"/>
       <c r="K1212" t="n">
@@ -59663,10 +59659,8 @@
         </is>
       </c>
       <c r="H1215" t="inlineStr"/>
-      <c r="I1215" t="inlineStr">
-        <is>
-          <t>5582999179543</t>
-        </is>
+      <c r="I1215" t="n">
+        <v>5582999179543</v>
       </c>
       <c r="J1215" t="inlineStr"/>
       <c r="K1215" t="n">
@@ -59763,10 +59757,8 @@
         </is>
       </c>
       <c r="H1217" t="inlineStr"/>
-      <c r="I1217" t="inlineStr">
-        <is>
-          <t>5571992866341</t>
-        </is>
+      <c r="I1217" t="n">
+        <v>5571992866341</v>
       </c>
       <c r="J1217" t="inlineStr"/>
       <c r="K1217" t="n">
@@ -59863,10 +59855,8 @@
         </is>
       </c>
       <c r="H1219" t="inlineStr"/>
-      <c r="I1219" t="inlineStr">
-        <is>
-          <t>5571989211052</t>
-        </is>
+      <c r="I1219" t="n">
+        <v>5571989211052</v>
       </c>
       <c r="J1219" t="inlineStr"/>
       <c r="K1219" t="n">
@@ -59974,6 +59964,954 @@
         </is>
       </c>
     </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Brasília</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://clinicapulsarti.com.br</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr"/>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>5561991431920</t>
+        </is>
+      </c>
+      <c r="J1222" t="inlineStr"/>
+      <c r="K1222" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1222" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Ebserh abre inscrições para médicos com salários de até R ...</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://agenciabrasil.ebc.com.br</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr"/>
+      <c r="I1223" t="inlineStr"/>
+      <c r="J1223" t="inlineStr"/>
+      <c r="K1223" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1223" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Hospital Alvorada Brasília: conheça os serviços da unidade</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.hospitalalvorada.com.br</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr"/>
+      <c r="I1224" t="inlineStr"/>
+      <c r="J1224" t="inlineStr"/>
+      <c r="K1224" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1224" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>HOME Hospital: PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://www.homehospital.com.br</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr"/>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>556138782878</t>
+        </is>
+      </c>
+      <c r="J1225" t="inlineStr"/>
+      <c r="K1225" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1225" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Hospital Águas Claras DF</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.hospitalaguasclaras.com.br</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr"/>
+      <c r="I1226" t="inlineStr"/>
+      <c r="J1226" t="inlineStr"/>
+      <c r="K1226" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1226" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>IOB - Instituto odontológico Brilhante</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://www.brilhanteodontologia.com</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr"/>
+      <c r="I1227" t="inlineStr"/>
+      <c r="J1227" t="inlineStr"/>
+      <c r="K1227" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1227" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Patrícia Luque</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://patricialuque.com.br</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr"/>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>5561981770119</t>
+        </is>
+      </c>
+      <c r="J1228" t="inlineStr"/>
+      <c r="K1228" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1228" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>B.Vieira Advogados</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://www.bvieira.adv.br</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr"/>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>556140420096</t>
+        </is>
+      </c>
+      <c r="J1229" t="inlineStr"/>
+      <c r="K1229" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1229" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Langamer Advogados</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://langamer.adv.br</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr"/>
+      <c r="I1230" t="inlineStr"/>
+      <c r="J1230" t="inlineStr"/>
+      <c r="K1230" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1230" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>[PDF] a educação física integrada à educação infantil no distrito</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://periodicos.furg.br</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr"/>
+      <c r="I1231" t="inlineStr"/>
+      <c r="J1231" t="inlineStr"/>
+      <c r="K1231" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1231" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Hit Haus: Academia, Boxe, Cycling &amp; Treinos Funcionais</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://hithaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr"/>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>5561999076634</t>
+        </is>
+      </c>
+      <c r="J1232" t="inlineStr"/>
+      <c r="K1232" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1232" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Academia Isac Rocha</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://www.isacrocha.com.br</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr"/>
+      <c r="I1233" t="inlineStr"/>
+      <c r="J1233" t="inlineStr"/>
+      <c r="K1233" t="n">
+        <v>40</v>
+      </c>
+      <c r="L1233" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Vista do Concepções de professores da Academia de Polícia Militar ...</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://revistas.usp.br</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr"/>
+      <c r="I1234" t="inlineStr"/>
+      <c r="J1234" t="inlineStr"/>
+      <c r="K1234" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1234" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://lp.casadofitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr"/>
+      <c r="I1235" t="inlineStr"/>
+      <c r="J1235" t="inlineStr"/>
+      <c r="K1235" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1235" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Amo Odontologia - Goiânia</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://amoodontologia.com</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr"/>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>5562999651090</t>
+        </is>
+      </c>
+      <c r="J1236" t="inlineStr"/>
+      <c r="K1236" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1236" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Psicologia</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://clinicanoroestegoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr"/>
+      <c r="I1237" t="inlineStr"/>
+      <c r="J1237" t="inlineStr"/>
+      <c r="K1237" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1237" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Brasil e Silveira Advogados</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://brasilesilveira.adv.br</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr"/>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>5562982773853</t>
+        </is>
+      </c>
+      <c r="J1238" t="inlineStr"/>
+      <c r="K1238" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1238" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Merola e Ribas</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://merolaeribas.adv.br</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr"/>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>5562981441323</t>
+        </is>
+      </c>
+      <c r="J1239" t="inlineStr"/>
+      <c r="K1239" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1239" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Nascimento Advogados</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://nassanadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr"/>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>5562992490054</t>
+        </is>
+      </c>
+      <c r="J1240" t="inlineStr"/>
+      <c r="K1240" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1240" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1240"/>
+  <dimension ref="A1:L1260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60001,10 +60001,8 @@
         </is>
       </c>
       <c r="H1222" t="inlineStr"/>
-      <c r="I1222" t="inlineStr">
-        <is>
-          <t>5561991431920</t>
-        </is>
+      <c r="I1222" t="n">
+        <v>5561991431920</v>
       </c>
       <c r="J1222" t="inlineStr"/>
       <c r="K1222" t="n">
@@ -60149,10 +60147,8 @@
         </is>
       </c>
       <c r="H1225" t="inlineStr"/>
-      <c r="I1225" t="inlineStr">
-        <is>
-          <t>556138782878</t>
-        </is>
+      <c r="I1225" t="n">
+        <v>556138782878</v>
       </c>
       <c r="J1225" t="inlineStr"/>
       <c r="K1225" t="n">
@@ -60297,10 +60293,8 @@
         </is>
       </c>
       <c r="H1228" t="inlineStr"/>
-      <c r="I1228" t="inlineStr">
-        <is>
-          <t>5561981770119</t>
-        </is>
+      <c r="I1228" t="n">
+        <v>5561981770119</v>
       </c>
       <c r="J1228" t="inlineStr"/>
       <c r="K1228" t="n">
@@ -60349,10 +60343,8 @@
         </is>
       </c>
       <c r="H1229" t="inlineStr"/>
-      <c r="I1229" t="inlineStr">
-        <is>
-          <t>556140420096</t>
-        </is>
+      <c r="I1229" t="n">
+        <v>556140420096</v>
       </c>
       <c r="J1229" t="inlineStr"/>
       <c r="K1229" t="n">
@@ -60497,10 +60489,8 @@
         </is>
       </c>
       <c r="H1232" t="inlineStr"/>
-      <c r="I1232" t="inlineStr">
-        <is>
-          <t>5561999076634</t>
-        </is>
+      <c r="I1232" t="n">
+        <v>5561999076634</v>
       </c>
       <c r="J1232" t="inlineStr"/>
       <c r="K1232" t="n">
@@ -60693,10 +60683,8 @@
         </is>
       </c>
       <c r="H1236" t="inlineStr"/>
-      <c r="I1236" t="inlineStr">
-        <is>
-          <t>5562999651090</t>
-        </is>
+      <c r="I1236" t="n">
+        <v>5562999651090</v>
       </c>
       <c r="J1236" t="inlineStr"/>
       <c r="K1236" t="n">
@@ -60793,10 +60781,8 @@
         </is>
       </c>
       <c r="H1238" t="inlineStr"/>
-      <c r="I1238" t="inlineStr">
-        <is>
-          <t>5562982773853</t>
-        </is>
+      <c r="I1238" t="n">
+        <v>5562982773853</v>
       </c>
       <c r="J1238" t="inlineStr"/>
       <c r="K1238" t="n">
@@ -60845,10 +60831,8 @@
         </is>
       </c>
       <c r="H1239" t="inlineStr"/>
-      <c r="I1239" t="inlineStr">
-        <is>
-          <t>5562981441323</t>
-        </is>
+      <c r="I1239" t="n">
+        <v>5562981441323</v>
       </c>
       <c r="J1239" t="inlineStr"/>
       <c r="K1239" t="n">
@@ -60897,10 +60881,8 @@
         </is>
       </c>
       <c r="H1240" t="inlineStr"/>
-      <c r="I1240" t="inlineStr">
-        <is>
-          <t>5562992490054</t>
-        </is>
+      <c r="I1240" t="n">
+        <v>5562992490054</v>
       </c>
       <c r="J1240" t="inlineStr"/>
       <c r="K1240" t="n">
@@ -60909,6 +60891,998 @@
       <c r="L1240" t="inlineStr">
         <is>
           <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Clinica Ortocruz — Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://saudenopais.com</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr"/>
+      <c r="I1241" t="inlineStr"/>
+      <c r="J1241" t="inlineStr"/>
+      <c r="K1241" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1241" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Urologista Online em Vitória</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://telemedico.med.br</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr"/>
+      <c r="I1242" t="inlineStr"/>
+      <c r="J1242" t="inlineStr"/>
+      <c r="K1242" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1242" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Vitória ES abre seleção para médico clínico com vaga imediata</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://folha.qconcursos.com</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr"/>
+      <c r="I1243" t="inlineStr"/>
+      <c r="J1243" t="inlineStr"/>
+      <c r="K1243" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1243" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>COI Odonto - Clínica Odontológica em Vitória</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://coiodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr"/>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>5527996220323</t>
+        </is>
+      </c>
+      <c r="J1244" t="inlineStr"/>
+      <c r="K1244" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1244" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Vista do A integração ensino-serviço em Odontologia no Brasil</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://revabeno.emnuvens.com.br</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr"/>
+      <c r="I1245" t="inlineStr"/>
+      <c r="J1245" t="inlineStr"/>
+      <c r="K1245" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1245" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Bernardo Carielo: Psicólogo em Vitória ES</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://psicologobernardo.com.br</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr"/>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>5527998331228</t>
+        </is>
+      </c>
+      <c r="J1246" t="inlineStr"/>
+      <c r="K1246" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1246" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Psicólogos Análise do Comportamento em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://psymple.com.br</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr"/>
+      <c r="I1247" t="inlineStr"/>
+      <c r="J1247" t="inlineStr"/>
+      <c r="K1247" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1247" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Mayra Novais</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://www.mayranovais.com.br</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr"/>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>5527997553110</t>
+        </is>
+      </c>
+      <c r="J1248" t="inlineStr"/>
+      <c r="K1248" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1248" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Coopsi</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://coopsi.coop.br</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr"/>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>5527996953392</t>
+        </is>
+      </c>
+      <c r="J1249" t="inlineStr"/>
+      <c r="K1249" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1249" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Grow Therapy</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://www.bing.com</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr"/>
+      <c r="I1250" t="inlineStr"/>
+      <c r="J1250" t="inlineStr"/>
+      <c r="K1250" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1250" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://www.tauilchequer.com.br</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr"/>
+      <c r="I1251" t="inlineStr"/>
+      <c r="J1251" t="inlineStr"/>
+      <c r="K1251" t="n">
+        <v>45</v>
+      </c>
+      <c r="L1251" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Site para Advogados e Escritórios de Advocacia em Vitória (ES)</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://weebsites.com.br</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr"/>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>553799196787</t>
+        </is>
+      </c>
+      <c r="J1252" t="inlineStr"/>
+      <c r="K1252" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1252" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Brasil Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://www.brasiladv.com</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr"/>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>5527997206931</t>
+        </is>
+      </c>
+      <c r="J1253" t="inlineStr"/>
+      <c r="K1253" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1253" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Seja bem-vindo</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://cefd.ufes.br</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr"/>
+      <c r="I1254" t="inlineStr"/>
+      <c r="J1254" t="inlineStr"/>
+      <c r="K1254" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1254" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>vitoriastudiofitness</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://www.vitoriastudiofitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr"/>
+      <c r="I1255" t="inlineStr"/>
+      <c r="J1255" t="inlineStr"/>
+      <c r="K1255" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1255" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Clínica Guarani</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://clinicaguarani.com.br</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr"/>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>553134332530</t>
+        </is>
+      </c>
+      <c r="J1256" t="inlineStr"/>
+      <c r="K1256" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1256" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Minascor Centro Médico</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://minascormg.com.br</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr"/>
+      <c r="I1257" t="inlineStr"/>
+      <c r="J1257" t="inlineStr"/>
+      <c r="K1257" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1257" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Top Therapists/ Psychologists Near Me in Belo Horizonte, State Of Minas Gerais</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://therapists.therapymantra.co</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr"/>
+      <c r="I1258" t="inlineStr"/>
+      <c r="J1258" t="inlineStr"/>
+      <c r="K1258" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1258" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Advogados na Cidade Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://www.encontrabelohorizonte.com.br</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr"/>
+      <c r="I1259" t="inlineStr"/>
+      <c r="J1259" t="inlineStr"/>
+      <c r="K1259" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1259" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Luciana Tasca Advogados</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.lucianatasca.com.br</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr"/>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>5531982130965</t>
+        </is>
+      </c>
+      <c r="J1260" t="inlineStr"/>
+      <c r="K1260" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1260"/>
+  <dimension ref="A1:L1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61075,10 +61075,8 @@
         </is>
       </c>
       <c r="H1244" t="inlineStr"/>
-      <c r="I1244" t="inlineStr">
-        <is>
-          <t>5527996220323</t>
-        </is>
+      <c r="I1244" t="n">
+        <v>5527996220323</v>
       </c>
       <c r="J1244" t="inlineStr"/>
       <c r="K1244" t="n">
@@ -61175,10 +61173,8 @@
         </is>
       </c>
       <c r="H1246" t="inlineStr"/>
-      <c r="I1246" t="inlineStr">
-        <is>
-          <t>5527998331228</t>
-        </is>
+      <c r="I1246" t="n">
+        <v>5527998331228</v>
       </c>
       <c r="J1246" t="inlineStr"/>
       <c r="K1246" t="n">
@@ -61275,10 +61271,8 @@
         </is>
       </c>
       <c r="H1248" t="inlineStr"/>
-      <c r="I1248" t="inlineStr">
-        <is>
-          <t>5527997553110</t>
-        </is>
+      <c r="I1248" t="n">
+        <v>5527997553110</v>
       </c>
       <c r="J1248" t="inlineStr"/>
       <c r="K1248" t="n">
@@ -61327,10 +61321,8 @@
         </is>
       </c>
       <c r="H1249" t="inlineStr"/>
-      <c r="I1249" t="inlineStr">
-        <is>
-          <t>5527996953392</t>
-        </is>
+      <c r="I1249" t="n">
+        <v>5527996953392</v>
       </c>
       <c r="J1249" t="inlineStr"/>
       <c r="K1249" t="n">
@@ -61475,10 +61467,8 @@
         </is>
       </c>
       <c r="H1252" t="inlineStr"/>
-      <c r="I1252" t="inlineStr">
-        <is>
-          <t>553799196787</t>
-        </is>
+      <c r="I1252" t="n">
+        <v>553799196787</v>
       </c>
       <c r="J1252" t="inlineStr"/>
       <c r="K1252" t="n">
@@ -61527,10 +61517,8 @@
         </is>
       </c>
       <c r="H1253" t="inlineStr"/>
-      <c r="I1253" t="inlineStr">
-        <is>
-          <t>5527997206931</t>
-        </is>
+      <c r="I1253" t="n">
+        <v>5527997206931</v>
       </c>
       <c r="J1253" t="inlineStr"/>
       <c r="K1253" t="n">
@@ -61675,10 +61663,8 @@
         </is>
       </c>
       <c r="H1256" t="inlineStr"/>
-      <c r="I1256" t="inlineStr">
-        <is>
-          <t>553134332530</t>
-        </is>
+      <c r="I1256" t="n">
+        <v>553134332530</v>
       </c>
       <c r="J1256" t="inlineStr"/>
       <c r="K1256" t="n">
@@ -61871,10 +61857,8 @@
         </is>
       </c>
       <c r="H1260" t="inlineStr"/>
-      <c r="I1260" t="inlineStr">
-        <is>
-          <t>5531982130965</t>
-        </is>
+      <c r="I1260" t="n">
+        <v>5531982130965</v>
       </c>
       <c r="J1260" t="inlineStr"/>
       <c r="K1260" t="n">
@@ -61883,6 +61867,602 @@
       <c r="L1260" t="inlineStr">
         <is>
           <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>As Clínicas Médicas mais buscadas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://www.acessomedico.com.br</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr"/>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>5541998759270</t>
+        </is>
+      </c>
+      <c r="J1261" t="inlineStr"/>
+      <c r="K1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Denise Moreira Odontologia</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://dradenisemoreira.com</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr"/>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>5541985003377</t>
+        </is>
+      </c>
+      <c r="J1262" t="inlineStr"/>
+      <c r="K1262" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Angelo Salignac - Psicólogo Clínico</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.salignac-psic.org</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr"/>
+      <c r="I1263" t="inlineStr"/>
+      <c r="J1263" t="inlineStr"/>
+      <c r="K1263" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Marcio Spagnol</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://www.marciospagnol.com.br</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr"/>
+      <c r="I1264" t="inlineStr"/>
+      <c r="J1264" t="inlineStr"/>
+      <c r="K1264" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>BIANCA SAUSEN</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://biancasausen.codental.site</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr"/>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>5551996195929</t>
+        </is>
+      </c>
+      <c r="J1265" t="inlineStr"/>
+      <c r="K1265" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Carlos Wunderlich Advocacia</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://www.carloswunderlich.com</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr"/>
+      <c r="I1266" t="inlineStr"/>
+      <c r="J1266" t="inlineStr"/>
+      <c r="K1266" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Advogado em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://rmpadvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr"/>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>5551981059125</t>
+        </is>
+      </c>
+      <c r="J1267" t="inlineStr"/>
+      <c r="K1267" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Alves Nunes Rodrigues Advogados</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://alvesnunesadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr"/>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>555135745063</t>
+        </is>
+      </c>
+      <c r="J1268" t="inlineStr"/>
+      <c r="K1268" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Fabiano Porcela</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://www.fabianoporcelaadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr"/>
+      <c r="I1269" t="inlineStr"/>
+      <c r="J1269" t="inlineStr"/>
+      <c r="K1269" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://portal.pucrs.br</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr"/>
+      <c r="I1270" t="inlineStr"/>
+      <c r="J1270" t="inlineStr"/>
+      <c r="K1270" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Vitória: Em Porto Alegre, Licenciatura em Educação Física é ...</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://www.confef.org.br</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr"/>
+      <c r="I1271" t="inlineStr"/>
+      <c r="J1271" t="inlineStr"/>
+      <c r="K1271" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Porto Alegre, RS - 36 Empresas</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://parafa.com.br</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr"/>
+      <c r="I1272" t="inlineStr"/>
+      <c r="J1272" t="inlineStr"/>
+      <c r="K1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>Crítico</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1272"/>
+  <dimension ref="A1:L1277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61907,10 +61907,8 @@
         </is>
       </c>
       <c r="H1261" t="inlineStr"/>
-      <c r="I1261" t="inlineStr">
-        <is>
-          <t>5541998759270</t>
-        </is>
+      <c r="I1261" t="n">
+        <v>5541998759270</v>
       </c>
       <c r="J1261" t="inlineStr"/>
       <c r="K1261" t="n">
@@ -61959,10 +61957,8 @@
         </is>
       </c>
       <c r="H1262" t="inlineStr"/>
-      <c r="I1262" t="inlineStr">
-        <is>
-          <t>5541985003377</t>
-        </is>
+      <c r="I1262" t="n">
+        <v>5541985003377</v>
       </c>
       <c r="J1262" t="inlineStr"/>
       <c r="K1262" t="n">
@@ -62107,10 +62103,8 @@
         </is>
       </c>
       <c r="H1265" t="inlineStr"/>
-      <c r="I1265" t="inlineStr">
-        <is>
-          <t>5551996195929</t>
-        </is>
+      <c r="I1265" t="n">
+        <v>5551996195929</v>
       </c>
       <c r="J1265" t="inlineStr"/>
       <c r="K1265" t="n">
@@ -62207,10 +62201,8 @@
         </is>
       </c>
       <c r="H1267" t="inlineStr"/>
-      <c r="I1267" t="inlineStr">
-        <is>
-          <t>5551981059125</t>
-        </is>
+      <c r="I1267" t="n">
+        <v>5551981059125</v>
       </c>
       <c r="J1267" t="inlineStr"/>
       <c r="K1267" t="n">
@@ -62259,10 +62251,8 @@
         </is>
       </c>
       <c r="H1268" t="inlineStr"/>
-      <c r="I1268" t="inlineStr">
-        <is>
-          <t>555135745063</t>
-        </is>
+      <c r="I1268" t="n">
+        <v>555135745063</v>
       </c>
       <c r="J1268" t="inlineStr"/>
       <c r="K1268" t="n">
@@ -62466,6 +62456,254 @@
         </is>
       </c>
     </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>8 Melhores Academias de Jiu-Jitsu em Rio Branco (2026) 4.8</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.academiasjiujitsu.com.br</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr"/>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>554792563353</t>
+        </is>
+      </c>
+      <c r="J1273" t="inlineStr"/>
+      <c r="K1273" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>VELT ACADEMIA</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://academiavelt.com.br</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr"/>
+      <c r="I1274" t="inlineStr"/>
+      <c r="J1274" t="inlineStr"/>
+      <c r="K1274" t="n">
+        <v>30</v>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Leo Bezerra entrega 3ª Academia da Cidade e prepara ...</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://rbtv.com.br</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr"/>
+      <c r="I1275" t="inlineStr"/>
+      <c r="J1275" t="inlineStr"/>
+      <c r="K1275" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>WN Odonto Medical</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://wnodontomedical.com.br</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr"/>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>5592994704141</t>
+        </is>
+      </c>
+      <c r="J1276" t="inlineStr"/>
+      <c r="K1276" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Vista do Doença de Gaucher e atuação do cirurgião-dentista: relato ...</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://archhealthinvestigation.com.br</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr"/>
+      <c r="I1277" t="inlineStr"/>
+      <c r="J1277" t="inlineStr"/>
+      <c r="K1277" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1277"/>
+  <dimension ref="A1:L1288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62493,10 +62493,8 @@
         </is>
       </c>
       <c r="H1273" t="inlineStr"/>
-      <c r="I1273" t="inlineStr">
-        <is>
-          <t>554792563353</t>
-        </is>
+      <c r="I1273" t="n">
+        <v>554792563353</v>
       </c>
       <c r="J1273" t="inlineStr"/>
       <c r="K1273" t="n">
@@ -62641,10 +62639,8 @@
         </is>
       </c>
       <c r="H1276" t="inlineStr"/>
-      <c r="I1276" t="inlineStr">
-        <is>
-          <t>5592994704141</t>
-        </is>
+      <c r="I1276" t="n">
+        <v>5592994704141</v>
       </c>
       <c r="J1276" t="inlineStr"/>
       <c r="K1276" t="n">
@@ -62704,6 +62700,550 @@
         </is>
       </c>
     </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Dr. Thiago Beltrão — Cirurgião-Dentista</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://thiagobeltrao.online</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr"/>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>5582000000000</t>
+        </is>
+      </c>
+      <c r="J1278" t="inlineStr"/>
+      <c r="K1278" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Yhasmim Marinho</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://yhasmimmarinho.psc.br</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr"/>
+      <c r="I1279" t="inlineStr"/>
+      <c r="J1279" t="inlineStr"/>
+      <c r="K1279" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Encontro de Profissionais de Educação Física do SUS ...</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.even3.com.br</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr"/>
+      <c r="I1280" t="inlineStr"/>
+      <c r="J1280" t="inlineStr"/>
+      <c r="K1280" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Representações do corpo por professores de Educação Física ...</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://periodicos.uff.br</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr"/>
+      <c r="I1281" t="inlineStr"/>
+      <c r="J1281" t="inlineStr"/>
+      <c r="K1281" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Rede de Referência</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://planobrasilsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr"/>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>5508009719777</t>
+        </is>
+      </c>
+      <c r="J1282" t="inlineStr"/>
+      <c r="K1282" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>cemesb.com.br</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://cemesb.com.br</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr"/>
+      <c r="I1283" t="inlineStr"/>
+      <c r="J1283" t="inlineStr"/>
+      <c r="K1283" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>clínica em Salvador</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://br.clinicby.com</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr"/>
+      <c r="I1284" t="inlineStr"/>
+      <c r="J1284" t="inlineStr"/>
+      <c r="K1284" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Iara Cardoso</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.terapeutaiara.com.br</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr"/>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>5571982154282</t>
+        </is>
+      </c>
+      <c r="J1285" t="inlineStr"/>
+      <c r="K1285" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Espaço Emanar</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.espacoemanar.com.br</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr"/>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>5571981354300</t>
+        </is>
+      </c>
+      <c r="J1286" t="inlineStr"/>
+      <c r="K1286" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://hapvidandi.pandape.com.br</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr"/>
+      <c r="I1287" t="inlineStr"/>
+      <c r="J1287" t="inlineStr"/>
+      <c r="K1287" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Vista do SINTOMAS OSTEOMUSCULARES EM ...</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www5.bahiana.edu.br</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr"/>
+      <c r="I1288" t="inlineStr"/>
+      <c r="J1288" t="inlineStr"/>
+      <c r="K1288" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1288"/>
+  <dimension ref="A1:L1300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62737,10 +62737,8 @@
         </is>
       </c>
       <c r="H1278" t="inlineStr"/>
-      <c r="I1278" t="inlineStr">
-        <is>
-          <t>5582000000000</t>
-        </is>
+      <c r="I1278" t="n">
+        <v>5582000000000</v>
       </c>
       <c r="J1278" t="inlineStr"/>
       <c r="K1278" t="n">
@@ -62933,10 +62931,8 @@
         </is>
       </c>
       <c r="H1282" t="inlineStr"/>
-      <c r="I1282" t="inlineStr">
-        <is>
-          <t>5508009719777</t>
-        </is>
+      <c r="I1282" t="n">
+        <v>5508009719777</v>
       </c>
       <c r="J1282" t="inlineStr"/>
       <c r="K1282" t="n">
@@ -63081,10 +63077,8 @@
         </is>
       </c>
       <c r="H1285" t="inlineStr"/>
-      <c r="I1285" t="inlineStr">
-        <is>
-          <t>5571982154282</t>
-        </is>
+      <c r="I1285" t="n">
+        <v>5571982154282</v>
       </c>
       <c r="J1285" t="inlineStr"/>
       <c r="K1285" t="n">
@@ -63133,10 +63127,8 @@
         </is>
       </c>
       <c r="H1286" t="inlineStr"/>
-      <c r="I1286" t="inlineStr">
-        <is>
-          <t>5571981354300</t>
-        </is>
+      <c r="I1286" t="n">
+        <v>5571981354300</v>
       </c>
       <c r="J1286" t="inlineStr"/>
       <c r="K1286" t="n">
@@ -63244,6 +63236,614 @@
         </is>
       </c>
     </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Brasília — Asa Sul</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://cefisbsb.com.br</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr"/>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>5561995092995</t>
+        </is>
+      </c>
+      <c r="J1289" t="inlineStr"/>
+      <c r="K1289" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Centro Médico de Brasília</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://centromedicodebrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr"/>
+      <c r="I1290" t="inlineStr"/>
+      <c r="J1290" t="inlineStr"/>
+      <c r="K1290" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Terapia TRG em Brasília</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.espacoemocional.com.br</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr"/>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>5561995704309</t>
+        </is>
+      </c>
+      <c r="J1291" t="inlineStr"/>
+      <c r="K1291" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Brasília</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://campospinho.adv.br</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr"/>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>5561981490953</t>
+        </is>
+      </c>
+      <c r="J1292" t="inlineStr"/>
+      <c r="K1292" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Via Médica</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>http://www.viamedica-go.com.br</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr"/>
+      <c r="I1293" t="inlineStr"/>
+      <c r="J1293" t="inlineStr"/>
+      <c r="K1293" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Clínica Médica Particular Acessível em Goiânia e Valparaíso</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://www.souclinicavitta.com.br</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr"/>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>556239960505</t>
+        </is>
+      </c>
+      <c r="J1294" t="inlineStr"/>
+      <c r="K1294" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Daniel Vieira</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>https://www.danielvieirapsicologo.com.br</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr"/>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>5562999574089</t>
+        </is>
+      </c>
+      <c r="J1295" t="inlineStr"/>
+      <c r="K1295" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Cairo Filho — Psicólogo Clínico</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>https://www.cairofilhopsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr"/>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>5562991674706</t>
+        </is>
+      </c>
+      <c r="J1296" t="inlineStr"/>
+      <c r="K1296" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Terapeuta Em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>https://claudiabarrosterapeuta.com</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr"/>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>556282361670</t>
+        </is>
+      </c>
+      <c r="J1297" t="inlineStr"/>
+      <c r="K1297" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Marília Martins Advocacia</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>https://mariliamartins.com.br</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr"/>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>5562994105041</t>
+        </is>
+      </c>
+      <c r="J1298" t="inlineStr"/>
+      <c r="K1298" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Bernardes &amp; Viana Advogados</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>https://www.bevadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr"/>
+      <c r="I1299" t="inlineStr"/>
+      <c r="J1299" t="inlineStr"/>
+      <c r="K1299" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>FEFD</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>https://fefd.ufg.br</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr"/>
+      <c r="I1300" t="inlineStr"/>
+      <c r="J1300" t="inlineStr"/>
+      <c r="K1300" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1300"/>
+  <dimension ref="A1:L1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63273,10 +63273,8 @@
         </is>
       </c>
       <c r="H1289" t="inlineStr"/>
-      <c r="I1289" t="inlineStr">
-        <is>
-          <t>5561995092995</t>
-        </is>
+      <c r="I1289" t="n">
+        <v>5561995092995</v>
       </c>
       <c r="J1289" t="inlineStr"/>
       <c r="K1289" t="n">
@@ -63373,10 +63371,8 @@
         </is>
       </c>
       <c r="H1291" t="inlineStr"/>
-      <c r="I1291" t="inlineStr">
-        <is>
-          <t>5561995704309</t>
-        </is>
+      <c r="I1291" t="n">
+        <v>5561995704309</v>
       </c>
       <c r="J1291" t="inlineStr"/>
       <c r="K1291" t="n">
@@ -63425,10 +63421,8 @@
         </is>
       </c>
       <c r="H1292" t="inlineStr"/>
-      <c r="I1292" t="inlineStr">
-        <is>
-          <t>5561981490953</t>
-        </is>
+      <c r="I1292" t="n">
+        <v>5561981490953</v>
       </c>
       <c r="J1292" t="inlineStr"/>
       <c r="K1292" t="n">
@@ -63525,10 +63519,8 @@
         </is>
       </c>
       <c r="H1294" t="inlineStr"/>
-      <c r="I1294" t="inlineStr">
-        <is>
-          <t>556239960505</t>
-        </is>
+      <c r="I1294" t="n">
+        <v>556239960505</v>
       </c>
       <c r="J1294" t="inlineStr"/>
       <c r="K1294" t="n">
@@ -63577,10 +63569,8 @@
         </is>
       </c>
       <c r="H1295" t="inlineStr"/>
-      <c r="I1295" t="inlineStr">
-        <is>
-          <t>5562999574089</t>
-        </is>
+      <c r="I1295" t="n">
+        <v>5562999574089</v>
       </c>
       <c r="J1295" t="inlineStr"/>
       <c r="K1295" t="n">
@@ -63629,10 +63619,8 @@
         </is>
       </c>
       <c r="H1296" t="inlineStr"/>
-      <c r="I1296" t="inlineStr">
-        <is>
-          <t>5562991674706</t>
-        </is>
+      <c r="I1296" t="n">
+        <v>5562991674706</v>
       </c>
       <c r="J1296" t="inlineStr"/>
       <c r="K1296" t="n">
@@ -63681,10 +63669,8 @@
         </is>
       </c>
       <c r="H1297" t="inlineStr"/>
-      <c r="I1297" t="inlineStr">
-        <is>
-          <t>556282361670</t>
-        </is>
+      <c r="I1297" t="n">
+        <v>556282361670</v>
       </c>
       <c r="J1297" t="inlineStr"/>
       <c r="K1297" t="n">
@@ -63733,10 +63719,8 @@
         </is>
       </c>
       <c r="H1298" t="inlineStr"/>
-      <c r="I1298" t="inlineStr">
-        <is>
-          <t>5562994105041</t>
-        </is>
+      <c r="I1298" t="n">
+        <v>5562994105041</v>
       </c>
       <c r="J1298" t="inlineStr"/>
       <c r="K1298" t="n">
@@ -63844,6 +63828,658 @@
         </is>
       </c>
     </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Vitória retoma agendamento on-line para consultas</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>https://esbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr"/>
+      <c r="I1301" t="inlineStr"/>
+      <c r="J1301" t="inlineStr"/>
+      <c r="K1301" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Guia Médico MedSênior em Vitória (ES)</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://medseniorvendas.com.br</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr"/>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>5511926055067</t>
+        </is>
+      </c>
+      <c r="J1302" t="inlineStr"/>
+      <c r="K1302" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Dra. Camila Moraes Dias</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>https://www.implanteenseadadosua.com</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr"/>
+      <c r="I1303" t="inlineStr"/>
+      <c r="J1303" t="inlineStr"/>
+      <c r="K1303" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Cieo Odontologia Digital</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>https://www.dentista-es.com.br</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr"/>
+      <c r="I1304" t="inlineStr"/>
+      <c r="J1304" t="inlineStr"/>
+      <c r="K1304" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>EasyFisio</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://easyfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr"/>
+      <c r="I1305" t="inlineStr"/>
+      <c r="J1305" t="inlineStr"/>
+      <c r="K1305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia Especializado</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://danielfrederighiadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr"/>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>5531984351476</t>
+        </is>
+      </c>
+      <c r="J1306" t="inlineStr"/>
+      <c r="K1306" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Educação Física na Anhanguera em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>https://www.anhangueracursos.com.br</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr"/>
+      <c r="I1307" t="inlineStr"/>
+      <c r="J1307" t="inlineStr"/>
+      <c r="K1307" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Amanda Faúla</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>https://amandafaulafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr"/>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>5531992228505</t>
+        </is>
+      </c>
+      <c r="J1308" t="inlineStr"/>
+      <c r="K1308" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta Maria Coxir</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>https://www.mariacoxirfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr"/>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>5531995862768</t>
+        </is>
+      </c>
+      <c r="J1309" t="inlineStr"/>
+      <c r="K1309" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Cristiane Lage</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>https://cristianelage.com.br</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr"/>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>553199566830</t>
+        </is>
+      </c>
+      <c r="J1310" t="inlineStr"/>
+      <c r="K1310" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Renata Cruzeiro Ribas — Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>https://reabilitacaocardiaca.com</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr"/>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>5531992890092</t>
+        </is>
+      </c>
+      <c r="J1311" t="inlineStr"/>
+      <c r="K1311" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Dra. Paula Gomes</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>https://paulagomesfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr"/>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>5531993783884</t>
+        </is>
+      </c>
+      <c r="J1312" t="inlineStr"/>
+      <c r="K1312" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Medicina de qualidade na Zona Oeste do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>https://clamedcm.com.br</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr"/>
+      <c r="I1313" t="inlineStr"/>
+      <c r="J1313" t="inlineStr"/>
+      <c r="K1313" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1313"/>
+  <dimension ref="A1:L1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63913,10 +63913,8 @@
         </is>
       </c>
       <c r="H1302" t="inlineStr"/>
-      <c r="I1302" t="inlineStr">
-        <is>
-          <t>5511926055067</t>
-        </is>
+      <c r="I1302" t="n">
+        <v>5511926055067</v>
       </c>
       <c r="J1302" t="inlineStr"/>
       <c r="K1302" t="n">
@@ -64109,10 +64107,8 @@
         </is>
       </c>
       <c r="H1306" t="inlineStr"/>
-      <c r="I1306" t="inlineStr">
-        <is>
-          <t>5531984351476</t>
-        </is>
+      <c r="I1306" t="n">
+        <v>5531984351476</v>
       </c>
       <c r="J1306" t="inlineStr"/>
       <c r="K1306" t="n">
@@ -64209,10 +64205,8 @@
         </is>
       </c>
       <c r="H1308" t="inlineStr"/>
-      <c r="I1308" t="inlineStr">
-        <is>
-          <t>5531992228505</t>
-        </is>
+      <c r="I1308" t="n">
+        <v>5531992228505</v>
       </c>
       <c r="J1308" t="inlineStr"/>
       <c r="K1308" t="n">
@@ -64261,10 +64255,8 @@
         </is>
       </c>
       <c r="H1309" t="inlineStr"/>
-      <c r="I1309" t="inlineStr">
-        <is>
-          <t>5531995862768</t>
-        </is>
+      <c r="I1309" t="n">
+        <v>5531995862768</v>
       </c>
       <c r="J1309" t="inlineStr"/>
       <c r="K1309" t="n">
@@ -64313,10 +64305,8 @@
         </is>
       </c>
       <c r="H1310" t="inlineStr"/>
-      <c r="I1310" t="inlineStr">
-        <is>
-          <t>553199566830</t>
-        </is>
+      <c r="I1310" t="n">
+        <v>553199566830</v>
       </c>
       <c r="J1310" t="inlineStr"/>
       <c r="K1310" t="n">
@@ -64365,10 +64355,8 @@
         </is>
       </c>
       <c r="H1311" t="inlineStr"/>
-      <c r="I1311" t="inlineStr">
-        <is>
-          <t>5531992890092</t>
-        </is>
+      <c r="I1311" t="n">
+        <v>5531992890092</v>
       </c>
       <c r="J1311" t="inlineStr"/>
       <c r="K1311" t="n">
@@ -64417,10 +64405,8 @@
         </is>
       </c>
       <c r="H1312" t="inlineStr"/>
-      <c r="I1312" t="inlineStr">
-        <is>
-          <t>5531993783884</t>
-        </is>
+      <c r="I1312" t="n">
+        <v>5531993783884</v>
       </c>
       <c r="J1312" t="inlineStr"/>
       <c r="K1312" t="n">
@@ -64480,6 +64466,406 @@
         </is>
       </c>
     </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>CEDISA</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>https://www.cedisasaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr"/>
+      <c r="I1314" t="inlineStr"/>
+      <c r="J1314" t="inlineStr"/>
+      <c r="K1314" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Medik Doctor</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>https://clinicamedikdoctor.com.br</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr"/>
+      <c r="I1315" t="inlineStr"/>
+      <c r="J1315" t="inlineStr"/>
+      <c r="K1315" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Elisa Villa</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>https://terapeutaelisavilla.com.br</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr"/>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>5541988377317</t>
+        </is>
+      </c>
+      <c r="J1316" t="inlineStr"/>
+      <c r="K1316" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Curitiba-PR</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>https://advogadofabianolima.com.br</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr"/>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>5541995158069</t>
+        </is>
+      </c>
+      <c r="J1317" t="inlineStr"/>
+      <c r="K1317" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Departamento de Educação Física</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>http://gradedf.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr"/>
+      <c r="I1318" t="inlineStr"/>
+      <c r="J1318" t="inlineStr"/>
+      <c r="K1318" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Benessere Terapia</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>https://www.benessereterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr"/>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>5551983441433</t>
+        </is>
+      </c>
+      <c r="J1319" t="inlineStr"/>
+      <c r="K1319" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Michelle Tarta Psicóloga</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>https://www.michelletartapsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr"/>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>5551992639978</t>
+        </is>
+      </c>
+      <c r="J1320" t="inlineStr"/>
+      <c r="K1320" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Artur Torres</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>http://arturtorres.com.br</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr"/>
+      <c r="I1321" t="inlineStr"/>
+      <c r="J1321" t="inlineStr"/>
+      <c r="K1321" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1321"/>
+  <dimension ref="A1:L1328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64599,10 +64599,8 @@
         </is>
       </c>
       <c r="H1316" t="inlineStr"/>
-      <c r="I1316" t="inlineStr">
-        <is>
-          <t>5541988377317</t>
-        </is>
+      <c r="I1316" t="n">
+        <v>5541988377317</v>
       </c>
       <c r="J1316" t="inlineStr"/>
       <c r="K1316" t="n">
@@ -64651,10 +64649,8 @@
         </is>
       </c>
       <c r="H1317" t="inlineStr"/>
-      <c r="I1317" t="inlineStr">
-        <is>
-          <t>5541995158069</t>
-        </is>
+      <c r="I1317" t="n">
+        <v>5541995158069</v>
       </c>
       <c r="J1317" t="inlineStr"/>
       <c r="K1317" t="n">
@@ -64751,10 +64747,8 @@
         </is>
       </c>
       <c r="H1319" t="inlineStr"/>
-      <c r="I1319" t="inlineStr">
-        <is>
-          <t>5551983441433</t>
-        </is>
+      <c r="I1319" t="n">
+        <v>5551983441433</v>
       </c>
       <c r="J1319" t="inlineStr"/>
       <c r="K1319" t="n">
@@ -64803,10 +64797,8 @@
         </is>
       </c>
       <c r="H1320" t="inlineStr"/>
-      <c r="I1320" t="inlineStr">
-        <is>
-          <t>5551992639978</t>
-        </is>
+      <c r="I1320" t="n">
+        <v>5551992639978</v>
       </c>
       <c r="J1320" t="inlineStr"/>
       <c r="K1320" t="n">
@@ -64866,6 +64858,354 @@
         </is>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>DENTISTA DA FAMILIA</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>https://querobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr"/>
+      <c r="I1322" t="inlineStr"/>
+      <c r="J1322" t="inlineStr"/>
+      <c r="K1322" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Tobias Meireles Advogados</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://tobiasmeirelesadvogados.com</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr"/>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>5568992383844</t>
+        </is>
+      </c>
+      <c r="J1323" t="inlineStr"/>
+      <c r="K1323" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Clínica Saúde Integrada</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>https://www.clinicasudeintegrada.com.br</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr"/>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>5596981388092</t>
+        </is>
+      </c>
+      <c r="J1324" t="inlineStr"/>
+      <c r="K1324" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica em Manaus</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>https://www.sanmede.com.br</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr"/>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>559231992420</t>
+        </is>
+      </c>
+      <c r="J1325" t="inlineStr"/>
+      <c r="K1325" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>VIANA &amp; BARBOSA ADVOGADOS - Advogado Trabalhista Manaus</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>https://vianaebarbosaadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr"/>
+      <c r="I1326" t="inlineStr"/>
+      <c r="J1326" t="inlineStr"/>
+      <c r="K1326" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Vestibular em Educação Física</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://www.unilasalle.edu.br</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr"/>
+      <c r="I1327" t="inlineStr"/>
+      <c r="J1327" t="inlineStr"/>
+      <c r="K1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Live Academia</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>https://www.liveacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr"/>
+      <c r="I1328" t="inlineStr"/>
+      <c r="J1328" t="inlineStr"/>
+      <c r="K1328" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1328"/>
+  <dimension ref="A1:L1341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64943,10 +64943,8 @@
         </is>
       </c>
       <c r="H1323" t="inlineStr"/>
-      <c r="I1323" t="inlineStr">
-        <is>
-          <t>5568992383844</t>
-        </is>
+      <c r="I1323" t="n">
+        <v>5568992383844</v>
       </c>
       <c r="J1323" t="inlineStr"/>
       <c r="K1323" t="n">
@@ -64995,10 +64993,8 @@
         </is>
       </c>
       <c r="H1324" t="inlineStr"/>
-      <c r="I1324" t="inlineStr">
-        <is>
-          <t>5596981388092</t>
-        </is>
+      <c r="I1324" t="n">
+        <v>5596981388092</v>
       </c>
       <c r="J1324" t="inlineStr"/>
       <c r="K1324" t="n">
@@ -65047,10 +65043,8 @@
         </is>
       </c>
       <c r="H1325" t="inlineStr"/>
-      <c r="I1325" t="inlineStr">
-        <is>
-          <t>559231992420</t>
-        </is>
+      <c r="I1325" t="n">
+        <v>559231992420</v>
       </c>
       <c r="J1325" t="inlineStr"/>
       <c r="K1325" t="n">
@@ -65206,6 +65200,662 @@
         </is>
       </c>
     </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Clínica Conatus</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>https://clinicaconatus.com.br</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr"/>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>5582993327839</t>
+        </is>
+      </c>
+      <c r="J1329" t="inlineStr"/>
+      <c r="K1329" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Dentista 24h em Maceió · Urgência Odontológica · Dr. Milton Aquino</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>https://www.drmiltonaquino.com.br</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr"/>
+      <c r="I1330" t="inlineStr"/>
+      <c r="J1330" t="inlineStr"/>
+      <c r="K1330" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Dra. Karla Amaral - Odontologia</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>https://drakarlaamaral.com.br</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr"/>
+      <c r="I1331" t="inlineStr"/>
+      <c r="J1331" t="inlineStr"/>
+      <c r="K1331" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Iracema de Lima Cazella</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>https://iracemacazella.adv.br</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr"/>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>5582988510501</t>
+        </is>
+      </c>
+      <c r="J1332" t="inlineStr"/>
+      <c r="K1332" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Academia das Emoções</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>https://doity.com.br</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr"/>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>551151989901</t>
+        </is>
+      </c>
+      <c r="J1333" t="inlineStr"/>
+      <c r="K1333" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Dra Ive Almeida</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>https://draivealmeida.com.br</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr"/>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>5571993786306</t>
+        </is>
+      </c>
+      <c r="J1334" t="inlineStr"/>
+      <c r="K1334" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Plano Odontológico em Salvador</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>https://www.coberturaidealodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr"/>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>5511945429541</t>
+        </is>
+      </c>
+      <c r="J1335" t="inlineStr"/>
+      <c r="K1335" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Lucas Carapiá</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>https://www.lucascarapia.adv.br</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr"/>
+      <c r="I1336" t="inlineStr"/>
+      <c r="J1336" t="inlineStr"/>
+      <c r="K1336" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Advogado Previdenciário em Salvador</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.viniciusmacedoadvogado.adv.br</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr"/>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>557131901041</t>
+        </is>
+      </c>
+      <c r="J1337" t="inlineStr"/>
+      <c r="K1337" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>I Encontro de Advogados e Contadores de Salvador</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>https://www.crcba.org.br</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr"/>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>5571996461571</t>
+        </is>
+      </c>
+      <c r="J1338" t="inlineStr"/>
+      <c r="K1338" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Advogado Previdenciário</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>https://galvaoadvprevidenciaria.com.br</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr"/>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>551140033273</t>
+        </is>
+      </c>
+      <c r="J1339" t="inlineStr"/>
+      <c r="K1339" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta, fisioterapia, clínicas de fisioterapia em Salvador</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>https://buscacidade.com.br</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr"/>
+      <c r="I1340" t="inlineStr"/>
+      <c r="J1340" t="inlineStr"/>
+      <c r="K1340" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Salvador/BA</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>https://fisiohelp.com.br</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr"/>
+      <c r="I1341" t="inlineStr"/>
+      <c r="J1341" t="inlineStr"/>
+      <c r="K1341" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1341"/>
+  <dimension ref="A1:L1347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65237,10 +65237,8 @@
         </is>
       </c>
       <c r="H1329" t="inlineStr"/>
-      <c r="I1329" t="inlineStr">
-        <is>
-          <t>5582993327839</t>
-        </is>
+      <c r="I1329" t="n">
+        <v>5582993327839</v>
       </c>
       <c r="J1329" t="inlineStr"/>
       <c r="K1329" t="n">
@@ -65385,10 +65383,8 @@
         </is>
       </c>
       <c r="H1332" t="inlineStr"/>
-      <c r="I1332" t="inlineStr">
-        <is>
-          <t>5582988510501</t>
-        </is>
+      <c r="I1332" t="n">
+        <v>5582988510501</v>
       </c>
       <c r="J1332" t="inlineStr"/>
       <c r="K1332" t="n">
@@ -65437,10 +65433,8 @@
         </is>
       </c>
       <c r="H1333" t="inlineStr"/>
-      <c r="I1333" t="inlineStr">
-        <is>
-          <t>551151989901</t>
-        </is>
+      <c r="I1333" t="n">
+        <v>551151989901</v>
       </c>
       <c r="J1333" t="inlineStr"/>
       <c r="K1333" t="n">
@@ -65489,10 +65483,8 @@
         </is>
       </c>
       <c r="H1334" t="inlineStr"/>
-      <c r="I1334" t="inlineStr">
-        <is>
-          <t>5571993786306</t>
-        </is>
+      <c r="I1334" t="n">
+        <v>5571993786306</v>
       </c>
       <c r="J1334" t="inlineStr"/>
       <c r="K1334" t="n">
@@ -65541,10 +65533,8 @@
         </is>
       </c>
       <c r="H1335" t="inlineStr"/>
-      <c r="I1335" t="inlineStr">
-        <is>
-          <t>5511945429541</t>
-        </is>
+      <c r="I1335" t="n">
+        <v>5511945429541</v>
       </c>
       <c r="J1335" t="inlineStr"/>
       <c r="K1335" t="n">
@@ -65641,10 +65631,8 @@
         </is>
       </c>
       <c r="H1337" t="inlineStr"/>
-      <c r="I1337" t="inlineStr">
-        <is>
-          <t>557131901041</t>
-        </is>
+      <c r="I1337" t="n">
+        <v>557131901041</v>
       </c>
       <c r="J1337" t="inlineStr"/>
       <c r="K1337" t="n">
@@ -65693,10 +65681,8 @@
         </is>
       </c>
       <c r="H1338" t="inlineStr"/>
-      <c r="I1338" t="inlineStr">
-        <is>
-          <t>5571996461571</t>
-        </is>
+      <c r="I1338" t="n">
+        <v>5571996461571</v>
       </c>
       <c r="J1338" t="inlineStr"/>
       <c r="K1338" t="n">
@@ -65745,10 +65731,8 @@
         </is>
       </c>
       <c r="H1339" t="inlineStr"/>
-      <c r="I1339" t="inlineStr">
-        <is>
-          <t>551140033273</t>
-        </is>
+      <c r="I1339" t="n">
+        <v>551140033273</v>
       </c>
       <c r="J1339" t="inlineStr"/>
       <c r="K1339" t="n">
@@ -65856,6 +65840,302 @@
         </is>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Psicólogo em Brasília</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>https://buscadoutor.com.br</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr"/>
+      <c r="I1342" t="inlineStr"/>
+      <c r="J1342" t="inlineStr"/>
+      <c r="K1342" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Venâncio Advocacia em Brasília</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>https://www.venancioadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr"/>
+      <c r="I1343" t="inlineStr"/>
+      <c r="J1343" t="inlineStr"/>
+      <c r="K1343" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Clínica médica e check-up em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>https://drjosevictor.com</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr"/>
+      <c r="I1344" t="inlineStr"/>
+      <c r="J1344" t="inlineStr"/>
+      <c r="K1344" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Musculação em Goiânia — Aula Experimental</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>https://athosacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr"/>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>556232801214</t>
+        </is>
+      </c>
+      <c r="J1345" t="inlineStr"/>
+      <c r="K1345" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>ABBA Fisioterapia em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>https://abbafisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr"/>
+      <c r="I1346" t="inlineStr"/>
+      <c r="J1346" t="inlineStr"/>
+      <c r="K1346" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia Goiânia</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>https://antoniofisio.com</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr"/>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>5562981040646</t>
+        </is>
+      </c>
+      <c r="J1347" t="inlineStr"/>
+      <c r="K1347" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1347"/>
+  <dimension ref="A1:L1357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66021,10 +66021,8 @@
         </is>
       </c>
       <c r="H1345" t="inlineStr"/>
-      <c r="I1345" t="inlineStr">
-        <is>
-          <t>556232801214</t>
-        </is>
+      <c r="I1345" t="n">
+        <v>556232801214</v>
       </c>
       <c r="J1345" t="inlineStr"/>
       <c r="K1345" t="n">
@@ -66121,16 +66119,522 @@
         </is>
       </c>
       <c r="H1347" t="inlineStr"/>
-      <c r="I1347" t="inlineStr">
-        <is>
-          <t>5562981040646</t>
-        </is>
+      <c r="I1347" t="n">
+        <v>5562981040646</v>
       </c>
       <c r="J1347" t="inlineStr"/>
       <c r="K1347" t="n">
         <v>62</v>
       </c>
       <c r="L1347" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Melhores clínica médica em Vitória</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>https://melhorguiabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr"/>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>5512982224742</t>
+        </is>
+      </c>
+      <c r="J1348" t="inlineStr"/>
+      <c r="K1348" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Advogado em Vitória ES</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>https://www.alissonbrandao.com.br</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr"/>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>5527992291973</t>
+        </is>
+      </c>
+      <c r="J1349" t="inlineStr"/>
+      <c r="K1349" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Abreu Júdice Advogados</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>https://www.abreujudice.com.br</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr"/>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>5527992486930</t>
+        </is>
+      </c>
+      <c r="J1350" t="inlineStr"/>
+      <c r="K1350" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Clínica Gontijo</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>https://www.clinicagontijo.com.br</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr"/>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>5531993042072</t>
+        </is>
+      </c>
+      <c r="J1351" t="inlineStr"/>
+      <c r="K1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Núcleo Odontológico Savassi</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>https://www.odontosavassi.com.br</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr"/>
+      <c r="I1352" t="inlineStr"/>
+      <c r="J1352" t="inlineStr"/>
+      <c r="K1352" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Dr Claudio Costa</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>https://www.drclaudiocosta.com.br</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr"/>
+      <c r="I1353" t="inlineStr"/>
+      <c r="J1353" t="inlineStr"/>
+      <c r="K1353" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1353" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Ângela Tupynambá Odontologia: Home</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>https://tupynambaodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr"/>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>5531987678683</t>
+        </is>
+      </c>
+      <c r="J1354" t="inlineStr"/>
+      <c r="K1354" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Leonardo Mendes</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>https://advogadoleonardomendes.com.br</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr"/>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>5531998663303</t>
+        </is>
+      </c>
+      <c r="J1355" t="inlineStr"/>
+      <c r="K1355" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Academias no Planalto</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>https://pratiquefitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr"/>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>553141411962</t>
+        </is>
+      </c>
+      <c r="J1356" t="inlineStr"/>
+      <c r="K1356" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>ProntoAme Duque de Caxias</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>https://prontoame.com.br</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr"/>
+      <c r="I1357" t="inlineStr"/>
+      <c r="J1357" t="inlineStr"/>
+      <c r="K1357" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1357" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1357"/>
+  <dimension ref="A1:L1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66169,10 +66169,8 @@
         </is>
       </c>
       <c r="H1348" t="inlineStr"/>
-      <c r="I1348" t="inlineStr">
-        <is>
-          <t>5512982224742</t>
-        </is>
+      <c r="I1348" t="n">
+        <v>5512982224742</v>
       </c>
       <c r="J1348" t="inlineStr"/>
       <c r="K1348" t="n">
@@ -66221,10 +66219,8 @@
         </is>
       </c>
       <c r="H1349" t="inlineStr"/>
-      <c r="I1349" t="inlineStr">
-        <is>
-          <t>5527992291973</t>
-        </is>
+      <c r="I1349" t="n">
+        <v>5527992291973</v>
       </c>
       <c r="J1349" t="inlineStr"/>
       <c r="K1349" t="n">
@@ -66273,10 +66269,8 @@
         </is>
       </c>
       <c r="H1350" t="inlineStr"/>
-      <c r="I1350" t="inlineStr">
-        <is>
-          <t>5527992486930</t>
-        </is>
+      <c r="I1350" t="n">
+        <v>5527992486930</v>
       </c>
       <c r="J1350" t="inlineStr"/>
       <c r="K1350" t="n">
@@ -66325,10 +66319,8 @@
         </is>
       </c>
       <c r="H1351" t="inlineStr"/>
-      <c r="I1351" t="inlineStr">
-        <is>
-          <t>5531993042072</t>
-        </is>
+      <c r="I1351" t="n">
+        <v>5531993042072</v>
       </c>
       <c r="J1351" t="inlineStr"/>
       <c r="K1351" t="n">
@@ -66473,10 +66465,8 @@
         </is>
       </c>
       <c r="H1354" t="inlineStr"/>
-      <c r="I1354" t="inlineStr">
-        <is>
-          <t>5531987678683</t>
-        </is>
+      <c r="I1354" t="n">
+        <v>5531987678683</v>
       </c>
       <c r="J1354" t="inlineStr"/>
       <c r="K1354" t="n">
@@ -66525,10 +66515,8 @@
         </is>
       </c>
       <c r="H1355" t="inlineStr"/>
-      <c r="I1355" t="inlineStr">
-        <is>
-          <t>5531998663303</t>
-        </is>
+      <c r="I1355" t="n">
+        <v>5531998663303</v>
       </c>
       <c r="J1355" t="inlineStr"/>
       <c r="K1355" t="n">
@@ -66577,10 +66565,8 @@
         </is>
       </c>
       <c r="H1356" t="inlineStr"/>
-      <c r="I1356" t="inlineStr">
-        <is>
-          <t>553141411962</t>
-        </is>
+      <c r="I1356" t="n">
+        <v>553141411962</v>
       </c>
       <c r="J1356" t="inlineStr"/>
       <c r="K1356" t="n">
@@ -66640,6 +66626,258 @@
         </is>
       </c>
     </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Hospital Los Angeles</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>https://clinicalosangeles.com.br</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr"/>
+      <c r="I1358" t="inlineStr"/>
+      <c r="J1358" t="inlineStr"/>
+      <c r="K1358" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1358" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Luge Odontologia</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>https://lugeodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr"/>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>555192373628</t>
+        </is>
+      </c>
+      <c r="J1359" t="inlineStr"/>
+      <c r="K1359" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1359" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Psicólogo em Porto Alegre: os 10 mais recomendados</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>https://saudeperto.com.br</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr"/>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>5511978817415</t>
+        </is>
+      </c>
+      <c r="J1360" t="inlineStr"/>
+      <c r="K1360" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1360" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Advogado em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>https://www.rodrigonunesadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr"/>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>5551995183531</t>
+        </is>
+      </c>
+      <c r="J1361" t="inlineStr"/>
+      <c r="K1361" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1361" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>PRATES Advogados - Assessoria Jurídica</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>https://pratesadvogados.com</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr"/>
+      <c r="I1362" t="inlineStr"/>
+      <c r="J1362" t="inlineStr"/>
+      <c r="K1362" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1362" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1362"/>
+  <dimension ref="A1:L1368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66711,10 +66711,8 @@
         </is>
       </c>
       <c r="H1359" t="inlineStr"/>
-      <c r="I1359" t="inlineStr">
-        <is>
-          <t>555192373628</t>
-        </is>
+      <c r="I1359" t="n">
+        <v>555192373628</v>
       </c>
       <c r="J1359" t="inlineStr"/>
       <c r="K1359" t="n">
@@ -66763,10 +66761,8 @@
         </is>
       </c>
       <c r="H1360" t="inlineStr"/>
-      <c r="I1360" t="inlineStr">
-        <is>
-          <t>5511978817415</t>
-        </is>
+      <c r="I1360" t="n">
+        <v>5511978817415</v>
       </c>
       <c r="J1360" t="inlineStr"/>
       <c r="K1360" t="n">
@@ -66815,10 +66811,8 @@
         </is>
       </c>
       <c r="H1361" t="inlineStr"/>
-      <c r="I1361" t="inlineStr">
-        <is>
-          <t>5551995183531</t>
-        </is>
+      <c r="I1361" t="n">
+        <v>5551995183531</v>
       </c>
       <c r="J1361" t="inlineStr"/>
       <c r="K1361" t="n">
@@ -66878,6 +66872,310 @@
         </is>
       </c>
     </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>https://r3academia.com.br</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr"/>
+      <c r="I1363" t="inlineStr"/>
+      <c r="J1363" t="inlineStr"/>
+      <c r="K1363" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1363" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Rede Odonto Manaus</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>https://www.redeodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr"/>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>558009428441</t>
+        </is>
+      </c>
+      <c r="J1364" t="inlineStr"/>
+      <c r="K1364" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1364" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica em Manaus</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>https://iobmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr"/>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>5592993055407</t>
+        </is>
+      </c>
+      <c r="J1365" t="inlineStr"/>
+      <c r="K1365" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1365" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Faculdades de Educação Física em Manaus - AM</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>https://qm-render-quero-bolsa.quero.space</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr"/>
+      <c r="I1366" t="inlineStr"/>
+      <c r="J1366" t="inlineStr"/>
+      <c r="K1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1366" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Selfit em MANAUS</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>https://www.academiasselfit.com.br</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr"/>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>558137889709</t>
+        </is>
+      </c>
+      <c r="J1367" t="inlineStr"/>
+      <c r="K1367" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1367" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Physioclin Manaus</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>https://physioclinmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr"/>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>5592994080673</t>
+        </is>
+      </c>
+      <c r="J1368" t="inlineStr"/>
+      <c r="K1368" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1368" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1368"/>
+  <dimension ref="A1:L1371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66957,10 +66957,8 @@
         </is>
       </c>
       <c r="H1364" t="inlineStr"/>
-      <c r="I1364" t="inlineStr">
-        <is>
-          <t>558009428441</t>
-        </is>
+      <c r="I1364" t="n">
+        <v>558009428441</v>
       </c>
       <c r="J1364" t="inlineStr"/>
       <c r="K1364" t="n">
@@ -67009,10 +67007,8 @@
         </is>
       </c>
       <c r="H1365" t="inlineStr"/>
-      <c r="I1365" t="inlineStr">
-        <is>
-          <t>5592993055407</t>
-        </is>
+      <c r="I1365" t="n">
+        <v>5592993055407</v>
       </c>
       <c r="J1365" t="inlineStr"/>
       <c r="K1365" t="n">
@@ -67109,10 +67105,8 @@
         </is>
       </c>
       <c r="H1367" t="inlineStr"/>
-      <c r="I1367" t="inlineStr">
-        <is>
-          <t>558137889709</t>
-        </is>
+      <c r="I1367" t="n">
+        <v>558137889709</v>
       </c>
       <c r="J1367" t="inlineStr"/>
       <c r="K1367" t="n">
@@ -67161,16 +67155,162 @@
         </is>
       </c>
       <c r="H1368" t="inlineStr"/>
-      <c r="I1368" t="inlineStr">
-        <is>
-          <t>5592994080673</t>
-        </is>
+      <c r="I1368" t="n">
+        <v>5592994080673</v>
       </c>
       <c r="J1368" t="inlineStr"/>
       <c r="K1368" t="n">
         <v>69</v>
       </c>
       <c r="L1368" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>William Torquato</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>https://www.williamtorquato.com.br</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr"/>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>5582981622319</t>
+        </is>
+      </c>
+      <c r="J1369" t="inlineStr"/>
+      <c r="K1369" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1369" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Clínica Médica Popular em Boca do Rio</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>https://bocadorio.atendja.com.br</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr"/>
+      <c r="I1370" t="inlineStr"/>
+      <c r="J1370" t="inlineStr"/>
+      <c r="K1370" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1370" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Encontre seu Médico</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>https://sbotba.com.br</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr"/>
+      <c r="I1371" t="inlineStr"/>
+      <c r="J1371" t="inlineStr"/>
+      <c r="K1371" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1371" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1371"/>
+  <dimension ref="A1:L1373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67205,10 +67205,8 @@
         </is>
       </c>
       <c r="H1369" t="inlineStr"/>
-      <c r="I1369" t="inlineStr">
-        <is>
-          <t>5582981622319</t>
-        </is>
+      <c r="I1369" t="n">
+        <v>5582981622319</v>
       </c>
       <c r="J1369" t="inlineStr"/>
       <c r="K1369" t="n">
@@ -67316,6 +67314,106 @@
         </is>
       </c>
     </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Psicólogo em Brasília</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>https://espacocontato.com.br</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr"/>
+      <c r="I1372" t="inlineStr"/>
+      <c r="J1372" t="inlineStr"/>
+      <c r="K1372" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1372" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Jayme Advogados</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>https://www.jaymeadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr"/>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>5562998622020</t>
+        </is>
+      </c>
+      <c r="J1373" t="inlineStr"/>
+      <c r="K1373" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1373" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1373"/>
+  <dimension ref="A1:L1384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67399,16 +67399,562 @@
         </is>
       </c>
       <c r="H1373" t="inlineStr"/>
-      <c r="I1373" t="inlineStr">
-        <is>
-          <t>5562998622020</t>
-        </is>
+      <c r="I1373" t="n">
+        <v>5562998622020</v>
       </c>
       <c r="J1373" t="inlineStr"/>
       <c r="K1373" t="n">
         <v>64</v>
       </c>
       <c r="L1373" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Centro Médico Jardins</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>https://corpoinforma.com</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr"/>
+      <c r="I1374" t="inlineStr"/>
+      <c r="J1374" t="inlineStr"/>
+      <c r="K1374" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1374" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Dra. Priscilla Guerra</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>https://www.drapriscillaguerra.com.br</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr"/>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>5527999152800</t>
+        </is>
+      </c>
+      <c r="J1375" t="inlineStr"/>
+      <c r="K1375" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1375" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Psicólogo Clínico em Vitória-ES por Chander Rian</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>https://psicologochander.com</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr"/>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>5527992493643</t>
+        </is>
+      </c>
+      <c r="J1376" t="inlineStr"/>
+      <c r="K1376" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1376" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Psicólogo Clínico em Vitória-ES</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>https://www.psiwelligtonqueiroz.com.br</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr"/>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>5527995140965</t>
+        </is>
+      </c>
+      <c r="J1377" t="inlineStr"/>
+      <c r="K1377" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1377" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Dr. Síderson Vitorino — Advogado</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>https://advsidersonvitorino.advtop.adv.br</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr"/>
+      <c r="I1378" t="inlineStr"/>
+      <c r="J1378" t="inlineStr"/>
+      <c r="K1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1378" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Andrade Domingos Advocacia</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>https://lista.adv.br</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr"/>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>5548999287716</t>
+        </is>
+      </c>
+      <c r="J1379" t="inlineStr"/>
+      <c r="K1379" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1379" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Academia Vitória Fitness</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>https://academiavitoriafitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr"/>
+      <c r="I1380" t="inlineStr"/>
+      <c r="J1380" t="inlineStr"/>
+      <c r="K1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1380" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Clínica Médica em BH</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>https://bhconsulta.com.br</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr"/>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>553132317500</t>
+        </is>
+      </c>
+      <c r="J1381" t="inlineStr"/>
+      <c r="K1381" t="n">
+        <v>71</v>
+      </c>
+      <c r="L1381" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Aba Saúde</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>https://www.abasaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr"/>
+      <c r="I1382" t="inlineStr"/>
+      <c r="J1382" t="inlineStr"/>
+      <c r="K1382" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1382" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Terapeutas em Belo Horizonte/MG</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>https://teravy.com.br</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr"/>
+      <c r="I1383" t="inlineStr"/>
+      <c r="J1383" t="inlineStr"/>
+      <c r="K1383" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1383" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>Academia em Belo Horizonte MG (2026)</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>https://bhguialocal.com.br</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr"/>
+      <c r="I1384" t="inlineStr"/>
+      <c r="J1384" t="inlineStr"/>
+      <c r="K1384" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1384" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1384"/>
+  <dimension ref="A1:L1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67497,10 +67497,8 @@
         </is>
       </c>
       <c r="H1375" t="inlineStr"/>
-      <c r="I1375" t="inlineStr">
-        <is>
-          <t>5527999152800</t>
-        </is>
+      <c r="I1375" t="n">
+        <v>5527999152800</v>
       </c>
       <c r="J1375" t="inlineStr"/>
       <c r="K1375" t="n">
@@ -67549,10 +67547,8 @@
         </is>
       </c>
       <c r="H1376" t="inlineStr"/>
-      <c r="I1376" t="inlineStr">
-        <is>
-          <t>5527992493643</t>
-        </is>
+      <c r="I1376" t="n">
+        <v>5527992493643</v>
       </c>
       <c r="J1376" t="inlineStr"/>
       <c r="K1376" t="n">
@@ -67601,10 +67597,8 @@
         </is>
       </c>
       <c r="H1377" t="inlineStr"/>
-      <c r="I1377" t="inlineStr">
-        <is>
-          <t>5527995140965</t>
-        </is>
+      <c r="I1377" t="n">
+        <v>5527995140965</v>
       </c>
       <c r="J1377" t="inlineStr"/>
       <c r="K1377" t="n">
@@ -67701,10 +67695,8 @@
         </is>
       </c>
       <c r="H1379" t="inlineStr"/>
-      <c r="I1379" t="inlineStr">
-        <is>
-          <t>5548999287716</t>
-        </is>
+      <c r="I1379" t="n">
+        <v>5548999287716</v>
       </c>
       <c r="J1379" t="inlineStr"/>
       <c r="K1379" t="n">
@@ -67801,10 +67793,8 @@
         </is>
       </c>
       <c r="H1381" t="inlineStr"/>
-      <c r="I1381" t="inlineStr">
-        <is>
-          <t>553132317500</t>
-        </is>
+      <c r="I1381" t="n">
+        <v>553132317500</v>
       </c>
       <c r="J1381" t="inlineStr"/>
       <c r="K1381" t="n">
@@ -67960,6 +67950,458 @@
         </is>
       </c>
     </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Ana Campelo — Psicóloga e Terapeuta EMDR</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>https://psicologaanacampelo.com.br</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr"/>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>5541992558780</t>
+        </is>
+      </c>
+      <c r="J1385" t="inlineStr"/>
+      <c r="K1385" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1385" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Yuri Adriano Farias — Advogado</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>https://yurifariasadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr"/>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>5541997098106</t>
+        </is>
+      </c>
+      <c r="J1386" t="inlineStr"/>
+      <c r="K1386" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1386" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Academia Azure - Musculação</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>https://azureacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr"/>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>5541987362988</t>
+        </is>
+      </c>
+      <c r="J1387" t="inlineStr"/>
+      <c r="K1387" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1387" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>https://www.perto-de-mim.com</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr"/>
+      <c r="I1388" t="inlineStr"/>
+      <c r="J1388" t="inlineStr"/>
+      <c r="K1388" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1388" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>https://abertaagora.com.br</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr"/>
+      <c r="I1389" t="inlineStr"/>
+      <c r="J1389" t="inlineStr"/>
+      <c r="K1389" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1389" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Clinica Médica</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>https://www.clinicajb.com</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr"/>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>5551993599720</t>
+        </is>
+      </c>
+      <c r="J1390" t="inlineStr"/>
+      <c r="K1390" t="n">
+        <v>71</v>
+      </c>
+      <c r="L1390" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Psicólogo em Porto Alegre e Online</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>https://psiandrecintra.com.br</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr"/>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>5551991659872</t>
+        </is>
+      </c>
+      <c r="J1391" t="inlineStr"/>
+      <c r="K1391" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1391" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Escola Superior de Educação Física (ESEF)</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>https://wikimapia.org</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr"/>
+      <c r="I1392" t="inlineStr"/>
+      <c r="J1392" t="inlineStr"/>
+      <c r="K1392" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1392" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Academias em Porto Alegre, RS</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>https://esportecidade.com</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="inlineStr"/>
+      <c r="J1393" t="inlineStr"/>
+      <c r="K1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1393" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1393"/>
+  <dimension ref="A1:L1406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67987,10 +67987,8 @@
         </is>
       </c>
       <c r="H1385" t="inlineStr"/>
-      <c r="I1385" t="inlineStr">
-        <is>
-          <t>5541992558780</t>
-        </is>
+      <c r="I1385" t="n">
+        <v>5541992558780</v>
       </c>
       <c r="J1385" t="inlineStr"/>
       <c r="K1385" t="n">
@@ -68039,10 +68037,8 @@
         </is>
       </c>
       <c r="H1386" t="inlineStr"/>
-      <c r="I1386" t="inlineStr">
-        <is>
-          <t>5541997098106</t>
-        </is>
+      <c r="I1386" t="n">
+        <v>5541997098106</v>
       </c>
       <c r="J1386" t="inlineStr"/>
       <c r="K1386" t="n">
@@ -68091,10 +68087,8 @@
         </is>
       </c>
       <c r="H1387" t="inlineStr"/>
-      <c r="I1387" t="inlineStr">
-        <is>
-          <t>5541987362988</t>
-        </is>
+      <c r="I1387" t="n">
+        <v>5541987362988</v>
       </c>
       <c r="J1387" t="inlineStr"/>
       <c r="K1387" t="n">
@@ -68239,10 +68233,8 @@
         </is>
       </c>
       <c r="H1390" t="inlineStr"/>
-      <c r="I1390" t="inlineStr">
-        <is>
-          <t>5551993599720</t>
-        </is>
+      <c r="I1390" t="n">
+        <v>5551993599720</v>
       </c>
       <c r="J1390" t="inlineStr"/>
       <c r="K1390" t="n">
@@ -68291,10 +68283,8 @@
         </is>
       </c>
       <c r="H1391" t="inlineStr"/>
-      <c r="I1391" t="inlineStr">
-        <is>
-          <t>5551991659872</t>
-        </is>
+      <c r="I1391" t="n">
+        <v>5551991659872</v>
       </c>
       <c r="J1391" t="inlineStr"/>
       <c r="K1391" t="n">
@@ -68402,6 +68392,630 @@
         </is>
       </c>
     </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Trabalhe Conosco</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>https://portal.ac.senac.br</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr"/>
+      <c r="I1394" t="inlineStr"/>
+      <c r="J1394" t="inlineStr"/>
+      <c r="K1394" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1394" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Arteterapia como estratégia de cuidado em saúde mental no âmbito ...</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>https://jmphc.emnuvens.com.br</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr"/>
+      <c r="I1395" t="inlineStr"/>
+      <c r="J1395" t="inlineStr"/>
+      <c r="K1395" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1395" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>https://paulosilva.site.med.br</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr"/>
+      <c r="I1396" t="inlineStr"/>
+      <c r="J1396" t="inlineStr"/>
+      <c r="K1396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1396" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Chabab Atlas Khenifra vs Itihad Khemisset</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>https://tips.gg</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr"/>
+      <c r="I1397" t="inlineStr"/>
+      <c r="J1397" t="inlineStr"/>
+      <c r="K1397" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1397" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Chabab Atlas Khenifra vs Ittihad Zemmouri Khemisset live score...</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>https://www.aiscore.com</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="inlineStr"/>
+      <c r="J1398" t="inlineStr"/>
+      <c r="K1398" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1398" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Prediksi Chabab Atl. Khenifra vs Ittihad Khemisset Botola 2 Hari...</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>https://nobartv.co.id</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr"/>
+      <c r="I1399" t="inlineStr"/>
+      <c r="J1399" t="inlineStr"/>
+      <c r="K1399" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1399" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Chabab Atlas Khénifra vs Ittihad Khemisset</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>https://iptv.events</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr"/>
+      <c r="I1400" t="inlineStr"/>
+      <c r="J1400" t="inlineStr"/>
+      <c r="K1400" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1400" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Chabab Atlas Khenifra vs Itihad Z. Khemisset Live Score &amp; Results...</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>https://ooscore.com</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr"/>
+      <c r="I1401" t="inlineStr"/>
+      <c r="J1401" t="inlineStr"/>
+      <c r="K1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1401" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Khenifra vs Itihad Khemisset live score, result and stats |...</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>https://www.matchplay.com</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr"/>
+      <c r="I1402" t="inlineStr"/>
+      <c r="J1402" t="inlineStr"/>
+      <c r="K1402" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1402" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Chabab Atlas Khenifra</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>https://offsidescores.com</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr"/>
+      <c r="I1403" t="inlineStr"/>
+      <c r="J1403" t="inlineStr"/>
+      <c r="K1403" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1403" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Chabab Atl. Khenifra vs Ittihad Khemisset</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>https://streamzeast.com</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr"/>
+      <c r="I1404" t="inlineStr"/>
+      <c r="J1404" t="inlineStr"/>
+      <c r="K1404" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1404" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>Peter J De Tolla DDS PC - Dentist in Levittown, NY</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>https://www.detolladental.com</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr"/>
+      <c r="I1405" t="inlineStr"/>
+      <c r="J1405" t="inlineStr"/>
+      <c r="K1405" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1405" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Dentist in Levittown, NY</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>https://www.godental365.com</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr"/>
+      <c r="I1406" t="inlineStr"/>
+      <c r="J1406" t="inlineStr"/>
+      <c r="K1406" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1406" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1406"/>
+  <dimension ref="A1:L1411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69016,6 +69016,258 @@
         </is>
       </c>
     </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Dra. Michelle Cavalcante: Dentista em Maceió!</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>https://dramichellecavalcante.com.br</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr"/>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>5582987441650</t>
+        </is>
+      </c>
+      <c r="J1407" t="inlineStr"/>
+      <c r="K1407" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1407" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Hugo Monteiro Advocacia</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>https://hugomonteiroadvocacia.com</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr"/>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>5582982214733</t>
+        </is>
+      </c>
+      <c r="J1408" t="inlineStr"/>
+      <c r="K1408" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1408" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Sousa &amp; Sousa Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>https://sousaesousaadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr"/>
+      <c r="I1409" t="inlineStr"/>
+      <c r="J1409" t="inlineStr"/>
+      <c r="K1409" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1409" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Clínicas médicas em Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>https://assistenciamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr"/>
+      <c r="I1410" t="inlineStr"/>
+      <c r="J1410" t="inlineStr"/>
+      <c r="K1410" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1410" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Top Saúde</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>https://topsaudeclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr"/>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>558530110158</t>
+        </is>
+      </c>
+      <c r="J1411" t="inlineStr"/>
+      <c r="K1411" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1411" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1411"/>
+  <dimension ref="A1:L1414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69053,10 +69053,8 @@
         </is>
       </c>
       <c r="H1407" t="inlineStr"/>
-      <c r="I1407" t="inlineStr">
-        <is>
-          <t>5582987441650</t>
-        </is>
+      <c r="I1407" t="n">
+        <v>5582987441650</v>
       </c>
       <c r="J1407" t="inlineStr"/>
       <c r="K1407" t="n">
@@ -69105,10 +69103,8 @@
         </is>
       </c>
       <c r="H1408" t="inlineStr"/>
-      <c r="I1408" t="inlineStr">
-        <is>
-          <t>5582982214733</t>
-        </is>
+      <c r="I1408" t="n">
+        <v>5582982214733</v>
       </c>
       <c r="J1408" t="inlineStr"/>
       <c r="K1408" t="n">
@@ -69253,16 +69249,162 @@
         </is>
       </c>
       <c r="H1411" t="inlineStr"/>
-      <c r="I1411" t="inlineStr">
-        <is>
-          <t>558530110158</t>
-        </is>
+      <c r="I1411" t="n">
+        <v>558530110158</v>
       </c>
       <c r="J1411" t="inlineStr"/>
       <c r="K1411" t="n">
         <v>81</v>
       </c>
       <c r="L1411" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>MRB Advogados</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>https://www.mrbadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr"/>
+      <c r="I1412" t="inlineStr"/>
+      <c r="J1412" t="inlineStr"/>
+      <c r="K1412" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1412" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Fernando Alves</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>https://www.fernandoalves.page</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr"/>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>5561999316023</t>
+        </is>
+      </c>
+      <c r="J1413" t="inlineStr"/>
+      <c r="K1413" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1413" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>SESI Goiás</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>https://sesigoias.com.br</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr"/>
+      <c r="I1414" t="inlineStr"/>
+      <c r="J1414" t="inlineStr"/>
+      <c r="K1414" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1414" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1414"/>
+  <dimension ref="A1:L1432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69347,10 +69347,8 @@
         </is>
       </c>
       <c r="H1413" t="inlineStr"/>
-      <c r="I1413" t="inlineStr">
-        <is>
-          <t>5561999316023</t>
-        </is>
+      <c r="I1413" t="n">
+        <v>5561999316023</v>
       </c>
       <c r="J1413" t="inlineStr"/>
       <c r="K1413" t="n">
@@ -69410,6 +69408,890 @@
         </is>
       </c>
     </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Centro Médico Jardins</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>https://centromedicojardins.com.br</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr"/>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>5527996207901</t>
+        </is>
+      </c>
+      <c r="J1415" t="inlineStr"/>
+      <c r="K1415" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1415" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Dra. Ligia</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>https://www.draligianeuropsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr"/>
+      <c r="I1416" t="inlineStr"/>
+      <c r="J1416" t="inlineStr"/>
+      <c r="K1416" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1416" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Soares Soares &amp; Nobre Advogados Associados ...</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>https://www.soaresnobreadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr"/>
+      <c r="I1417" t="inlineStr"/>
+      <c r="J1417" t="inlineStr"/>
+      <c r="K1417" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1417" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Centro de Educação Física e Desportos</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>https://visite.vitoria.net.br</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr"/>
+      <c r="I1418" t="inlineStr"/>
+      <c r="J1418" t="inlineStr"/>
+      <c r="K1418" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1418" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>CLINIFORT CLÍNICA MÉDICA</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>https://www.clinifort.com.br</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr"/>
+      <c r="I1419" t="inlineStr"/>
+      <c r="J1419" t="inlineStr"/>
+      <c r="K1419" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1419" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>Clínica Carijós</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>https://www.grupocarijos.com.br</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr"/>
+      <c r="I1420" t="inlineStr"/>
+      <c r="J1420" t="inlineStr"/>
+      <c r="K1420" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1420" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Dr. Guilherme Marques</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>https://www.drguilhermemarques.com</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr"/>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>5531972488306</t>
+        </is>
+      </c>
+      <c r="J1421" t="inlineStr"/>
+      <c r="K1421" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1421" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Valdir Lima</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>https://valdirlimapsicologo.com</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr"/>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>5531992786203</t>
+        </is>
+      </c>
+      <c r="J1422" t="inlineStr"/>
+      <c r="K1422" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1422" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Marcos Paulo</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>https://psicologomarcospaulo.com.br</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr"/>
+      <c r="I1423" t="inlineStr"/>
+      <c r="J1423" t="inlineStr"/>
+      <c r="K1423" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1423" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>Adalberto Ferraz de Paula Dantas Psicólogo e Psicanalista em Belo ...</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>https://www.adalbertodantaspsicologo.com.br</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr"/>
+      <c r="I1424" t="inlineStr"/>
+      <c r="J1424" t="inlineStr"/>
+      <c r="K1424" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1424" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Eduardo Araújo - Advogados e Consultores</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>https://www.araujoconsultores.com</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr"/>
+      <c r="I1425" t="inlineStr"/>
+      <c r="J1425" t="inlineStr"/>
+      <c r="K1425" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1425" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>educação física (bacharelado)</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>https://universo.edu.br</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr"/>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>5508007210251</t>
+        </is>
+      </c>
+      <c r="J1426" t="inlineStr"/>
+      <c r="K1426" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1426" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Vista do Percepção da educação física escolar em escolas de ...</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>https://portalrevistas.ucb.br</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr"/>
+      <c r="I1427" t="inlineStr"/>
+      <c r="J1427" t="inlineStr"/>
+      <c r="K1427" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1427" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>Medidas disciplinadoras na Educação Física em diferentes ...</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>https://retratosdaescola.emnuvens.com.br</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr"/>
+      <c r="I1428" t="inlineStr"/>
+      <c r="J1428" t="inlineStr"/>
+      <c r="K1428" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1428" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>Academias em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>https://gymbelohorizonte.com</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr"/>
+      <c r="I1429" t="inlineStr"/>
+      <c r="J1429" t="inlineStr"/>
+      <c r="K1429" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1429" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>Nova Home</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>https://imagemacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr"/>
+      <c r="I1430" t="inlineStr"/>
+      <c r="J1430" t="inlineStr"/>
+      <c r="K1430" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1430" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>Única-Gym</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>https://unicagym.com.br</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr"/>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>553171925828</t>
+        </is>
+      </c>
+      <c r="J1431" t="inlineStr"/>
+      <c r="K1431" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1431" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>Top 10+ Dentists in Rio De Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>https://www.whatclinic.com</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr"/>
+      <c r="I1432" t="inlineStr"/>
+      <c r="J1432" t="inlineStr"/>
+      <c r="K1432" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1432" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1432"/>
+  <dimension ref="A1:L1456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69445,10 +69445,8 @@
         </is>
       </c>
       <c r="H1415" t="inlineStr"/>
-      <c r="I1415" t="inlineStr">
-        <is>
-          <t>5527996207901</t>
-        </is>
+      <c r="I1415" t="n">
+        <v>5527996207901</v>
       </c>
       <c r="J1415" t="inlineStr"/>
       <c r="K1415" t="n">
@@ -69737,10 +69735,8 @@
         </is>
       </c>
       <c r="H1421" t="inlineStr"/>
-      <c r="I1421" t="inlineStr">
-        <is>
-          <t>5531972488306</t>
-        </is>
+      <c r="I1421" t="n">
+        <v>5531972488306</v>
       </c>
       <c r="J1421" t="inlineStr"/>
       <c r="K1421" t="n">
@@ -69789,10 +69785,8 @@
         </is>
       </c>
       <c r="H1422" t="inlineStr"/>
-      <c r="I1422" t="inlineStr">
-        <is>
-          <t>5531992786203</t>
-        </is>
+      <c r="I1422" t="n">
+        <v>5531992786203</v>
       </c>
       <c r="J1422" t="inlineStr"/>
       <c r="K1422" t="n">
@@ -69985,10 +69979,8 @@
         </is>
       </c>
       <c r="H1426" t="inlineStr"/>
-      <c r="I1426" t="inlineStr">
-        <is>
-          <t>5508007210251</t>
-        </is>
+      <c r="I1426" t="n">
+        <v>5508007210251</v>
       </c>
       <c r="J1426" t="inlineStr"/>
       <c r="K1426" t="n">
@@ -70229,10 +70221,8 @@
         </is>
       </c>
       <c r="H1431" t="inlineStr"/>
-      <c r="I1431" t="inlineStr">
-        <is>
-          <t>553171925828</t>
-        </is>
+      <c r="I1431" t="n">
+        <v>553171925828</v>
       </c>
       <c r="J1431" t="inlineStr"/>
       <c r="K1431" t="n">
@@ -70292,6 +70282,1202 @@
         </is>
       </c>
     </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>9ª Jornada Paranaense de Clínica Médica acontece em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>https://www.sbcm.org.br</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr"/>
+      <c r="I1433" t="inlineStr"/>
+      <c r="J1433" t="inlineStr"/>
+      <c r="K1433" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1433" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>MEET Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>https://clinicameet.com.br</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr"/>
+      <c r="I1434" t="inlineStr"/>
+      <c r="J1434" t="inlineStr"/>
+      <c r="K1434" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1434" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>Clínica Médica Dr. Felipe Miceli</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>https://drfelipemiceli.com.br</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr"/>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>5541991543211</t>
+        </is>
+      </c>
+      <c r="J1435" t="inlineStr"/>
+      <c r="K1435" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1435" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>Dentistas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>https://agendadent.com.br</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr"/>
+      <c r="I1436" t="inlineStr"/>
+      <c r="J1436" t="inlineStr"/>
+      <c r="K1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1436" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>Dr. Rodrigo Silva</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>https://www.drrodrigosilva.com</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr"/>
+      <c r="I1437" t="inlineStr"/>
+      <c r="J1437" t="inlineStr"/>
+      <c r="K1437" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1437" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>Clinica Soma Psicologia</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>https://www.soma.psc.br</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr"/>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>5541996325947</t>
+        </is>
+      </c>
+      <c r="J1438" t="inlineStr"/>
+      <c r="K1438" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1438" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>Clever Gonçalves</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>https://cleverpsicologo.com.br</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr"/>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>5541997561144</t>
+        </is>
+      </c>
+      <c r="J1439" t="inlineStr"/>
+      <c r="K1439" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1439" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>Leandro Paes</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>https://www.psicologoleandropaes.com</t>
+        </is>
+      </c>
+      <c r="H1440" t="inlineStr"/>
+      <c r="I1440" t="inlineStr"/>
+      <c r="J1440" t="inlineStr"/>
+      <c r="K1440" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1440" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>Psicóloga em Curitiba - Rosane Dias de Almeida</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>https://www.psicologacuritiba.com</t>
+        </is>
+      </c>
+      <c r="H1441" t="inlineStr"/>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>5541999445900</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr"/>
+      <c r="K1441" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1441" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>Terapia Viva</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>https://www.terapiaviva.com.br</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr"/>
+      <c r="I1442" t="inlineStr"/>
+      <c r="J1442" t="inlineStr"/>
+      <c r="K1442" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1442" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>Nossa História no Centro de Psicoterapia Corporal ...</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>https://centroreichiano.com.br</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr"/>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>5541991140425</t>
+        </is>
+      </c>
+      <c r="J1443" t="inlineStr"/>
+      <c r="K1443" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1443" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>Instituto Paranaense de Terapias Cognitivas: IPTC</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>https://iptc.net.br</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr"/>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>5541992632977</t>
+        </is>
+      </c>
+      <c r="J1444" t="inlineStr"/>
+      <c r="K1444" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1444" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>Advogado Inventário e Herança Curitiba</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>https://www.jasteradvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr"/>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>5541996522171</t>
+        </is>
+      </c>
+      <c r="J1445" t="inlineStr"/>
+      <c r="K1445" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1445" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>rangel de miranda advogados</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>https://www.rangeldemiranda.com.br</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr"/>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>554130575050</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr"/>
+      <c r="K1446" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1446" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>VP Advocacia: Home</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>https://www.vp.adv.br</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr"/>
+      <c r="I1447" t="inlineStr"/>
+      <c r="J1447" t="inlineStr"/>
+      <c r="K1447" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1447" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>Power Camp</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>https://powercampbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr"/>
+      <c r="I1448" t="inlineStr"/>
+      <c r="J1448" t="inlineStr"/>
+      <c r="K1448" t="n">
+        <v>40</v>
+      </c>
+      <c r="L1448" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>Onda das academias gigantes chega a Curitiba</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>https://www.bemparana.com.br</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr"/>
+      <c r="I1449" t="inlineStr"/>
+      <c r="J1449" t="inlineStr"/>
+      <c r="K1449" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1449" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>UPLAY Campo Comprido</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>https://academiauplaycc.com.br</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr"/>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>5541991765594</t>
+        </is>
+      </c>
+      <c r="J1450" t="inlineStr"/>
+      <c r="K1450" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1450" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>Fernanda Prestes Fisioterapeuta Domiciliar</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>https://www.fernandaprestesfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr"/>
+      <c r="I1451" t="inlineStr"/>
+      <c r="J1451" t="inlineStr"/>
+      <c r="K1451" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1451" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>Clínica Herter</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>https://clinicaherter.com.br</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr"/>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>5551999167650</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr"/>
+      <c r="K1452" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1452" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>Médicos que denominam ruas em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>https://www.amrigs.org.br</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr"/>
+      <c r="I1453" t="inlineStr"/>
+      <c r="J1453" t="inlineStr"/>
+      <c r="K1453" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1453" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>FundMed: Fundação Médica do Rio Grande do ...</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>https://fundmed.org.br</t>
+        </is>
+      </c>
+      <c r="H1454" t="inlineStr"/>
+      <c r="I1454" t="inlineStr"/>
+      <c r="J1454" t="inlineStr"/>
+      <c r="K1454" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1454" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>Psicóloga em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>https://www.psicologaflorence.com.br</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr"/>
+      <c r="I1455" t="inlineStr"/>
+      <c r="J1455" t="inlineStr"/>
+      <c r="K1455" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1455" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>https://aurapsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr"/>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>5551991495565</t>
+        </is>
+      </c>
+      <c r="J1456" t="inlineStr"/>
+      <c r="K1456" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1456" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1456"/>
+  <dimension ref="A1:L1481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70415,10 +70415,8 @@
         </is>
       </c>
       <c r="H1435" t="inlineStr"/>
-      <c r="I1435" t="inlineStr">
-        <is>
-          <t>5541991543211</t>
-        </is>
+      <c r="I1435" t="n">
+        <v>5541991543211</v>
       </c>
       <c r="J1435" t="inlineStr"/>
       <c r="K1435" t="n">
@@ -70563,10 +70561,8 @@
         </is>
       </c>
       <c r="H1438" t="inlineStr"/>
-      <c r="I1438" t="inlineStr">
-        <is>
-          <t>5541996325947</t>
-        </is>
+      <c r="I1438" t="n">
+        <v>5541996325947</v>
       </c>
       <c r="J1438" t="inlineStr"/>
       <c r="K1438" t="n">
@@ -70615,10 +70611,8 @@
         </is>
       </c>
       <c r="H1439" t="inlineStr"/>
-      <c r="I1439" t="inlineStr">
-        <is>
-          <t>5541997561144</t>
-        </is>
+      <c r="I1439" t="n">
+        <v>5541997561144</v>
       </c>
       <c r="J1439" t="inlineStr"/>
       <c r="K1439" t="n">
@@ -70715,10 +70709,8 @@
         </is>
       </c>
       <c r="H1441" t="inlineStr"/>
-      <c r="I1441" t="inlineStr">
-        <is>
-          <t>5541999445900</t>
-        </is>
+      <c r="I1441" t="n">
+        <v>5541999445900</v>
       </c>
       <c r="J1441" t="inlineStr"/>
       <c r="K1441" t="n">
@@ -70815,10 +70807,8 @@
         </is>
       </c>
       <c r="H1443" t="inlineStr"/>
-      <c r="I1443" t="inlineStr">
-        <is>
-          <t>5541991140425</t>
-        </is>
+      <c r="I1443" t="n">
+        <v>5541991140425</v>
       </c>
       <c r="J1443" t="inlineStr"/>
       <c r="K1443" t="n">
@@ -70867,10 +70857,8 @@
         </is>
       </c>
       <c r="H1444" t="inlineStr"/>
-      <c r="I1444" t="inlineStr">
-        <is>
-          <t>5541992632977</t>
-        </is>
+      <c r="I1444" t="n">
+        <v>5541992632977</v>
       </c>
       <c r="J1444" t="inlineStr"/>
       <c r="K1444" t="n">
@@ -70919,10 +70907,8 @@
         </is>
       </c>
       <c r="H1445" t="inlineStr"/>
-      <c r="I1445" t="inlineStr">
-        <is>
-          <t>5541996522171</t>
-        </is>
+      <c r="I1445" t="n">
+        <v>5541996522171</v>
       </c>
       <c r="J1445" t="inlineStr"/>
       <c r="K1445" t="n">
@@ -70971,10 +70957,8 @@
         </is>
       </c>
       <c r="H1446" t="inlineStr"/>
-      <c r="I1446" t="inlineStr">
-        <is>
-          <t>554130575050</t>
-        </is>
+      <c r="I1446" t="n">
+        <v>554130575050</v>
       </c>
       <c r="J1446" t="inlineStr"/>
       <c r="K1446" t="n">
@@ -71167,10 +71151,8 @@
         </is>
       </c>
       <c r="H1450" t="inlineStr"/>
-      <c r="I1450" t="inlineStr">
-        <is>
-          <t>5541991765594</t>
-        </is>
+      <c r="I1450" t="n">
+        <v>5541991765594</v>
       </c>
       <c r="J1450" t="inlineStr"/>
       <c r="K1450" t="n">
@@ -71267,10 +71249,8 @@
         </is>
       </c>
       <c r="H1452" t="inlineStr"/>
-      <c r="I1452" t="inlineStr">
-        <is>
-          <t>5551999167650</t>
-        </is>
+      <c r="I1452" t="n">
+        <v>5551999167650</v>
       </c>
       <c r="J1452" t="inlineStr"/>
       <c r="K1452" t="n">
@@ -71463,16 +71443,1274 @@
         </is>
       </c>
       <c r="H1456" t="inlineStr"/>
-      <c r="I1456" t="inlineStr">
-        <is>
-          <t>5551991495565</t>
-        </is>
+      <c r="I1456" t="n">
+        <v>5551991495565</v>
       </c>
       <c r="J1456" t="inlineStr"/>
       <c r="K1456" t="n">
         <v>73</v>
       </c>
       <c r="L1456" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>ultraclinicaac.com.br</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>https://ultraclinicaac.com.br</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr"/>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>5568992201206</t>
+        </is>
+      </c>
+      <c r="J1457" t="inlineStr"/>
+      <c r="K1457" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1457" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>Advogado em Rio Branco e no Acre</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>http://www.luizreisadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr"/>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>5568999365825</t>
+        </is>
+      </c>
+      <c r="J1458" t="inlineStr"/>
+      <c r="K1458" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1458" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>Dr Michel Paes</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>https://michelpaes.adv.br</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr"/>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>5568981182940</t>
+        </is>
+      </c>
+      <c r="J1459" t="inlineStr"/>
+      <c r="K1459" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1459" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>Instituto Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>https://visitebrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr"/>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>5561996728177</t>
+        </is>
+      </c>
+      <c r="J1460" t="inlineStr"/>
+      <c r="K1460" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1460" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Rio Branco, Acre, AC</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>https://encontraac.com.br</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr"/>
+      <c r="I1461" t="inlineStr"/>
+      <c r="J1461" t="inlineStr"/>
+      <c r="K1461" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1461" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>https://dralcimarcos.com.br</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr"/>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>5596991112889</t>
+        </is>
+      </c>
+      <c r="J1462" t="inlineStr"/>
+      <c r="K1462" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1462" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>Dra Amanda Corrêa</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>https://draamandacorrea.com.br</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr"/>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>5596981064291</t>
+        </is>
+      </c>
+      <c r="J1463" t="inlineStr"/>
+      <c r="K1463" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1463" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>Advogado em Macapá</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>https://gusteman.adv.br</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr"/>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>5545999102383</t>
+        </is>
+      </c>
+      <c r="J1464" t="inlineStr"/>
+      <c r="K1464" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1464" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>Advogado Em Macapá</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>https://advogadoandre.com</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr"/>
+      <c r="I1465" t="inlineStr"/>
+      <c r="J1465" t="inlineStr"/>
+      <c r="K1465" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1465" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>BLOCO DO CURSO DE EDUCAÇÃO FISICA em Macapá</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>https://www.escolasbrasil.com</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr"/>
+      <c r="I1466" t="inlineStr"/>
+      <c r="J1466" t="inlineStr"/>
+      <c r="K1466" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1466" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>Manaus Medical Center</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>https://manausmedicalcenter.cucco.com.br</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr"/>
+      <c r="I1467" t="inlineStr"/>
+      <c r="J1467" t="inlineStr"/>
+      <c r="K1467" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1467" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>D'Clinic</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>https://dclinic.com.br</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr"/>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>5592981240286</t>
+        </is>
+      </c>
+      <c r="J1468" t="inlineStr"/>
+      <c r="K1468" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1468" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>Dentista em Manaus</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>https://barucodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr"/>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>5592991817053</t>
+        </is>
+      </c>
+      <c r="J1469" t="inlineStr"/>
+      <c r="K1469" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1469" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>Dentista em Manaus</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>https://carolinamenahem.com.br</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr"/>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>5592981723355</t>
+        </is>
+      </c>
+      <c r="J1470" t="inlineStr"/>
+      <c r="K1470" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1470" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>Aleson Macedo</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>https://www.alesonpsicologo.com.br</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr"/>
+      <c r="I1471" t="inlineStr"/>
+      <c r="J1471" t="inlineStr"/>
+      <c r="K1471" t="n">
+        <v>47</v>
+      </c>
+      <c r="L1471" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>Oliveira Advocacia e Consultoria Jurídica</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>https://oliveiraconsultoriaadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr"/>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>5592982491054</t>
+        </is>
+      </c>
+      <c r="J1472" t="inlineStr"/>
+      <c r="K1472" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1472" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>Advogados em Manaus</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>https://advogadosmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr"/>
+      <c r="I1473" t="inlineStr"/>
+      <c r="J1473" t="inlineStr"/>
+      <c r="K1473" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1473" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>https://guiamanausam.com.br</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr"/>
+      <c r="I1474" t="inlineStr"/>
+      <c r="J1474" t="inlineStr"/>
+      <c r="K1474" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1474" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>Dra. Gerlen Mascarenhas</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>https://www.gerlenmascarenhas.com.br</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr"/>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>5592992555753</t>
+        </is>
+      </c>
+      <c r="J1475" t="inlineStr"/>
+      <c r="K1475" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1475" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>Clínica Médica Belém, Exames, Consultas Médicos</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>https://clinicaredemaissaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr"/>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>5591985207358</t>
+        </is>
+      </c>
+      <c r="J1476" t="inlineStr"/>
+      <c r="K1476" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1476" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>Clínica — Aqui pela sua saúde, todos os dias</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>https://redemeumedico.com.br</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr"/>
+      <c r="I1477" t="inlineStr"/>
+      <c r="J1477" t="inlineStr"/>
+      <c r="K1477" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1477" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>COMVIDA</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>https://comvidamp.com.br</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr"/>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>5591984567400</t>
+        </is>
+      </c>
+      <c r="J1478" t="inlineStr"/>
+      <c r="K1478" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1478" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>Consulta Fácil - PA</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>https://consultafacilpa.com.br</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr"/>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>5591980108716</t>
+        </is>
+      </c>
+      <c r="J1479" t="inlineStr"/>
+      <c r="K1479" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1479" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>ACCEB — Centro Médico</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>https://acceb.com.br</t>
+        </is>
+      </c>
+      <c r="H1480" t="inlineStr"/>
+      <c r="I1480" t="inlineStr"/>
+      <c r="J1480" t="inlineStr"/>
+      <c r="K1480" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1480" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>Médicos, Clínicas e Consultórios Medicos em Belém</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>https://www.encontrabelem.com.br</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr"/>
+      <c r="I1481" t="inlineStr"/>
+      <c r="J1481" t="inlineStr"/>
+      <c r="K1481" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1481" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1481"/>
+  <dimension ref="A1:L1507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71493,10 +71493,8 @@
         </is>
       </c>
       <c r="H1457" t="inlineStr"/>
-      <c r="I1457" t="inlineStr">
-        <is>
-          <t>5568992201206</t>
-        </is>
+      <c r="I1457" t="n">
+        <v>5568992201206</v>
       </c>
       <c r="J1457" t="inlineStr"/>
       <c r="K1457" t="n">
@@ -71545,10 +71543,8 @@
         </is>
       </c>
       <c r="H1458" t="inlineStr"/>
-      <c r="I1458" t="inlineStr">
-        <is>
-          <t>5568999365825</t>
-        </is>
+      <c r="I1458" t="n">
+        <v>5568999365825</v>
       </c>
       <c r="J1458" t="inlineStr"/>
       <c r="K1458" t="n">
@@ -71597,10 +71593,8 @@
         </is>
       </c>
       <c r="H1459" t="inlineStr"/>
-      <c r="I1459" t="inlineStr">
-        <is>
-          <t>5568981182940</t>
-        </is>
+      <c r="I1459" t="n">
+        <v>5568981182940</v>
       </c>
       <c r="J1459" t="inlineStr"/>
       <c r="K1459" t="n">
@@ -71649,10 +71643,8 @@
         </is>
       </c>
       <c r="H1460" t="inlineStr"/>
-      <c r="I1460" t="inlineStr">
-        <is>
-          <t>5561996728177</t>
-        </is>
+      <c r="I1460" t="n">
+        <v>5561996728177</v>
       </c>
       <c r="J1460" t="inlineStr"/>
       <c r="K1460" t="n">
@@ -71749,10 +71741,8 @@
         </is>
       </c>
       <c r="H1462" t="inlineStr"/>
-      <c r="I1462" t="inlineStr">
-        <is>
-          <t>5596991112889</t>
-        </is>
+      <c r="I1462" t="n">
+        <v>5596991112889</v>
       </c>
       <c r="J1462" t="inlineStr"/>
       <c r="K1462" t="n">
@@ -71801,10 +71791,8 @@
         </is>
       </c>
       <c r="H1463" t="inlineStr"/>
-      <c r="I1463" t="inlineStr">
-        <is>
-          <t>5596981064291</t>
-        </is>
+      <c r="I1463" t="n">
+        <v>5596981064291</v>
       </c>
       <c r="J1463" t="inlineStr"/>
       <c r="K1463" t="n">
@@ -71853,10 +71841,8 @@
         </is>
       </c>
       <c r="H1464" t="inlineStr"/>
-      <c r="I1464" t="inlineStr">
-        <is>
-          <t>5545999102383</t>
-        </is>
+      <c r="I1464" t="n">
+        <v>5545999102383</v>
       </c>
       <c r="J1464" t="inlineStr"/>
       <c r="K1464" t="n">
@@ -72049,10 +72035,8 @@
         </is>
       </c>
       <c r="H1468" t="inlineStr"/>
-      <c r="I1468" t="inlineStr">
-        <is>
-          <t>5592981240286</t>
-        </is>
+      <c r="I1468" t="n">
+        <v>5592981240286</v>
       </c>
       <c r="J1468" t="inlineStr"/>
       <c r="K1468" t="n">
@@ -72101,10 +72085,8 @@
         </is>
       </c>
       <c r="H1469" t="inlineStr"/>
-      <c r="I1469" t="inlineStr">
-        <is>
-          <t>5592991817053</t>
-        </is>
+      <c r="I1469" t="n">
+        <v>5592991817053</v>
       </c>
       <c r="J1469" t="inlineStr"/>
       <c r="K1469" t="n">
@@ -72153,10 +72135,8 @@
         </is>
       </c>
       <c r="H1470" t="inlineStr"/>
-      <c r="I1470" t="inlineStr">
-        <is>
-          <t>5592981723355</t>
-        </is>
+      <c r="I1470" t="n">
+        <v>5592981723355</v>
       </c>
       <c r="J1470" t="inlineStr"/>
       <c r="K1470" t="n">
@@ -72253,10 +72233,8 @@
         </is>
       </c>
       <c r="H1472" t="inlineStr"/>
-      <c r="I1472" t="inlineStr">
-        <is>
-          <t>5592982491054</t>
-        </is>
+      <c r="I1472" t="n">
+        <v>5592982491054</v>
       </c>
       <c r="J1472" t="inlineStr"/>
       <c r="K1472" t="n">
@@ -72401,10 +72379,8 @@
         </is>
       </c>
       <c r="H1475" t="inlineStr"/>
-      <c r="I1475" t="inlineStr">
-        <is>
-          <t>5592992555753</t>
-        </is>
+      <c r="I1475" t="n">
+        <v>5592992555753</v>
       </c>
       <c r="J1475" t="inlineStr"/>
       <c r="K1475" t="n">
@@ -72453,10 +72429,8 @@
         </is>
       </c>
       <c r="H1476" t="inlineStr"/>
-      <c r="I1476" t="inlineStr">
-        <is>
-          <t>5591985207358</t>
-        </is>
+      <c r="I1476" t="n">
+        <v>5591985207358</v>
       </c>
       <c r="J1476" t="inlineStr"/>
       <c r="K1476" t="n">
@@ -72553,10 +72527,8 @@
         </is>
       </c>
       <c r="H1478" t="inlineStr"/>
-      <c r="I1478" t="inlineStr">
-        <is>
-          <t>5591984567400</t>
-        </is>
+      <c r="I1478" t="n">
+        <v>5591984567400</v>
       </c>
       <c r="J1478" t="inlineStr"/>
       <c r="K1478" t="n">
@@ -72605,10 +72577,8 @@
         </is>
       </c>
       <c r="H1479" t="inlineStr"/>
-      <c r="I1479" t="inlineStr">
-        <is>
-          <t>5591980108716</t>
-        </is>
+      <c r="I1479" t="n">
+        <v>5591980108716</v>
       </c>
       <c r="J1479" t="inlineStr"/>
       <c r="K1479" t="n">
@@ -72716,6 +72686,1306 @@
         </is>
       </c>
     </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>Dr Aldo Agra de Albuquerque Neto</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>https://www.draldoagrapneumo.com.br</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr"/>
+      <c r="I1482" t="inlineStr"/>
+      <c r="J1482" t="inlineStr"/>
+      <c r="K1482" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1482" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>Dra. Elaine Sobral Leite</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>https://draelainesleite.com.br</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr"/>
+      <c r="I1483" t="inlineStr"/>
+      <c r="J1483" t="inlineStr"/>
+      <c r="K1483" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1483" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>Psicólogo Thiago Acioly</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>https://www.psithiagoacioly.com</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr"/>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>5582993166034</t>
+        </is>
+      </c>
+      <c r="J1484" t="inlineStr"/>
+      <c r="K1484" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1484" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>Solange Goez Terapeuta</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>https://solangegoez.com.br</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr"/>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>5511918518797</t>
+        </is>
+      </c>
+      <c r="J1485" t="inlineStr"/>
+      <c r="K1485" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1485" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>19058</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>https://publicacoes.estadao.com.br</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr"/>
+      <c r="I1486" t="inlineStr"/>
+      <c r="J1486" t="inlineStr"/>
+      <c r="K1486" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1486" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>Centro Universitário CESMAC</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>https://cesmac.edu.br</t>
+        </is>
+      </c>
+      <c r="H1487" t="inlineStr"/>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>558232155000</t>
+        </is>
+      </c>
+      <c r="J1487" t="inlineStr"/>
+      <c r="K1487" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1487" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>Rafael Filgueira</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>https://www.rafaelfilgueira.com.br</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr"/>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>558296165487</t>
+        </is>
+      </c>
+      <c r="J1488" t="inlineStr"/>
+      <c r="K1488" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1488" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica CLIOPAF</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>https://cliopaf.com.br</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr"/>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>5571987000818</t>
+        </is>
+      </c>
+      <c r="J1489" t="inlineStr"/>
+      <c r="K1489" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1489" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>https://www.nascimentomuniz.adv.br</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr"/>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>5571982171292</t>
+        </is>
+      </c>
+      <c r="J1490" t="inlineStr"/>
+      <c r="K1490" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1490" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>Infinito Movimento: Educação Física, Saúde e Cência em ação ...</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>https://infinitomovimento.com</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr"/>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>5571981952060</t>
+        </is>
+      </c>
+      <c r="J1491" t="inlineStr"/>
+      <c r="K1491" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1491" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>https://www.uniftc.edu.br</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr"/>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>5508000566666</t>
+        </is>
+      </c>
+      <c r="J1492" t="inlineStr"/>
+      <c r="K1492" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1492" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>Médicos em Fortaleza - CE</t>
+        </is>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>https://www.partic.com.br</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr"/>
+      <c r="I1493" t="inlineStr"/>
+      <c r="J1493" t="inlineStr"/>
+      <c r="K1493" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1493" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>https://www.dranatalialucena.com</t>
+        </is>
+      </c>
+      <c r="H1494" t="inlineStr"/>
+      <c r="I1494" t="inlineStr"/>
+      <c r="J1494" t="inlineStr"/>
+      <c r="K1494" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1494" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>Greater Seattle Business Investment Report 2026</t>
+        </is>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>https://greater-seattle.com</t>
+        </is>
+      </c>
+      <c r="H1495" t="inlineStr"/>
+      <c r="I1495" t="inlineStr"/>
+      <c r="J1495" t="inlineStr"/>
+      <c r="K1495" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1495" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>Seattle and San Francisco: Big tech, political backlash and the ...</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>https://www.geekwire.com</t>
+        </is>
+      </c>
+      <c r="H1496" t="inlineStr"/>
+      <c r="I1496" t="inlineStr"/>
+      <c r="J1496" t="inlineStr"/>
+      <c r="K1496" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1496" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>City of Seattle 2025-2026 AI Plan</t>
+        </is>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>https://www.seattle.gov</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr"/>
+      <c r="I1497" t="inlineStr"/>
+      <c r="J1497" t="inlineStr"/>
+      <c r="K1497" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1497" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>Seattle Tech Industry Statistics</t>
+        </is>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>https://worldmetrics.org</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr"/>
+      <c r="I1498" t="inlineStr"/>
+      <c r="J1498" t="inlineStr"/>
+      <c r="K1498" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1498" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>Seattle attracts tech startups amid AI boom</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>https://www.seattletimes.com</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr"/>
+      <c r="I1499" t="inlineStr"/>
+      <c r="J1499" t="inlineStr"/>
+      <c r="K1499" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1499" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>Seattle’s Artificial Intelligence (AI) Vision: Centering Human...</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>https://wilson.seattle.gov</t>
+        </is>
+      </c>
+      <c r="H1500" t="inlineStr"/>
+      <c r="I1500" t="inlineStr"/>
+      <c r="J1500" t="inlineStr"/>
+      <c r="K1500" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1500" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>Psicóloga Gardênia Rocha</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>https://www.gardeniarocha.com.br</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr"/>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>558591829372</t>
+        </is>
+      </c>
+      <c r="J1501" t="inlineStr"/>
+      <c r="K1501" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1501" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>Gabriel Rodrigues</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>https://psicologogabriel.com</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr"/>
+      <c r="I1502" t="inlineStr"/>
+      <c r="J1502" t="inlineStr"/>
+      <c r="K1502" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1502" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>Vitor Sales</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>https://www.vitorsalespsicologia.com</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr"/>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>5585997118888</t>
+        </is>
+      </c>
+      <c r="J1503" t="inlineStr"/>
+      <c r="K1503" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1503" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>https://unifor.br</t>
+        </is>
+      </c>
+      <c r="H1504" t="inlineStr"/>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>558592466625</t>
+        </is>
+      </c>
+      <c r="J1504" t="inlineStr"/>
+      <c r="K1504" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1504" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>Educação Física (ABI)- Licenciatura</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>https://prograd.ufc.br</t>
+        </is>
+      </c>
+      <c r="H1505" t="inlineStr"/>
+      <c r="I1505" t="inlineStr"/>
+      <c r="J1505" t="inlineStr"/>
+      <c r="K1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1505" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>Porão Academias</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>https://poraoacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr"/>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>5585991985849</t>
+        </is>
+      </c>
+      <c r="J1506" t="inlineStr"/>
+      <c r="K1506" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1506" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>Greenlife Academias</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>https://greenlifeacademias.com.br</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr"/>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>5585989023059</t>
+        </is>
+      </c>
+      <c r="J1507" t="inlineStr"/>
+      <c r="K1507" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1507" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1507"/>
+  <dimension ref="A1:L1520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72819,10 +72819,8 @@
         </is>
       </c>
       <c r="H1484" t="inlineStr"/>
-      <c r="I1484" t="inlineStr">
-        <is>
-          <t>5582993166034</t>
-        </is>
+      <c r="I1484" t="n">
+        <v>5582993166034</v>
       </c>
       <c r="J1484" t="inlineStr"/>
       <c r="K1484" t="n">
@@ -72871,10 +72869,8 @@
         </is>
       </c>
       <c r="H1485" t="inlineStr"/>
-      <c r="I1485" t="inlineStr">
-        <is>
-          <t>5511918518797</t>
-        </is>
+      <c r="I1485" t="n">
+        <v>5511918518797</v>
       </c>
       <c r="J1485" t="inlineStr"/>
       <c r="K1485" t="n">
@@ -72971,10 +72967,8 @@
         </is>
       </c>
       <c r="H1487" t="inlineStr"/>
-      <c r="I1487" t="inlineStr">
-        <is>
-          <t>558232155000</t>
-        </is>
+      <c r="I1487" t="n">
+        <v>558232155000</v>
       </c>
       <c r="J1487" t="inlineStr"/>
       <c r="K1487" t="n">
@@ -73023,10 +73017,8 @@
         </is>
       </c>
       <c r="H1488" t="inlineStr"/>
-      <c r="I1488" t="inlineStr">
-        <is>
-          <t>558296165487</t>
-        </is>
+      <c r="I1488" t="n">
+        <v>558296165487</v>
       </c>
       <c r="J1488" t="inlineStr"/>
       <c r="K1488" t="n">
@@ -73075,10 +73067,8 @@
         </is>
       </c>
       <c r="H1489" t="inlineStr"/>
-      <c r="I1489" t="inlineStr">
-        <is>
-          <t>5571987000818</t>
-        </is>
+      <c r="I1489" t="n">
+        <v>5571987000818</v>
       </c>
       <c r="J1489" t="inlineStr"/>
       <c r="K1489" t="n">
@@ -73127,10 +73117,8 @@
         </is>
       </c>
       <c r="H1490" t="inlineStr"/>
-      <c r="I1490" t="inlineStr">
-        <is>
-          <t>5571982171292</t>
-        </is>
+      <c r="I1490" t="n">
+        <v>5571982171292</v>
       </c>
       <c r="J1490" t="inlineStr"/>
       <c r="K1490" t="n">
@@ -73179,10 +73167,8 @@
         </is>
       </c>
       <c r="H1491" t="inlineStr"/>
-      <c r="I1491" t="inlineStr">
-        <is>
-          <t>5571981952060</t>
-        </is>
+      <c r="I1491" t="n">
+        <v>5571981952060</v>
       </c>
       <c r="J1491" t="inlineStr"/>
       <c r="K1491" t="n">
@@ -73231,10 +73217,8 @@
         </is>
       </c>
       <c r="H1492" t="inlineStr"/>
-      <c r="I1492" t="inlineStr">
-        <is>
-          <t>5508000566666</t>
-        </is>
+      <c r="I1492" t="n">
+        <v>5508000566666</v>
       </c>
       <c r="J1492" t="inlineStr"/>
       <c r="K1492" t="n">
@@ -73667,10 +73651,8 @@
         </is>
       </c>
       <c r="H1501" t="inlineStr"/>
-      <c r="I1501" t="inlineStr">
-        <is>
-          <t>558591829372</t>
-        </is>
+      <c r="I1501" t="n">
+        <v>558591829372</v>
       </c>
       <c r="J1501" t="inlineStr"/>
       <c r="K1501" t="n">
@@ -73767,10 +73749,8 @@
         </is>
       </c>
       <c r="H1503" t="inlineStr"/>
-      <c r="I1503" t="inlineStr">
-        <is>
-          <t>5585997118888</t>
-        </is>
+      <c r="I1503" t="n">
+        <v>5585997118888</v>
       </c>
       <c r="J1503" t="inlineStr"/>
       <c r="K1503" t="n">
@@ -73819,10 +73799,8 @@
         </is>
       </c>
       <c r="H1504" t="inlineStr"/>
-      <c r="I1504" t="inlineStr">
-        <is>
-          <t>558592466625</t>
-        </is>
+      <c r="I1504" t="n">
+        <v>558592466625</v>
       </c>
       <c r="J1504" t="inlineStr"/>
       <c r="K1504" t="n">
@@ -73919,10 +73897,8 @@
         </is>
       </c>
       <c r="H1506" t="inlineStr"/>
-      <c r="I1506" t="inlineStr">
-        <is>
-          <t>5585991985849</t>
-        </is>
+      <c r="I1506" t="n">
+        <v>5585991985849</v>
       </c>
       <c r="J1506" t="inlineStr"/>
       <c r="K1506" t="n">
@@ -73971,16 +73947,674 @@
         </is>
       </c>
       <c r="H1507" t="inlineStr"/>
-      <c r="I1507" t="inlineStr">
-        <is>
-          <t>5585989023059</t>
-        </is>
+      <c r="I1507" t="n">
+        <v>5585989023059</v>
       </c>
       <c r="J1507" t="inlineStr"/>
       <c r="K1507" t="n">
         <v>70</v>
       </c>
       <c r="L1507" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>PSICANALISTA BRASÍLIA BRASIL| MIRIAM KRUEGER</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>https://www.miriamkruegerpsi.com</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr"/>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>5561991261600</t>
+        </is>
+      </c>
+      <c r="J1508" t="inlineStr"/>
+      <c r="K1508" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1508" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>Psicólogo em Brasília e online</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>https://brunodonascimento.com.br</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr"/>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>5561999552066</t>
+        </is>
+      </c>
+      <c r="J1509" t="inlineStr"/>
+      <c r="K1509" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1509" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>Arandu Espaço Terapêutico</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>https://aranduterapeutico.com.br</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr"/>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>5561993190653</t>
+        </is>
+      </c>
+      <c r="J1510" t="inlineStr"/>
+      <c r="K1510" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1510" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>Carla Miranda Terapeuta</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>https://www.carlamirandaterapeuta.com</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr"/>
+      <c r="I1511" t="inlineStr"/>
+      <c r="J1511" t="inlineStr"/>
+      <c r="K1511" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1511" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>Francisco Camargo Advogados</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>https://franciscocamargoadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr"/>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>5561984835444</t>
+        </is>
+      </c>
+      <c r="J1512" t="inlineStr"/>
+      <c r="K1512" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1512" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>Advogado em Brasília/DF</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>https://marquesescritorioadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr"/>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>5561995613055</t>
+        </is>
+      </c>
+      <c r="J1513" t="inlineStr"/>
+      <c r="K1513" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1513" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>Alberto Araújo Advocacia</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>https://albertoaraujo.adv.br</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr"/>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>5561998688749</t>
+        </is>
+      </c>
+      <c r="J1514" t="inlineStr"/>
+      <c r="K1514" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1514" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>Dra. Thays Tavares</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>https://fisioterapiathaystavares.com.br</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr"/>
+      <c r="I1515" t="inlineStr"/>
+      <c r="J1515" t="inlineStr"/>
+      <c r="K1515" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1515" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>https://premierodontologiago.com.br</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr"/>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>5562996678906</t>
+        </is>
+      </c>
+      <c r="J1516" t="inlineStr"/>
+      <c r="K1516" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1516" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>https://drmarceloeuripedes.com.br</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr"/>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>5562982699726</t>
+        </is>
+      </c>
+      <c r="J1517" t="inlineStr"/>
+      <c r="K1517" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1517" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>Dr. Ilamar Fernandes: Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>https://ilamaradvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr"/>
+      <c r="I1518" t="inlineStr"/>
+      <c r="J1518" t="inlineStr"/>
+      <c r="K1518" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1518" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>Hudson Oliveira</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>https://hudsonoliveira.adv.br</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr"/>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>5562996028530</t>
+        </is>
+      </c>
+      <c r="J1519" t="inlineStr"/>
+      <c r="K1519" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1519" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Cuiabá (MT) — Agendar consulta</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>https://endoclinicabsb.com.br</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr"/>
+      <c r="I1520" t="inlineStr"/>
+      <c r="J1520" t="inlineStr"/>
+      <c r="K1520" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1520" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1520"/>
+  <dimension ref="A1:L1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73997,10 +73997,8 @@
         </is>
       </c>
       <c r="H1508" t="inlineStr"/>
-      <c r="I1508" t="inlineStr">
-        <is>
-          <t>5561991261600</t>
-        </is>
+      <c r="I1508" t="n">
+        <v>5561991261600</v>
       </c>
       <c r="J1508" t="inlineStr"/>
       <c r="K1508" t="n">
@@ -74049,10 +74047,8 @@
         </is>
       </c>
       <c r="H1509" t="inlineStr"/>
-      <c r="I1509" t="inlineStr">
-        <is>
-          <t>5561999552066</t>
-        </is>
+      <c r="I1509" t="n">
+        <v>5561999552066</v>
       </c>
       <c r="J1509" t="inlineStr"/>
       <c r="K1509" t="n">
@@ -74101,10 +74097,8 @@
         </is>
       </c>
       <c r="H1510" t="inlineStr"/>
-      <c r="I1510" t="inlineStr">
-        <is>
-          <t>5561993190653</t>
-        </is>
+      <c r="I1510" t="n">
+        <v>5561993190653</v>
       </c>
       <c r="J1510" t="inlineStr"/>
       <c r="K1510" t="n">
@@ -74201,10 +74195,8 @@
         </is>
       </c>
       <c r="H1512" t="inlineStr"/>
-      <c r="I1512" t="inlineStr">
-        <is>
-          <t>5561984835444</t>
-        </is>
+      <c r="I1512" t="n">
+        <v>5561984835444</v>
       </c>
       <c r="J1512" t="inlineStr"/>
       <c r="K1512" t="n">
@@ -74253,10 +74245,8 @@
         </is>
       </c>
       <c r="H1513" t="inlineStr"/>
-      <c r="I1513" t="inlineStr">
-        <is>
-          <t>5561995613055</t>
-        </is>
+      <c r="I1513" t="n">
+        <v>5561995613055</v>
       </c>
       <c r="J1513" t="inlineStr"/>
       <c r="K1513" t="n">
@@ -74305,10 +74295,8 @@
         </is>
       </c>
       <c r="H1514" t="inlineStr"/>
-      <c r="I1514" t="inlineStr">
-        <is>
-          <t>5561998688749</t>
-        </is>
+      <c r="I1514" t="n">
+        <v>5561998688749</v>
       </c>
       <c r="J1514" t="inlineStr"/>
       <c r="K1514" t="n">
@@ -74405,10 +74393,8 @@
         </is>
       </c>
       <c r="H1516" t="inlineStr"/>
-      <c r="I1516" t="inlineStr">
-        <is>
-          <t>5562996678906</t>
-        </is>
+      <c r="I1516" t="n">
+        <v>5562996678906</v>
       </c>
       <c r="J1516" t="inlineStr"/>
       <c r="K1516" t="n">
@@ -74457,10 +74443,8 @@
         </is>
       </c>
       <c r="H1517" t="inlineStr"/>
-      <c r="I1517" t="inlineStr">
-        <is>
-          <t>5562982699726</t>
-        </is>
+      <c r="I1517" t="n">
+        <v>5562982699726</v>
       </c>
       <c r="J1517" t="inlineStr"/>
       <c r="K1517" t="n">
@@ -74557,10 +74541,8 @@
         </is>
       </c>
       <c r="H1519" t="inlineStr"/>
-      <c r="I1519" t="inlineStr">
-        <is>
-          <t>5562996028530</t>
-        </is>
+      <c r="I1519" t="n">
+        <v>5562996028530</v>
       </c>
       <c r="J1519" t="inlineStr"/>
       <c r="K1519" t="n">
@@ -74620,6 +74602,642 @@
         </is>
       </c>
     </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>Ortopedista e Cirurgião de Joelho Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>https://www.drfranciscocarvalho.com</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr"/>
+      <c r="I1521" t="inlineStr"/>
+      <c r="J1521" t="inlineStr"/>
+      <c r="K1521" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1521" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>Roberlan Matos, Psicólogo Clínico e Neuropsicólogo em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>https://roberlanmatospsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr"/>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>5527999299195</t>
+        </is>
+      </c>
+      <c r="J1522" t="inlineStr"/>
+      <c r="K1522" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1522" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>Advogado em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>https://oliveirajorge.com.br</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr"/>
+      <c r="I1523" t="inlineStr"/>
+      <c r="J1523" t="inlineStr"/>
+      <c r="K1523" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1523" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>Clínica Penchel</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>https://clinicapenchel.com.br</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr"/>
+      <c r="I1524" t="inlineStr"/>
+      <c r="J1524" t="inlineStr"/>
+      <c r="K1524" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1524" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>Profissionais de Saúde altamente recomendados em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>https://www.helpsaude.com</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr"/>
+      <c r="I1525" t="inlineStr"/>
+      <c r="J1525" t="inlineStr"/>
+      <c r="K1525" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1525" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>Andrea Moura</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>https://www.andreamourapsicologaneurociencia.com</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr"/>
+      <c r="I1526" t="inlineStr"/>
+      <c r="J1526" t="inlineStr"/>
+      <c r="K1526" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1526" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>Silveira e Silva Advogados Sociedade de Advogados</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>https://silveiraesilvaadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr"/>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>5531998136642</t>
+        </is>
+      </c>
+      <c r="J1527" t="inlineStr"/>
+      <c r="K1527" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1527" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>FitBridge</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>https://www.fitbridge.com.br</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr"/>
+      <c r="I1528" t="inlineStr"/>
+      <c r="J1528" t="inlineStr"/>
+      <c r="K1528" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1528" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>Fit One Academia</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>https://www.fitonebh.com.br</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr"/>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>5531999186411</t>
+        </is>
+      </c>
+      <c r="J1529" t="inlineStr"/>
+      <c r="K1529" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1529" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>FAMINAS-BH</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>https://faminasbh.edu.br</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr"/>
+      <c r="I1530" t="inlineStr"/>
+      <c r="J1530" t="inlineStr"/>
+      <c r="K1530" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1530" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>Dr. Clayton Quintão</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>https://www.drclaytonquintao.com</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr"/>
+      <c r="I1531" t="inlineStr"/>
+      <c r="J1531" t="inlineStr"/>
+      <c r="K1531" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1531" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>Clínica Rio</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>http://www.clinicarioiraja.com.br</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr"/>
+      <c r="I1532" t="inlineStr"/>
+      <c r="J1532" t="inlineStr"/>
+      <c r="K1532" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1532" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>Terapeutas RJ</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>https://www.terapiasonline.com.br</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr"/>
+      <c r="I1533" t="inlineStr"/>
+      <c r="J1533" t="inlineStr"/>
+      <c r="K1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1533" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1533"/>
+  <dimension ref="A1:L1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74687,10 +74687,8 @@
         </is>
       </c>
       <c r="H1522" t="inlineStr"/>
-      <c r="I1522" t="inlineStr">
-        <is>
-          <t>5527999299195</t>
-        </is>
+      <c r="I1522" t="n">
+        <v>5527999299195</v>
       </c>
       <c r="J1522" t="inlineStr"/>
       <c r="K1522" t="n">
@@ -74931,10 +74929,8 @@
         </is>
       </c>
       <c r="H1527" t="inlineStr"/>
-      <c r="I1527" t="inlineStr">
-        <is>
-          <t>5531998136642</t>
-        </is>
+      <c r="I1527" t="n">
+        <v>5531998136642</v>
       </c>
       <c r="J1527" t="inlineStr"/>
       <c r="K1527" t="n">
@@ -75031,10 +75027,8 @@
         </is>
       </c>
       <c r="H1529" t="inlineStr"/>
-      <c r="I1529" t="inlineStr">
-        <is>
-          <t>5531999186411</t>
-        </is>
+      <c r="I1529" t="n">
+        <v>5531999186411</v>
       </c>
       <c r="J1529" t="inlineStr"/>
       <c r="K1529" t="n">
@@ -75238,6 +75232,458 @@
         </is>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>Kosop Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>https://www.kosopclinicamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr"/>
+      <c r="I1534" t="inlineStr"/>
+      <c r="J1534" t="inlineStr"/>
+      <c r="K1534" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1534" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>Clínica Gandhi</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>https://clinicagandhi.com.br</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr"/>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>5541991018429</t>
+        </is>
+      </c>
+      <c r="J1535" t="inlineStr"/>
+      <c r="K1535" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1535" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>Psicóloga Francine Porfirio</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>https://francineporfirio.com</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr"/>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>5541991662300</t>
+        </is>
+      </c>
+      <c r="J1536" t="inlineStr"/>
+      <c r="K1536" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1536" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>Psicóloga Gloria Nogueira</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>https://www.psicologaglorianogueira.com.br</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr"/>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>5541987040376</t>
+        </is>
+      </c>
+      <c r="J1537" t="inlineStr"/>
+      <c r="K1537" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1537" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>Thai Brasil</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>https://thaibrasil.com</t>
+        </is>
+      </c>
+      <c r="H1538" t="inlineStr"/>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>5541992876002</t>
+        </is>
+      </c>
+      <c r="J1538" t="inlineStr"/>
+      <c r="K1538" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1538" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>New Clinic Barrra</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>https://newclinicbarra.com.br</t>
+        </is>
+      </c>
+      <c r="H1539" t="inlineStr"/>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>5551992583921</t>
+        </is>
+      </c>
+      <c r="J1539" t="inlineStr"/>
+      <c r="K1539" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1539" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>Médico em Porto Alegre - RS</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>https://doutorlocal.com.br</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr"/>
+      <c r="I1540" t="inlineStr"/>
+      <c r="J1540" t="inlineStr"/>
+      <c r="K1540" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1540" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>Terapeutas em Porto Alegre — Perfis Verificados</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>https://centraldoser.com.br</t>
+        </is>
+      </c>
+      <c r="H1541" t="inlineStr"/>
+      <c r="I1541" t="inlineStr"/>
+      <c r="J1541" t="inlineStr"/>
+      <c r="K1541" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1541" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>Andréia Teixeira Advogada</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>https://www.andreiateixeira.adv.br</t>
+        </is>
+      </c>
+      <c r="H1542" t="inlineStr"/>
+      <c r="I1542" t="inlineStr"/>
+      <c r="J1542" t="inlineStr"/>
+      <c r="K1542" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1542" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1542"/>
+  <dimension ref="A1:L1562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75317,10 +75317,8 @@
         </is>
       </c>
       <c r="H1535" t="inlineStr"/>
-      <c r="I1535" t="inlineStr">
-        <is>
-          <t>5541991018429</t>
-        </is>
+      <c r="I1535" t="n">
+        <v>5541991018429</v>
       </c>
       <c r="J1535" t="inlineStr"/>
       <c r="K1535" t="n">
@@ -75369,10 +75367,8 @@
         </is>
       </c>
       <c r="H1536" t="inlineStr"/>
-      <c r="I1536" t="inlineStr">
-        <is>
-          <t>5541991662300</t>
-        </is>
+      <c r="I1536" t="n">
+        <v>5541991662300</v>
       </c>
       <c r="J1536" t="inlineStr"/>
       <c r="K1536" t="n">
@@ -75421,10 +75417,8 @@
         </is>
       </c>
       <c r="H1537" t="inlineStr"/>
-      <c r="I1537" t="inlineStr">
-        <is>
-          <t>5541987040376</t>
-        </is>
+      <c r="I1537" t="n">
+        <v>5541987040376</v>
       </c>
       <c r="J1537" t="inlineStr"/>
       <c r="K1537" t="n">
@@ -75473,10 +75467,8 @@
         </is>
       </c>
       <c r="H1538" t="inlineStr"/>
-      <c r="I1538" t="inlineStr">
-        <is>
-          <t>5541992876002</t>
-        </is>
+      <c r="I1538" t="n">
+        <v>5541992876002</v>
       </c>
       <c r="J1538" t="inlineStr"/>
       <c r="K1538" t="n">
@@ -75525,10 +75517,8 @@
         </is>
       </c>
       <c r="H1539" t="inlineStr"/>
-      <c r="I1539" t="inlineStr">
-        <is>
-          <t>5551992583921</t>
-        </is>
+      <c r="I1539" t="n">
+        <v>5551992583921</v>
       </c>
       <c r="J1539" t="inlineStr"/>
       <c r="K1539" t="n">
@@ -75684,6 +75674,1014 @@
         </is>
       </c>
     </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Rio Branco, AC</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>https://multilocal.com.br</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr"/>
+      <c r="I1543" t="inlineStr">
+        <is>
+          <t>558432187576</t>
+        </is>
+      </c>
+      <c r="J1543" t="inlineStr"/>
+      <c r="K1543" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1543" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>Instituto Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>https://www.diplomacy.edu</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr"/>
+      <c r="I1544" t="inlineStr"/>
+      <c r="J1544" t="inlineStr"/>
+      <c r="K1544" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1544" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>Hospitais em Macapá - AP</t>
+        </is>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>https://www.hospitais.com</t>
+        </is>
+      </c>
+      <c r="H1545" t="inlineStr"/>
+      <c r="I1545" t="inlineStr"/>
+      <c r="J1545" t="inlineStr"/>
+      <c r="K1545" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1545" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>Clínica Integrare</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>https://autismoperto.com.br</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr"/>
+      <c r="I1546" t="inlineStr"/>
+      <c r="J1546" t="inlineStr"/>
+      <c r="K1546" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1546" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>Advogados em MACAPA (AP)</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>https://escritorios.juriscorrespondente.com.br</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr"/>
+      <c r="I1547" t="inlineStr"/>
+      <c r="J1547" t="inlineStr"/>
+      <c r="K1547" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1547" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>https://acessosaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr"/>
+      <c r="I1548" t="inlineStr">
+        <is>
+          <t>5541991032078</t>
+        </is>
+      </c>
+      <c r="J1548" t="inlineStr"/>
+      <c r="K1548" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1548" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>CREF8</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>https://www.cref8.org.br</t>
+        </is>
+      </c>
+      <c r="H1549" t="inlineStr"/>
+      <c r="I1549" t="inlineStr"/>
+      <c r="J1549" t="inlineStr"/>
+      <c r="K1549" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1549" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>Bacharelado em Educação Física</t>
+        </is>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>https://feff.ufam.edu.br</t>
+        </is>
+      </c>
+      <c r="H1550" t="inlineStr"/>
+      <c r="I1550" t="inlineStr"/>
+      <c r="J1550" t="inlineStr"/>
+      <c r="K1550" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1550" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>Academia Athletica Z Fitness</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>https://athleticazfitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr"/>
+      <c r="I1551" t="inlineStr">
+        <is>
+          <t>5592994195086</t>
+        </is>
+      </c>
+      <c r="J1551" t="inlineStr"/>
+      <c r="K1551" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1551" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>Contato e localização</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>https://www.saudebelem.com</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr"/>
+      <c r="I1552" t="inlineStr"/>
+      <c r="J1552" t="inlineStr"/>
+      <c r="K1552" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1552" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>Amar Saúde</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>https://www.amarsaudeclinica.com</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr"/>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>5591981878047</t>
+        </is>
+      </c>
+      <c r="J1553" t="inlineStr"/>
+      <c r="K1553" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1553" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>Sorrise Odontologia</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>http://clinicasorrise.com.br</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr"/>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>5591985044237</t>
+        </is>
+      </c>
+      <c r="J1554" t="inlineStr"/>
+      <c r="K1554" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1554" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>Dra. Ingrid Sales</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>https://draingridsales.com.br</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr"/>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>5591982598910</t>
+        </is>
+      </c>
+      <c r="J1555" t="inlineStr"/>
+      <c r="K1555" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1555" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>Dentista em Belém</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>https://oralsaudemais.com</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr"/>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>5591984353838</t>
+        </is>
+      </c>
+      <c r="J1556" t="inlineStr"/>
+      <c r="K1556" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1556" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>Luan Sampaio, Psicólogo e Psicanalista, em Belém-PA e Online</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>https://www.psiluansampaio.com.br</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr"/>
+      <c r="I1557" t="inlineStr"/>
+      <c r="J1557" t="inlineStr"/>
+      <c r="K1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1557" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>Railane Mendes</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>https://railanemendes.com.br</t>
+        </is>
+      </c>
+      <c r="H1558" t="inlineStr"/>
+      <c r="I1558" t="inlineStr">
+        <is>
+          <t>5591986170522</t>
+        </is>
+      </c>
+      <c r="J1558" t="inlineStr"/>
+      <c r="K1558" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1558" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>Psicóloga Clínica Laura Amaral</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>https://www.lauraamaral.com.br</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr"/>
+      <c r="I1559" t="inlineStr">
+        <is>
+          <t>5591981785235</t>
+        </is>
+      </c>
+      <c r="J1559" t="inlineStr"/>
+      <c r="K1559" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1559" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>Terapeuta em Belém, PA</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>https://wanianepomucenoterapeuta.com.br</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr"/>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>5591986349528</t>
+        </is>
+      </c>
+      <c r="J1560" t="inlineStr"/>
+      <c r="K1560" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1560" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>Psicóloga Renata Couto</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>https://renatacoutopsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr"/>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>5591991040759</t>
+        </is>
+      </c>
+      <c r="J1561" t="inlineStr"/>
+      <c r="K1561" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1561" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>David Aguiar, Advogado, Belém, Pará</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>https://davidaguiar.adv.br</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr"/>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>5591983759584</t>
+        </is>
+      </c>
+      <c r="J1562" t="inlineStr"/>
+      <c r="K1562" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1562" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1562"/>
+  <dimension ref="A1:L1578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75711,10 +75711,8 @@
         </is>
       </c>
       <c r="H1543" t="inlineStr"/>
-      <c r="I1543" t="inlineStr">
-        <is>
-          <t>558432187576</t>
-        </is>
+      <c r="I1543" t="n">
+        <v>558432187576</v>
       </c>
       <c r="J1543" t="inlineStr"/>
       <c r="K1543" t="n">
@@ -75955,10 +75953,8 @@
         </is>
       </c>
       <c r="H1548" t="inlineStr"/>
-      <c r="I1548" t="inlineStr">
-        <is>
-          <t>5541991032078</t>
-        </is>
+      <c r="I1548" t="n">
+        <v>5541991032078</v>
       </c>
       <c r="J1548" t="inlineStr"/>
       <c r="K1548" t="n">
@@ -76103,10 +76099,8 @@
         </is>
       </c>
       <c r="H1551" t="inlineStr"/>
-      <c r="I1551" t="inlineStr">
-        <is>
-          <t>5592994195086</t>
-        </is>
+      <c r="I1551" t="n">
+        <v>5592994195086</v>
       </c>
       <c r="J1551" t="inlineStr"/>
       <c r="K1551" t="n">
@@ -76203,10 +76197,8 @@
         </is>
       </c>
       <c r="H1553" t="inlineStr"/>
-      <c r="I1553" t="inlineStr">
-        <is>
-          <t>5591981878047</t>
-        </is>
+      <c r="I1553" t="n">
+        <v>5591981878047</v>
       </c>
       <c r="J1553" t="inlineStr"/>
       <c r="K1553" t="n">
@@ -76255,10 +76247,8 @@
         </is>
       </c>
       <c r="H1554" t="inlineStr"/>
-      <c r="I1554" t="inlineStr">
-        <is>
-          <t>5591985044237</t>
-        </is>
+      <c r="I1554" t="n">
+        <v>5591985044237</v>
       </c>
       <c r="J1554" t="inlineStr"/>
       <c r="K1554" t="n">
@@ -76307,10 +76297,8 @@
         </is>
       </c>
       <c r="H1555" t="inlineStr"/>
-      <c r="I1555" t="inlineStr">
-        <is>
-          <t>5591982598910</t>
-        </is>
+      <c r="I1555" t="n">
+        <v>5591982598910</v>
       </c>
       <c r="J1555" t="inlineStr"/>
       <c r="K1555" t="n">
@@ -76359,10 +76347,8 @@
         </is>
       </c>
       <c r="H1556" t="inlineStr"/>
-      <c r="I1556" t="inlineStr">
-        <is>
-          <t>5591984353838</t>
-        </is>
+      <c r="I1556" t="n">
+        <v>5591984353838</v>
       </c>
       <c r="J1556" t="inlineStr"/>
       <c r="K1556" t="n">
@@ -76459,10 +76445,8 @@
         </is>
       </c>
       <c r="H1558" t="inlineStr"/>
-      <c r="I1558" t="inlineStr">
-        <is>
-          <t>5591986170522</t>
-        </is>
+      <c r="I1558" t="n">
+        <v>5591986170522</v>
       </c>
       <c r="J1558" t="inlineStr"/>
       <c r="K1558" t="n">
@@ -76511,10 +76495,8 @@
         </is>
       </c>
       <c r="H1559" t="inlineStr"/>
-      <c r="I1559" t="inlineStr">
-        <is>
-          <t>5591981785235</t>
-        </is>
+      <c r="I1559" t="n">
+        <v>5591981785235</v>
       </c>
       <c r="J1559" t="inlineStr"/>
       <c r="K1559" t="n">
@@ -76563,10 +76545,8 @@
         </is>
       </c>
       <c r="H1560" t="inlineStr"/>
-      <c r="I1560" t="inlineStr">
-        <is>
-          <t>5591986349528</t>
-        </is>
+      <c r="I1560" t="n">
+        <v>5591986349528</v>
       </c>
       <c r="J1560" t="inlineStr"/>
       <c r="K1560" t="n">
@@ -76615,10 +76595,8 @@
         </is>
       </c>
       <c r="H1561" t="inlineStr"/>
-      <c r="I1561" t="inlineStr">
-        <is>
-          <t>5591991040759</t>
-        </is>
+      <c r="I1561" t="n">
+        <v>5591991040759</v>
       </c>
       <c r="J1561" t="inlineStr"/>
       <c r="K1561" t="n">
@@ -76667,16 +76645,810 @@
         </is>
       </c>
       <c r="H1562" t="inlineStr"/>
-      <c r="I1562" t="inlineStr">
-        <is>
-          <t>5591983759584</t>
-        </is>
+      <c r="I1562" t="n">
+        <v>5591983759584</v>
       </c>
       <c r="J1562" t="inlineStr"/>
       <c r="K1562" t="n">
         <v>55</v>
       </c>
       <c r="L1562" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>Fraturas</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>https://www.thiagomendoncaortopedista.com</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr"/>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>558299007213</t>
+        </is>
+      </c>
+      <c r="J1563" t="inlineStr"/>
+      <c r="K1563" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1563" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>Jully Barbosa Psicóloga Maceió</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>https://www.jullybarbosapsicologa.com</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr"/>
+      <c r="I1564" t="inlineStr"/>
+      <c r="J1564" t="inlineStr"/>
+      <c r="K1564" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1564" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>Chá de Terapia</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>https://www.chadeterapia.com</t>
+        </is>
+      </c>
+      <c r="H1565" t="inlineStr"/>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>558298400449</t>
+        </is>
+      </c>
+      <c r="J1565" t="inlineStr"/>
+      <c r="K1565" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1565" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>TFG Advocacia</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>https://tfgadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr"/>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>5582982000797</t>
+        </is>
+      </c>
+      <c r="J1566" t="inlineStr"/>
+      <c r="K1566" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1566" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>Graduação em Educação Física CESMAC Presencial</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>https://cursos.io</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr"/>
+      <c r="I1567" t="inlineStr"/>
+      <c r="J1567" t="inlineStr"/>
+      <c r="K1567" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1567" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>Educação Física - Licenciatura com bolsa EAD</t>
+        </is>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>https://www.faculdadesdobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr"/>
+      <c r="I1568" t="inlineStr">
+        <is>
+          <t>5515992550132</t>
+        </is>
+      </c>
+      <c r="J1568" t="inlineStr"/>
+      <c r="K1568" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1568" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>Educação Física, UFAL</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>https://cursarei.com.br</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr"/>
+      <c r="I1569" t="inlineStr"/>
+      <c r="J1569" t="inlineStr"/>
+      <c r="K1569" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1569" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>Educação Física (Semipresencial Maceió) UMJ</t>
+        </is>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>https://umj.edu.br</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr"/>
+      <c r="I1570" t="inlineStr"/>
+      <c r="J1570" t="inlineStr"/>
+      <c r="K1570" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1570" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>Advogados em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>https://masterjuris.com.br</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr"/>
+      <c r="I1571" t="inlineStr"/>
+      <c r="J1571" t="inlineStr"/>
+      <c r="K1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1571" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>https://landing.unifacs.br</t>
+        </is>
+      </c>
+      <c r="H1572" t="inlineStr"/>
+      <c r="I1572" t="inlineStr"/>
+      <c r="J1572" t="inlineStr"/>
+      <c r="K1572" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1572" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>Alyne Santos</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>https://alynesantospsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr"/>
+      <c r="I1573" t="inlineStr"/>
+      <c r="J1573" t="inlineStr"/>
+      <c r="K1573" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1573" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>Gabriel Brasil Psicólogo em Fortaleza / CE</t>
+        </is>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>https://gabrielbrasilpsi.com</t>
+        </is>
+      </c>
+      <c r="H1574" t="inlineStr"/>
+      <c r="I1574" t="inlineStr">
+        <is>
+          <t>5585996539922</t>
+        </is>
+      </c>
+      <c r="J1574" t="inlineStr"/>
+      <c r="K1574" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1574" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>Fátima Marques</t>
+        </is>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>https://www.psicologafatimamarques.com.br</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr"/>
+      <c r="I1575" t="inlineStr"/>
+      <c r="J1575" t="inlineStr"/>
+      <c r="K1575" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1575" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>Massagem em Fortaleza CE</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>https://terapeutasfortaleza.com</t>
+        </is>
+      </c>
+      <c r="H1576" t="inlineStr"/>
+      <c r="I1576" t="inlineStr">
+        <is>
+          <t>5585982183038</t>
+        </is>
+      </c>
+      <c r="J1576" t="inlineStr"/>
+      <c r="K1576" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1576" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>Sara Ammarati</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>https://massagemceara.com.br</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr"/>
+      <c r="I1577" t="inlineStr">
+        <is>
+          <t>5511943909759</t>
+        </is>
+      </c>
+      <c r="J1577" t="inlineStr"/>
+      <c r="K1577" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1577" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>Psicóloga Daniela Rolim</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>https://www.psicologadanielarolim.com.br</t>
+        </is>
+      </c>
+      <c r="H1578" t="inlineStr"/>
+      <c r="I1578" t="inlineStr"/>
+      <c r="J1578" t="inlineStr"/>
+      <c r="K1578" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1578" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1578"/>
+  <dimension ref="A1:L1583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76695,10 +76695,8 @@
         </is>
       </c>
       <c r="H1563" t="inlineStr"/>
-      <c r="I1563" t="inlineStr">
-        <is>
-          <t>558299007213</t>
-        </is>
+      <c r="I1563" t="n">
+        <v>558299007213</v>
       </c>
       <c r="J1563" t="inlineStr"/>
       <c r="K1563" t="n">
@@ -76795,10 +76793,8 @@
         </is>
       </c>
       <c r="H1565" t="inlineStr"/>
-      <c r="I1565" t="inlineStr">
-        <is>
-          <t>558298400449</t>
-        </is>
+      <c r="I1565" t="n">
+        <v>558298400449</v>
       </c>
       <c r="J1565" t="inlineStr"/>
       <c r="K1565" t="n">
@@ -76847,10 +76843,8 @@
         </is>
       </c>
       <c r="H1566" t="inlineStr"/>
-      <c r="I1566" t="inlineStr">
-        <is>
-          <t>5582982000797</t>
-        </is>
+      <c r="I1566" t="n">
+        <v>5582982000797</v>
       </c>
       <c r="J1566" t="inlineStr"/>
       <c r="K1566" t="n">
@@ -76947,10 +76941,8 @@
         </is>
       </c>
       <c r="H1568" t="inlineStr"/>
-      <c r="I1568" t="inlineStr">
-        <is>
-          <t>5515992550132</t>
-        </is>
+      <c r="I1568" t="n">
+        <v>5515992550132</v>
       </c>
       <c r="J1568" t="inlineStr"/>
       <c r="K1568" t="n">
@@ -77239,10 +77231,8 @@
         </is>
       </c>
       <c r="H1574" t="inlineStr"/>
-      <c r="I1574" t="inlineStr">
-        <is>
-          <t>5585996539922</t>
-        </is>
+      <c r="I1574" t="n">
+        <v>5585996539922</v>
       </c>
       <c r="J1574" t="inlineStr"/>
       <c r="K1574" t="n">
@@ -77339,10 +77329,8 @@
         </is>
       </c>
       <c r="H1576" t="inlineStr"/>
-      <c r="I1576" t="inlineStr">
-        <is>
-          <t>5585982183038</t>
-        </is>
+      <c r="I1576" t="n">
+        <v>5585982183038</v>
       </c>
       <c r="J1576" t="inlineStr"/>
       <c r="K1576" t="n">
@@ -77391,10 +77379,8 @@
         </is>
       </c>
       <c r="H1577" t="inlineStr"/>
-      <c r="I1577" t="inlineStr">
-        <is>
-          <t>5511943909759</t>
-        </is>
+      <c r="I1577" t="n">
+        <v>5511943909759</v>
       </c>
       <c r="J1577" t="inlineStr"/>
       <c r="K1577" t="n">
@@ -77454,6 +77440,250 @@
         </is>
       </c>
     </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>Fisioclin</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>https://www.fisioclinbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr"/>
+      <c r="I1579" t="inlineStr"/>
+      <c r="J1579" t="inlineStr"/>
+      <c r="K1579" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1579" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Cuiabá (MT) — Agendar consulta</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>https://endoclinicas.com</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr"/>
+      <c r="I1580" t="inlineStr"/>
+      <c r="J1580" t="inlineStr"/>
+      <c r="K1580" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1580" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>Dr. Estevão Virgilio</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>https://drestevaovirgilio.com.br</t>
+        </is>
+      </c>
+      <c r="H1581" t="inlineStr"/>
+      <c r="I1581" t="inlineStr"/>
+      <c r="J1581" t="inlineStr"/>
+      <c r="K1581" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1581" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>Dr. Daniel Figueiredo e Silva</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>https://drdanielgeriatra.com.br</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr"/>
+      <c r="I1582" t="inlineStr">
+        <is>
+          <t>5565981291176</t>
+        </is>
+      </c>
+      <c r="J1582" t="inlineStr"/>
+      <c r="K1582" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1582" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>Dra. Giselly Almeida</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>https://www.dragisellyalmeida.com.br</t>
+        </is>
+      </c>
+      <c r="H1583" t="inlineStr"/>
+      <c r="I1583" t="inlineStr"/>
+      <c r="J1583" t="inlineStr"/>
+      <c r="K1583" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1583" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1583"/>
+  <dimension ref="A1:L1592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77621,10 +77621,8 @@
         </is>
       </c>
       <c r="H1582" t="inlineStr"/>
-      <c r="I1582" t="inlineStr">
-        <is>
-          <t>5565981291176</t>
-        </is>
+      <c r="I1582" t="n">
+        <v>5565981291176</v>
       </c>
       <c r="J1582" t="inlineStr"/>
       <c r="K1582" t="n">
@@ -77684,6 +77682,450 @@
         </is>
       </c>
     </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>TOPFITNESS</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>http://www.topfitness.com.br</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr"/>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>5527988801000</t>
+        </is>
+      </c>
+      <c r="J1584" t="inlineStr"/>
+      <c r="K1584" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1584" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>Academia Vitória Sports</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>https://anajustrabeneficios.com.br</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr"/>
+      <c r="I1585" t="inlineStr"/>
+      <c r="J1585" t="inlineStr"/>
+      <c r="K1585" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1585" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>Academia Vitória Sports</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>https://www.planetabrasileiro.com</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr"/>
+      <c r="I1586" t="inlineStr"/>
+      <c r="J1586" t="inlineStr"/>
+      <c r="K1586" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1586" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>Academias em Vitória, Espírito Santo, ES</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>https://www.encontraes.com.br</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr"/>
+      <c r="I1587" t="inlineStr"/>
+      <c r="J1587" t="inlineStr"/>
+      <c r="K1587" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1587" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>Mariângela Prado</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>https://mariangelaprado.com.br</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr"/>
+      <c r="I1588" t="inlineStr">
+        <is>
+          <t>5531988771964</t>
+        </is>
+      </c>
+      <c r="J1588" t="inlineStr"/>
+      <c r="K1588" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1588" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>Dayrell Hotel</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>https://www.dayrell.com.br</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr"/>
+      <c r="I1589" t="inlineStr"/>
+      <c r="J1589" t="inlineStr"/>
+      <c r="K1589" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1589" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>Natação em Belo Horizonte: escolas, academias e aulas</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>https://natacaoemfoco.com.br</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr"/>
+      <c r="I1590" t="inlineStr"/>
+      <c r="J1590" t="inlineStr"/>
+      <c r="K1590" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1590" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>Instituto Federal de Educação, Ciência e Tecnologia de ...</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>https://www.ifmg.edu.br</t>
+        </is>
+      </c>
+      <c r="H1591" t="inlineStr"/>
+      <c r="I1591" t="inlineStr"/>
+      <c r="J1591" t="inlineStr"/>
+      <c r="K1591" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1591" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Belo Horizonte · Trícia Borsatto</t>
+        </is>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>https://triciaborsattofisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1592" t="inlineStr"/>
+      <c r="I1592" t="inlineStr">
+        <is>
+          <t>5531995025166</t>
+        </is>
+      </c>
+      <c r="J1592" t="inlineStr"/>
+      <c r="K1592" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1592" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1592"/>
+  <dimension ref="A1:L1606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77719,10 +77719,8 @@
         </is>
       </c>
       <c r="H1584" t="inlineStr"/>
-      <c r="I1584" t="inlineStr">
-        <is>
-          <t>5527988801000</t>
-        </is>
+      <c r="I1584" t="n">
+        <v>5527988801000</v>
       </c>
       <c r="J1584" t="inlineStr"/>
       <c r="K1584" t="n">
@@ -77915,10 +77913,8 @@
         </is>
       </c>
       <c r="H1588" t="inlineStr"/>
-      <c r="I1588" t="inlineStr">
-        <is>
-          <t>5531988771964</t>
-        </is>
+      <c r="I1588" t="n">
+        <v>5531988771964</v>
       </c>
       <c r="J1588" t="inlineStr"/>
       <c r="K1588" t="n">
@@ -78111,16 +78107,718 @@
         </is>
       </c>
       <c r="H1592" t="inlineStr"/>
-      <c r="I1592" t="inlineStr">
-        <is>
-          <t>5531995025166</t>
-        </is>
+      <c r="I1592" t="n">
+        <v>5531995025166</v>
       </c>
       <c r="J1592" t="inlineStr"/>
       <c r="K1592" t="n">
         <v>67</v>
       </c>
       <c r="L1592" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>Clinimarc</t>
+        </is>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>https://clinimarc.com.br</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr"/>
+      <c r="I1593" t="inlineStr"/>
+      <c r="J1593" t="inlineStr"/>
+      <c r="K1593" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1593" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>Ederson Erig</t>
+        </is>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>https://www.edersonerig.com.br</t>
+        </is>
+      </c>
+      <c r="H1594" t="inlineStr"/>
+      <c r="I1594" t="inlineStr"/>
+      <c r="J1594" t="inlineStr"/>
+      <c r="K1594" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1594" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>Spazio Psicologia Clínica</t>
+        </is>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>https://www.spaziopsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr"/>
+      <c r="I1595" t="inlineStr"/>
+      <c r="J1595" t="inlineStr"/>
+      <c r="K1595" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1595" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>Psicóloga Gisele Souza</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>https://www.psicogiselesouza.com</t>
+        </is>
+      </c>
+      <c r="H1596" t="inlineStr"/>
+      <c r="I1596" t="inlineStr">
+        <is>
+          <t>5541996382889</t>
+        </is>
+      </c>
+      <c r="J1596" t="inlineStr"/>
+      <c r="K1596" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1596" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>Thiago Oliari - Psicologia</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>https://www.psioliari.com</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr"/>
+      <c r="I1597" t="inlineStr">
+        <is>
+          <t>5541988560408</t>
+        </is>
+      </c>
+      <c r="J1597" t="inlineStr"/>
+      <c r="K1597" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1597" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>Guia Médico</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>https://app.unimedpoa.com.br</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr"/>
+      <c r="I1598" t="inlineStr"/>
+      <c r="J1598" t="inlineStr"/>
+      <c r="K1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1598" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>Dentista em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>https://rcodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr"/>
+      <c r="I1599" t="inlineStr">
+        <is>
+          <t>5551984461749</t>
+        </is>
+      </c>
+      <c r="J1599" t="inlineStr"/>
+      <c r="K1599" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1599" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>https://www.magmaodonto.com</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr"/>
+      <c r="I1600" t="inlineStr">
+        <is>
+          <t>5551996558544</t>
+        </is>
+      </c>
+      <c r="J1600" t="inlineStr"/>
+      <c r="K1600" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1600" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>Rodrigues &amp; Silva Advocacia</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>https://rsadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr"/>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>555185130721</t>
+        </is>
+      </c>
+      <c r="J1601" t="inlineStr"/>
+      <c r="K1601" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1601" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>Assis Brasil</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>https://academiacorpoealma.com</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr"/>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>555137416253</t>
+        </is>
+      </c>
+      <c r="J1602" t="inlineStr"/>
+      <c r="K1602" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1602" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>Espaço de Fisioterapia Dra. Caroline Mazutti</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>https://www.espacodracarolinemazutti.com</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr"/>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>5551997492556</t>
+        </is>
+      </c>
+      <c r="J1603" t="inlineStr"/>
+      <c r="K1603" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1603" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>Médicos, Clínicas e Consultórios Medicos em Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>https://www.encontraflorianopolis.com.br</t>
+        </is>
+      </c>
+      <c r="H1604" t="inlineStr"/>
+      <c r="I1604" t="inlineStr"/>
+      <c r="J1604" t="inlineStr"/>
+      <c r="K1604" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1604" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>Médicos e Clínicas no Centro de Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>https://www.encontracentrofloripa.com.br</t>
+        </is>
+      </c>
+      <c r="H1605" t="inlineStr"/>
+      <c r="I1605" t="inlineStr"/>
+      <c r="J1605" t="inlineStr"/>
+      <c r="K1605" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1605" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>Dra. Juliana Esmanhotto de Almeida</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>https://www.drajulianaesmanhotto.com</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr"/>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>5548991413325</t>
+        </is>
+      </c>
+      <c r="J1606" t="inlineStr"/>
+      <c r="K1606" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1606" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1606"/>
+  <dimension ref="A1:L1621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78301,10 +78301,8 @@
         </is>
       </c>
       <c r="H1596" t="inlineStr"/>
-      <c r="I1596" t="inlineStr">
-        <is>
-          <t>5541996382889</t>
-        </is>
+      <c r="I1596" t="n">
+        <v>5541996382889</v>
       </c>
       <c r="J1596" t="inlineStr"/>
       <c r="K1596" t="n">
@@ -78353,10 +78351,8 @@
         </is>
       </c>
       <c r="H1597" t="inlineStr"/>
-      <c r="I1597" t="inlineStr">
-        <is>
-          <t>5541988560408</t>
-        </is>
+      <c r="I1597" t="n">
+        <v>5541988560408</v>
       </c>
       <c r="J1597" t="inlineStr"/>
       <c r="K1597" t="n">
@@ -78453,10 +78449,8 @@
         </is>
       </c>
       <c r="H1599" t="inlineStr"/>
-      <c r="I1599" t="inlineStr">
-        <is>
-          <t>5551984461749</t>
-        </is>
+      <c r="I1599" t="n">
+        <v>5551984461749</v>
       </c>
       <c r="J1599" t="inlineStr"/>
       <c r="K1599" t="n">
@@ -78505,10 +78499,8 @@
         </is>
       </c>
       <c r="H1600" t="inlineStr"/>
-      <c r="I1600" t="inlineStr">
-        <is>
-          <t>5551996558544</t>
-        </is>
+      <c r="I1600" t="n">
+        <v>5551996558544</v>
       </c>
       <c r="J1600" t="inlineStr"/>
       <c r="K1600" t="n">
@@ -78557,10 +78549,8 @@
         </is>
       </c>
       <c r="H1601" t="inlineStr"/>
-      <c r="I1601" t="inlineStr">
-        <is>
-          <t>555185130721</t>
-        </is>
+      <c r="I1601" t="n">
+        <v>555185130721</v>
       </c>
       <c r="J1601" t="inlineStr"/>
       <c r="K1601" t="n">
@@ -78609,10 +78599,8 @@
         </is>
       </c>
       <c r="H1602" t="inlineStr"/>
-      <c r="I1602" t="inlineStr">
-        <is>
-          <t>555137416253</t>
-        </is>
+      <c r="I1602" t="n">
+        <v>555137416253</v>
       </c>
       <c r="J1602" t="inlineStr"/>
       <c r="K1602" t="n">
@@ -78661,10 +78649,8 @@
         </is>
       </c>
       <c r="H1603" t="inlineStr"/>
-      <c r="I1603" t="inlineStr">
-        <is>
-          <t>5551997492556</t>
-        </is>
+      <c r="I1603" t="n">
+        <v>5551997492556</v>
       </c>
       <c r="J1603" t="inlineStr"/>
       <c r="K1603" t="n">
@@ -78809,16 +78795,750 @@
         </is>
       </c>
       <c r="H1606" t="inlineStr"/>
-      <c r="I1606" t="inlineStr">
-        <is>
-          <t>5548991413325</t>
-        </is>
+      <c r="I1606" t="n">
+        <v>5548991413325</v>
       </c>
       <c r="J1606" t="inlineStr"/>
       <c r="K1606" t="n">
         <v>69</v>
       </c>
       <c r="L1606" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>Psicólogo em Macapá</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>https://www.marciliolira.com</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr"/>
+      <c r="I1607" t="inlineStr"/>
+      <c r="J1607" t="inlineStr"/>
+      <c r="K1607" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1607" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>Você conhece o curso de Educação Física da UNIFAP?</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>https://www.unifap.br</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr"/>
+      <c r="I1608" t="inlineStr"/>
+      <c r="J1608" t="inlineStr"/>
+      <c r="K1608" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1608" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>Clinica Ebenezer</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>https://www.clinicaebenezer.com</t>
+        </is>
+      </c>
+      <c r="H1609" t="inlineStr"/>
+      <c r="I1609" t="inlineStr"/>
+      <c r="J1609" t="inlineStr"/>
+      <c r="K1609" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1609" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>Dentistas</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>https://acheseudentista.com.br</t>
+        </is>
+      </c>
+      <c r="H1610" t="inlineStr"/>
+      <c r="I1610" t="inlineStr"/>
+      <c r="J1610" t="inlineStr"/>
+      <c r="K1610" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1610" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>Psicóloga em Manaus</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>https://psicologafatimafarias.com.br</t>
+        </is>
+      </c>
+      <c r="H1611" t="inlineStr"/>
+      <c r="I1611" t="inlineStr">
+        <is>
+          <t>5592999960521</t>
+        </is>
+      </c>
+      <c r="J1611" t="inlineStr"/>
+      <c r="K1611" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1611" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>Cidade: Manaus</t>
+        </is>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>https://centraldeterapeutas.com.br</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr"/>
+      <c r="I1612" t="inlineStr">
+        <is>
+          <t>5511949482332</t>
+        </is>
+      </c>
+      <c r="J1612" t="inlineStr"/>
+      <c r="K1612" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1612" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>ADVOGADO MANAUS</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>https://advogadomanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr"/>
+      <c r="I1613" t="inlineStr"/>
+      <c r="J1613" t="inlineStr"/>
+      <c r="K1613" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1613" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Dra. Amanda Dias Simões</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>https://adsdo.com.br</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr"/>
+      <c r="I1614" t="inlineStr"/>
+      <c r="J1614" t="inlineStr"/>
+      <c r="K1614" t="n">
+        <v>45</v>
+      </c>
+      <c r="L1614" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>Os 7 Fisioterapeuta mais indicados em Manaus/AM</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>https://en.catalogo.med.br</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr"/>
+      <c r="I1615" t="inlineStr"/>
+      <c r="J1615" t="inlineStr"/>
+      <c r="K1615" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1615" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>Saúde para toda a família</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>https://www.clinicacaluf.com</t>
+        </is>
+      </c>
+      <c r="H1616" t="inlineStr"/>
+      <c r="I1616" t="inlineStr"/>
+      <c r="J1616" t="inlineStr"/>
+      <c r="K1616" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1616" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>Clínica Saúde Belém</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>https://saudebelem.cloud</t>
+        </is>
+      </c>
+      <c r="H1617" t="inlineStr"/>
+      <c r="I1617" t="inlineStr"/>
+      <c r="J1617" t="inlineStr"/>
+      <c r="K1617" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1617" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>Dra. Fabíola Azevedo</t>
+        </is>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>https://www.drafabiolaazevedo.com.br</t>
+        </is>
+      </c>
+      <c r="H1618" t="inlineStr"/>
+      <c r="I1618" t="inlineStr">
+        <is>
+          <t>5591999811196</t>
+        </is>
+      </c>
+      <c r="J1618" t="inlineStr"/>
+      <c r="K1618" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1618" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>Dentista em Belém</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>https://oralfybelem.com.br</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr"/>
+      <c r="I1619" t="inlineStr">
+        <is>
+          <t>5591993060141</t>
+        </is>
+      </c>
+      <c r="J1619" t="inlineStr"/>
+      <c r="K1619" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1619" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>Oral Clínica Belém</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>https://oralclinicabelem.com.br</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr"/>
+      <c r="I1620" t="inlineStr"/>
+      <c r="J1620" t="inlineStr"/>
+      <c r="K1620" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1620" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>Consultório Dra. Caroline Caldeira</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>https://www.dracarolinecaldeira.com</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr"/>
+      <c r="I1621" t="inlineStr"/>
+      <c r="J1621" t="inlineStr"/>
+      <c r="K1621" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1621" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1621"/>
+  <dimension ref="A1:L1631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79037,10 +79037,8 @@
         </is>
       </c>
       <c r="H1611" t="inlineStr"/>
-      <c r="I1611" t="inlineStr">
-        <is>
-          <t>5592999960521</t>
-        </is>
+      <c r="I1611" t="n">
+        <v>5592999960521</v>
       </c>
       <c r="J1611" t="inlineStr"/>
       <c r="K1611" t="n">
@@ -79089,10 +79087,8 @@
         </is>
       </c>
       <c r="H1612" t="inlineStr"/>
-      <c r="I1612" t="inlineStr">
-        <is>
-          <t>5511949482332</t>
-        </is>
+      <c r="I1612" t="n">
+        <v>5511949482332</v>
       </c>
       <c r="J1612" t="inlineStr"/>
       <c r="K1612" t="n">
@@ -79381,10 +79377,8 @@
         </is>
       </c>
       <c r="H1618" t="inlineStr"/>
-      <c r="I1618" t="inlineStr">
-        <is>
-          <t>5591999811196</t>
-        </is>
+      <c r="I1618" t="n">
+        <v>5591999811196</v>
       </c>
       <c r="J1618" t="inlineStr"/>
       <c r="K1618" t="n">
@@ -79433,10 +79427,8 @@
         </is>
       </c>
       <c r="H1619" t="inlineStr"/>
-      <c r="I1619" t="inlineStr">
-        <is>
-          <t>5591993060141</t>
-        </is>
+      <c r="I1619" t="n">
+        <v>5591993060141</v>
       </c>
       <c r="J1619" t="inlineStr"/>
       <c r="K1619" t="n">
@@ -79544,6 +79536,514 @@
         </is>
       </c>
     </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>Advogado em Maceió</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>https://acucena.adv.br</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr"/>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>5582993669393</t>
+        </is>
+      </c>
+      <c r="J1622" t="inlineStr"/>
+      <c r="K1622" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1622" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>Cliasi</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>https://cliasi.com.br</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr"/>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>557131906418</t>
+        </is>
+      </c>
+      <c r="J1623" t="inlineStr"/>
+      <c r="K1623" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1623" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>Advogado em Salvador</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>https://vitorsousa.adv.br</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr"/>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>5571991447281</t>
+        </is>
+      </c>
+      <c r="J1624" t="inlineStr"/>
+      <c r="K1624" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1624" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>Academia Salvador terá novo sistema para agendar aulas gratuitas</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>https://bahia.ba</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr"/>
+      <c r="I1625" t="inlineStr"/>
+      <c r="J1625" t="inlineStr"/>
+      <c r="K1625" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1625" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Pinho Psicólogo</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>https://www.felipepinho.com.br</t>
+        </is>
+      </c>
+      <c r="H1626" t="inlineStr"/>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>5585986737095</t>
+        </is>
+      </c>
+      <c r="J1626" t="inlineStr"/>
+      <c r="K1626" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1626" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>Psicóloga Linda Teles</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>https://lindateles.com.br</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr"/>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>558588811012</t>
+        </is>
+      </c>
+      <c r="J1627" t="inlineStr"/>
+      <c r="K1627" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1627" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>Advogados em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>https://brasiladvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr"/>
+      <c r="I1628" t="inlineStr"/>
+      <c r="J1628" t="inlineStr"/>
+      <c r="K1628" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1628" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>Advogado de Família em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>https://www.stivelcarvalho.adv.br</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr"/>
+      <c r="I1629" t="inlineStr">
+        <is>
+          <t>5585996819771</t>
+        </is>
+      </c>
+      <c r="J1629" t="inlineStr"/>
+      <c r="K1629" t="n">
+        <v>100</v>
+      </c>
+      <c r="L1629" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>Bezerra de Menezes Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>https://www.bezerrademenezes.adv.br</t>
+        </is>
+      </c>
+      <c r="H1630" t="inlineStr"/>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>5585996732394</t>
+        </is>
+      </c>
+      <c r="J1630" t="inlineStr"/>
+      <c r="K1630" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1630" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>https://guia.fortal.br</t>
+        </is>
+      </c>
+      <c r="H1631" t="inlineStr"/>
+      <c r="I1631" t="inlineStr"/>
+      <c r="J1631" t="inlineStr"/>
+      <c r="K1631" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1631" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1631"/>
+  <dimension ref="A1:L1638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79573,10 +79573,8 @@
         </is>
       </c>
       <c r="H1622" t="inlineStr"/>
-      <c r="I1622" t="inlineStr">
-        <is>
-          <t>5582993669393</t>
-        </is>
+      <c r="I1622" t="n">
+        <v>5582993669393</v>
       </c>
       <c r="J1622" t="inlineStr"/>
       <c r="K1622" t="n">
@@ -79625,10 +79623,8 @@
         </is>
       </c>
       <c r="H1623" t="inlineStr"/>
-      <c r="I1623" t="inlineStr">
-        <is>
-          <t>557131906418</t>
-        </is>
+      <c r="I1623" t="n">
+        <v>557131906418</v>
       </c>
       <c r="J1623" t="inlineStr"/>
       <c r="K1623" t="n">
@@ -79677,10 +79673,8 @@
         </is>
       </c>
       <c r="H1624" t="inlineStr"/>
-      <c r="I1624" t="inlineStr">
-        <is>
-          <t>5571991447281</t>
-        </is>
+      <c r="I1624" t="n">
+        <v>5571991447281</v>
       </c>
       <c r="J1624" t="inlineStr"/>
       <c r="K1624" t="n">
@@ -79777,10 +79771,8 @@
         </is>
       </c>
       <c r="H1626" t="inlineStr"/>
-      <c r="I1626" t="inlineStr">
-        <is>
-          <t>5585986737095</t>
-        </is>
+      <c r="I1626" t="n">
+        <v>5585986737095</v>
       </c>
       <c r="J1626" t="inlineStr"/>
       <c r="K1626" t="n">
@@ -79829,10 +79821,8 @@
         </is>
       </c>
       <c r="H1627" t="inlineStr"/>
-      <c r="I1627" t="inlineStr">
-        <is>
-          <t>558588811012</t>
-        </is>
+      <c r="I1627" t="n">
+        <v>558588811012</v>
       </c>
       <c r="J1627" t="inlineStr"/>
       <c r="K1627" t="n">
@@ -79929,10 +79919,8 @@
         </is>
       </c>
       <c r="H1629" t="inlineStr"/>
-      <c r="I1629" t="inlineStr">
-        <is>
-          <t>5585996819771</t>
-        </is>
+      <c r="I1629" t="n">
+        <v>5585996819771</v>
       </c>
       <c r="J1629" t="inlineStr"/>
       <c r="K1629" t="n">
@@ -79981,10 +79969,8 @@
         </is>
       </c>
       <c r="H1630" t="inlineStr"/>
-      <c r="I1630" t="inlineStr">
-        <is>
-          <t>5585996732394</t>
-        </is>
+      <c r="I1630" t="n">
+        <v>5585996732394</v>
       </c>
       <c r="J1630" t="inlineStr"/>
       <c r="K1630" t="n">
@@ -80044,6 +80030,354 @@
         </is>
       </c>
     </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>Fit One Academias</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>https://www.fitoneacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1632" t="inlineStr"/>
+      <c r="I1632" t="inlineStr">
+        <is>
+          <t>5561992499590</t>
+        </is>
+      </c>
+      <c r="J1632" t="inlineStr"/>
+      <c r="K1632" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1632" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>Clinica CMD</t>
+        </is>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>https://clinicacmdgo.com.br</t>
+        </is>
+      </c>
+      <c r="H1633" t="inlineStr"/>
+      <c r="I1633" t="inlineStr"/>
+      <c r="J1633" t="inlineStr"/>
+      <c r="K1633" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1633" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>José Rizzotto Neto</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>https://www.joserizzottoneto.com.br</t>
+        </is>
+      </c>
+      <c r="H1634" t="inlineStr"/>
+      <c r="I1634" t="inlineStr">
+        <is>
+          <t>5565981116230</t>
+        </is>
+      </c>
+      <c r="J1634" t="inlineStr"/>
+      <c r="K1634" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1634" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>Patricia Katz</t>
+        </is>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>https://www.psicologapatriciakatz.com</t>
+        </is>
+      </c>
+      <c r="H1635" t="inlineStr"/>
+      <c r="I1635" t="inlineStr"/>
+      <c r="J1635" t="inlineStr"/>
+      <c r="K1635" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1635" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>Clínica de Psicologia Andréia Corrêa Psique em Cuiabá MT</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>https://www.andreiacorreapsique.com.br</t>
+        </is>
+      </c>
+      <c r="H1636" t="inlineStr"/>
+      <c r="I1636" t="inlineStr">
+        <is>
+          <t>5565981272795</t>
+        </is>
+      </c>
+      <c r="J1636" t="inlineStr"/>
+      <c r="K1636" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1636" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>Guia Cidade</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>https://guiacidade.com.br</t>
+        </is>
+      </c>
+      <c r="H1637" t="inlineStr"/>
+      <c r="I1637" t="inlineStr"/>
+      <c r="J1637" t="inlineStr"/>
+      <c r="K1637" t="n">
+        <v>47</v>
+      </c>
+      <c r="L1637" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>Tecfit Brasil</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>https://www.tecfitbrasil.com</t>
+        </is>
+      </c>
+      <c r="H1638" t="inlineStr"/>
+      <c r="I1638" t="inlineStr"/>
+      <c r="J1638" t="inlineStr"/>
+      <c r="K1638" t="n">
+        <v>40</v>
+      </c>
+      <c r="L1638" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1638"/>
+  <dimension ref="A1:L1650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80067,10 +80067,8 @@
         </is>
       </c>
       <c r="H1632" t="inlineStr"/>
-      <c r="I1632" t="inlineStr">
-        <is>
-          <t>5561992499590</t>
-        </is>
+      <c r="I1632" t="n">
+        <v>5561992499590</v>
       </c>
       <c r="J1632" t="inlineStr"/>
       <c r="K1632" t="n">
@@ -80167,10 +80165,8 @@
         </is>
       </c>
       <c r="H1634" t="inlineStr"/>
-      <c r="I1634" t="inlineStr">
-        <is>
-          <t>5565981116230</t>
-        </is>
+      <c r="I1634" t="n">
+        <v>5565981116230</v>
       </c>
       <c r="J1634" t="inlineStr"/>
       <c r="K1634" t="n">
@@ -80267,10 +80263,8 @@
         </is>
       </c>
       <c r="H1636" t="inlineStr"/>
-      <c r="I1636" t="inlineStr">
-        <is>
-          <t>5565981272795</t>
-        </is>
+      <c r="I1636" t="n">
+        <v>5565981272795</v>
       </c>
       <c r="J1636" t="inlineStr"/>
       <c r="K1636" t="n">
@@ -80378,6 +80372,602 @@
         </is>
       </c>
     </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>Clínica Vitória</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>https://vitoriaclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H1639" t="inlineStr"/>
+      <c r="I1639" t="inlineStr"/>
+      <c r="J1639" t="inlineStr"/>
+      <c r="K1639" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1639" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia e Reabilitação Vitória</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>http://clinicavitoria.com</t>
+        </is>
+      </c>
+      <c r="H1640" t="inlineStr"/>
+      <c r="I1640" t="inlineStr"/>
+      <c r="J1640" t="inlineStr"/>
+      <c r="K1640" t="n">
+        <v>47</v>
+      </c>
+      <c r="L1640" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>Clínica Vitória Saúde</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>https://vitoriasaude.com</t>
+        </is>
+      </c>
+      <c r="H1641" t="inlineStr"/>
+      <c r="I1641" t="inlineStr">
+        <is>
+          <t>5521965328002</t>
+        </is>
+      </c>
+      <c r="J1641" t="inlineStr"/>
+      <c r="K1641" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1641" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>Hospital Vitória</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>https://www.hospitalvitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H1642" t="inlineStr"/>
+      <c r="I1642" t="inlineStr"/>
+      <c r="J1642" t="inlineStr"/>
+      <c r="K1642" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1642" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>Clínica Neurologia Integrada</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>https://www.neurologiavitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H1643" t="inlineStr"/>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>5527997950350</t>
+        </is>
+      </c>
+      <c r="J1643" t="inlineStr"/>
+      <c r="K1643" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1643" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>Médicos, Clínicas e Consultórios Medicos no Centro de Belo ...</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>https://www.encontracentrobh.com.br</t>
+        </is>
+      </c>
+      <c r="H1644" t="inlineStr"/>
+      <c r="I1644" t="inlineStr"/>
+      <c r="J1644" t="inlineStr"/>
+      <c r="K1644" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1644" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>Dentista em Belo Horizonte - Quintão Odontologia</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>https://quintaoodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1645" t="inlineStr"/>
+      <c r="I1645" t="inlineStr"/>
+      <c r="J1645" t="inlineStr"/>
+      <c r="K1645" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1645" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>Souza Sousa Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>https://souzasousa.com.br</t>
+        </is>
+      </c>
+      <c r="H1646" t="inlineStr"/>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>5531988221660</t>
+        </is>
+      </c>
+      <c r="J1646" t="inlineStr"/>
+      <c r="K1646" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1646" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>Clínica Lis</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>https://clinicalisrj.com.br</t>
+        </is>
+      </c>
+      <c r="H1647" t="inlineStr"/>
+      <c r="I1647" t="inlineStr"/>
+      <c r="J1647" t="inlineStr"/>
+      <c r="K1647" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1647" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>Psicóloga Clínica Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>https://psicologamarciagil.com</t>
+        </is>
+      </c>
+      <c r="H1648" t="inlineStr"/>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>5521988793192</t>
+        </is>
+      </c>
+      <c r="J1648" t="inlineStr"/>
+      <c r="K1648" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1648" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>Maria Carolina de Souza Soares</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>https://www.psicologamariacarolinass.com</t>
+        </is>
+      </c>
+      <c r="H1649" t="inlineStr"/>
+      <c r="I1649" t="inlineStr"/>
+      <c r="J1649" t="inlineStr"/>
+      <c r="K1649" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1649" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>Psicólogo Rio de Janeiro Rj Psicoterapia</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>https://psicologiario.com.br</t>
+        </is>
+      </c>
+      <c r="H1650" t="inlineStr"/>
+      <c r="I1650" t="inlineStr">
+        <is>
+          <t>5521994830200</t>
+        </is>
+      </c>
+      <c r="J1650" t="inlineStr"/>
+      <c r="K1650" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1650" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1650"/>
+  <dimension ref="A1:L1658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80505,10 +80505,8 @@
         </is>
       </c>
       <c r="H1641" t="inlineStr"/>
-      <c r="I1641" t="inlineStr">
-        <is>
-          <t>5521965328002</t>
-        </is>
+      <c r="I1641" t="n">
+        <v>5521965328002</v>
       </c>
       <c r="J1641" t="inlineStr"/>
       <c r="K1641" t="n">
@@ -80605,10 +80603,8 @@
         </is>
       </c>
       <c r="H1643" t="inlineStr"/>
-      <c r="I1643" t="inlineStr">
-        <is>
-          <t>5527997950350</t>
-        </is>
+      <c r="I1643" t="n">
+        <v>5527997950350</v>
       </c>
       <c r="J1643" t="inlineStr"/>
       <c r="K1643" t="n">
@@ -80753,10 +80749,8 @@
         </is>
       </c>
       <c r="H1646" t="inlineStr"/>
-      <c r="I1646" t="inlineStr">
-        <is>
-          <t>5531988221660</t>
-        </is>
+      <c r="I1646" t="n">
+        <v>5531988221660</v>
       </c>
       <c r="J1646" t="inlineStr"/>
       <c r="K1646" t="n">
@@ -80853,10 +80847,8 @@
         </is>
       </c>
       <c r="H1648" t="inlineStr"/>
-      <c r="I1648" t="inlineStr">
-        <is>
-          <t>5521988793192</t>
-        </is>
+      <c r="I1648" t="n">
+        <v>5521988793192</v>
       </c>
       <c r="J1648" t="inlineStr"/>
       <c r="K1648" t="n">
@@ -80953,16 +80945,410 @@
         </is>
       </c>
       <c r="H1650" t="inlineStr"/>
-      <c r="I1650" t="inlineStr">
-        <is>
-          <t>5521994830200</t>
-        </is>
+      <c r="I1650" t="n">
+        <v>5521994830200</v>
       </c>
       <c r="J1650" t="inlineStr"/>
       <c r="K1650" t="n">
         <v>67</v>
       </c>
       <c r="L1650" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>Zap Médicos</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>https://www.guiamedicodecuritiba.com</t>
+        </is>
+      </c>
+      <c r="H1651" t="inlineStr"/>
+      <c r="I1651" t="inlineStr"/>
+      <c r="J1651" t="inlineStr"/>
+      <c r="K1651" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1651" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>Bacharelado em Educação Física</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>https://utfpr.curitiba.br</t>
+        </is>
+      </c>
+      <c r="H1652" t="inlineStr"/>
+      <c r="I1652" t="inlineStr"/>
+      <c r="J1652" t="inlineStr"/>
+      <c r="K1652" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1652" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>Paola Alves</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>https://www.paolaalvespsicologa.com</t>
+        </is>
+      </c>
+      <c r="H1653" t="inlineStr"/>
+      <c r="I1653" t="inlineStr"/>
+      <c r="J1653" t="inlineStr"/>
+      <c r="K1653" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1653" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>Damo Advocacia &amp; Consultoria Jurídica</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>https://damoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1654" t="inlineStr"/>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>5551984887751</t>
+        </is>
+      </c>
+      <c r="J1654" t="inlineStr"/>
+      <c r="K1654" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1654" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>Médicos em Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>http://www.guiamedicofloripa.com.br</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr"/>
+      <c r="I1655" t="inlineStr"/>
+      <c r="J1655" t="inlineStr"/>
+      <c r="K1655" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1655" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>Guia Médico de Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>https://guiamedicoflorianopolis.com.br</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr"/>
+      <c r="I1656" t="inlineStr"/>
+      <c r="J1656" t="inlineStr"/>
+      <c r="K1656" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1656" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>Dentista Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>https://dentistafloripa.com</t>
+        </is>
+      </c>
+      <c r="H1657" t="inlineStr"/>
+      <c r="I1657" t="inlineStr">
+        <is>
+          <t>5548988221122</t>
+        </is>
+      </c>
+      <c r="J1657" t="inlineStr"/>
+      <c r="K1657" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1657" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>Blanc Odontologia Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>https://blancodontologia.com</t>
+        </is>
+      </c>
+      <c r="H1658" t="inlineStr"/>
+      <c r="I1658" t="inlineStr">
+        <is>
+          <t>5548991086854</t>
+        </is>
+      </c>
+      <c r="J1658" t="inlineStr"/>
+      <c r="K1658" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1658" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1658"/>
+  <dimension ref="A1:L1666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81139,10 +81139,8 @@
         </is>
       </c>
       <c r="H1654" t="inlineStr"/>
-      <c r="I1654" t="inlineStr">
-        <is>
-          <t>5551984887751</t>
-        </is>
+      <c r="I1654" t="n">
+        <v>5551984887751</v>
       </c>
       <c r="J1654" t="inlineStr"/>
       <c r="K1654" t="n">
@@ -81287,10 +81285,8 @@
         </is>
       </c>
       <c r="H1657" t="inlineStr"/>
-      <c r="I1657" t="inlineStr">
-        <is>
-          <t>5548988221122</t>
-        </is>
+      <c r="I1657" t="n">
+        <v>5548988221122</v>
       </c>
       <c r="J1657" t="inlineStr"/>
       <c r="K1657" t="n">
@@ -81339,16 +81335,410 @@
         </is>
       </c>
       <c r="H1658" t="inlineStr"/>
-      <c r="I1658" t="inlineStr">
-        <is>
-          <t>5548991086854</t>
-        </is>
+      <c r="I1658" t="n">
+        <v>5548991086854</v>
       </c>
       <c r="J1658" t="inlineStr"/>
       <c r="K1658" t="n">
         <v>73</v>
       </c>
       <c r="L1658" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>Macapá AP: Guia Completo da Saúde Particular</t>
+        </is>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>https://saudeaz.com.br</t>
+        </is>
+      </c>
+      <c r="H1659" t="inlineStr"/>
+      <c r="I1659" t="inlineStr"/>
+      <c r="J1659" t="inlineStr"/>
+      <c r="K1659" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1659" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>https://ifap.edu.br</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr"/>
+      <c r="I1660" t="inlineStr"/>
+      <c r="J1660" t="inlineStr"/>
+      <c r="K1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1660" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta Geral em Consultório de Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>https://guiasaudebrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1661" t="inlineStr"/>
+      <c r="I1661" t="inlineStr"/>
+      <c r="J1661" t="inlineStr"/>
+      <c r="K1661" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1661" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>Clinica Sorriso Novo Manaus</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>https://sorriso-novo.com</t>
+        </is>
+      </c>
+      <c r="H1662" t="inlineStr"/>
+      <c r="I1662" t="inlineStr"/>
+      <c r="J1662" t="inlineStr"/>
+      <c r="K1662" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1662" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>Advogado em Manaus e no Amazonas</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>https://matheusmendesjur.com.br</t>
+        </is>
+      </c>
+      <c r="H1663" t="inlineStr"/>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>5597981111570</t>
+        </is>
+      </c>
+      <c r="J1663" t="inlineStr"/>
+      <c r="K1663" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1663" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>Nogueira &amp; Paiva Advocacia</t>
+        </is>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>https://nogueirapaiva.com</t>
+        </is>
+      </c>
+      <c r="H1664" t="inlineStr"/>
+      <c r="I1664" t="inlineStr">
+        <is>
+          <t>5592993664378</t>
+        </is>
+      </c>
+      <c r="J1664" t="inlineStr"/>
+      <c r="K1664" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1664" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>Bruno Araújo Advocacia</t>
+        </is>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>https://advbrunoaraujo.com.br</t>
+        </is>
+      </c>
+      <c r="H1665" t="inlineStr"/>
+      <c r="I1665" t="inlineStr">
+        <is>
+          <t>5592981024849</t>
+        </is>
+      </c>
+      <c r="J1665" t="inlineStr"/>
+      <c r="K1665" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1665" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>Carvalho e Tavares</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>https://www.advogadosct.com</t>
+        </is>
+      </c>
+      <c r="H1666" t="inlineStr"/>
+      <c r="I1666" t="inlineStr"/>
+      <c r="J1666" t="inlineStr"/>
+      <c r="K1666" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1666" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1666"/>
+  <dimension ref="A1:L1672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81577,10 +81577,8 @@
         </is>
       </c>
       <c r="H1663" t="inlineStr"/>
-      <c r="I1663" t="inlineStr">
-        <is>
-          <t>5597981111570</t>
-        </is>
+      <c r="I1663" t="n">
+        <v>5597981111570</v>
       </c>
       <c r="J1663" t="inlineStr"/>
       <c r="K1663" t="n">
@@ -81629,10 +81627,8 @@
         </is>
       </c>
       <c r="H1664" t="inlineStr"/>
-      <c r="I1664" t="inlineStr">
-        <is>
-          <t>5592993664378</t>
-        </is>
+      <c r="I1664" t="n">
+        <v>5592993664378</v>
       </c>
       <c r="J1664" t="inlineStr"/>
       <c r="K1664" t="n">
@@ -81681,10 +81677,8 @@
         </is>
       </c>
       <c r="H1665" t="inlineStr"/>
-      <c r="I1665" t="inlineStr">
-        <is>
-          <t>5592981024849</t>
-        </is>
+      <c r="I1665" t="n">
+        <v>5592981024849</v>
       </c>
       <c r="J1665" t="inlineStr"/>
       <c r="K1665" t="n">
@@ -81744,6 +81738,314 @@
         </is>
       </c>
     </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Maceió</t>
+        </is>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>https://cmdiagnostica.com.br</t>
+        </is>
+      </c>
+      <c r="H1667" t="inlineStr"/>
+      <c r="I1667" t="inlineStr">
+        <is>
+          <t>5582999974950</t>
+        </is>
+      </c>
+      <c r="J1667" t="inlineStr"/>
+      <c r="K1667" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1667" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>Fontan &amp; Lins Advogados O Fontan &amp; Lins Advogados é um ...</t>
+        </is>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>https://fontanelins.com.br</t>
+        </is>
+      </c>
+      <c r="H1668" t="inlineStr"/>
+      <c r="I1668" t="inlineStr">
+        <is>
+          <t>5582993021131</t>
+        </is>
+      </c>
+      <c r="J1668" t="inlineStr"/>
+      <c r="K1668" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1668" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>Psicólogo Online e em Salvador/BA</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>https://psicologomoiseslopes.com.br</t>
+        </is>
+      </c>
+      <c r="H1669" t="inlineStr"/>
+      <c r="I1669" t="inlineStr"/>
+      <c r="J1669" t="inlineStr"/>
+      <c r="K1669" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1669" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>Fisioterapia Domiciliar em Lauro de Freitas e Salvador BA</t>
+        </is>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>https://drdanilosodre.com</t>
+        </is>
+      </c>
+      <c r="H1670" t="inlineStr"/>
+      <c r="I1670" t="inlineStr">
+        <is>
+          <t>5571984259504</t>
+        </is>
+      </c>
+      <c r="J1670" t="inlineStr"/>
+      <c r="K1670" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1670" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>Clínica em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>https://www.clinicaexpressosaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1671" t="inlineStr"/>
+      <c r="I1671" t="inlineStr">
+        <is>
+          <t>5585997677837</t>
+        </is>
+      </c>
+      <c r="J1671" t="inlineStr"/>
+      <c r="K1671" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1671" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>Camila Marques - Psicóloga</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>https://psicologacamilamarques.com.br</t>
+        </is>
+      </c>
+      <c r="H1672" t="inlineStr"/>
+      <c r="I1672" t="inlineStr">
+        <is>
+          <t>5585994057740</t>
+        </is>
+      </c>
+      <c r="J1672" t="inlineStr"/>
+      <c r="K1672" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1672" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1672"/>
+  <dimension ref="A1:L1696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81775,10 +81775,8 @@
         </is>
       </c>
       <c r="H1667" t="inlineStr"/>
-      <c r="I1667" t="inlineStr">
-        <is>
-          <t>5582999974950</t>
-        </is>
+      <c r="I1667" t="n">
+        <v>5582999974950</v>
       </c>
       <c r="J1667" t="inlineStr"/>
       <c r="K1667" t="n">
@@ -81827,10 +81825,8 @@
         </is>
       </c>
       <c r="H1668" t="inlineStr"/>
-      <c r="I1668" t="inlineStr">
-        <is>
-          <t>5582993021131</t>
-        </is>
+      <c r="I1668" t="n">
+        <v>5582993021131</v>
       </c>
       <c r="J1668" t="inlineStr"/>
       <c r="K1668" t="n">
@@ -81927,10 +81923,8 @@
         </is>
       </c>
       <c r="H1670" t="inlineStr"/>
-      <c r="I1670" t="inlineStr">
-        <is>
-          <t>5571984259504</t>
-        </is>
+      <c r="I1670" t="n">
+        <v>5571984259504</v>
       </c>
       <c r="J1670" t="inlineStr"/>
       <c r="K1670" t="n">
@@ -81979,10 +81973,8 @@
         </is>
       </c>
       <c r="H1671" t="inlineStr"/>
-      <c r="I1671" t="inlineStr">
-        <is>
-          <t>5585997677837</t>
-        </is>
+      <c r="I1671" t="n">
+        <v>5585997677837</v>
       </c>
       <c r="J1671" t="inlineStr"/>
       <c r="K1671" t="n">
@@ -82031,16 +82023,1222 @@
         </is>
       </c>
       <c r="H1672" t="inlineStr"/>
-      <c r="I1672" t="inlineStr">
-        <is>
-          <t>5585994057740</t>
-        </is>
+      <c r="I1672" t="n">
+        <v>5585994057740</v>
       </c>
       <c r="J1672" t="inlineStr"/>
       <c r="K1672" t="n">
         <v>75</v>
       </c>
       <c r="L1672" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>Ōru Clinic</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>https://oruclinic.com</t>
+        </is>
+      </c>
+      <c r="H1673" t="inlineStr"/>
+      <c r="I1673" t="inlineStr"/>
+      <c r="J1673" t="inlineStr"/>
+      <c r="K1673" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1673" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>Academias no Brasília, Brasília: preços e avaliações</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>https://academiasgru.com.br</t>
+        </is>
+      </c>
+      <c r="H1674" t="inlineStr"/>
+      <c r="I1674" t="inlineStr"/>
+      <c r="J1674" t="inlineStr"/>
+      <c r="K1674" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1674" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>Fisio Corpus - Clínica de Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>https://www.fisiocorpusdf.com.br</t>
+        </is>
+      </c>
+      <c r="H1675" t="inlineStr"/>
+      <c r="I1675" t="inlineStr"/>
+      <c r="J1675" t="inlineStr"/>
+      <c r="K1675" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1675" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>Especialista em coluna</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>https://www.drrenatobonafim.com.br</t>
+        </is>
+      </c>
+      <c r="H1676" t="inlineStr"/>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>5565981548226</t>
+        </is>
+      </c>
+      <c r="J1676" t="inlineStr"/>
+      <c r="K1676" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1676" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>Thiago Pinho Advogado</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>https://thiagopinho.adv.br</t>
+        </is>
+      </c>
+      <c r="H1677" t="inlineStr"/>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>5565999324612</t>
+        </is>
+      </c>
+      <c r="J1677" t="inlineStr"/>
+      <c r="K1677" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1677" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>Anderson Gadelha</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>https://andersongadelha.adv.br</t>
+        </is>
+      </c>
+      <c r="H1678" t="inlineStr"/>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>5565992060683</t>
+        </is>
+      </c>
+      <c r="J1678" t="inlineStr"/>
+      <c r="K1678" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1678" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>Dr. Marcos Pescara</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>https://marcospescaraadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1679" t="inlineStr"/>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>5565996701321</t>
+        </is>
+      </c>
+      <c r="J1679" t="inlineStr"/>
+      <c r="K1679" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1679" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>Furtunato Advocacia</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>https://furtunatoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1680" t="inlineStr"/>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>5517997368799</t>
+        </is>
+      </c>
+      <c r="J1680" t="inlineStr"/>
+      <c r="K1680" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1680" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>Guia</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>https://cuiabamt.com.br</t>
+        </is>
+      </c>
+      <c r="H1681" t="inlineStr"/>
+      <c r="I1681" t="inlineStr"/>
+      <c r="J1681" t="inlineStr"/>
+      <c r="K1681" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1681" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>Power Fit Academia</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>https://www.powerfitacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1682" t="inlineStr"/>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>5565992455033</t>
+        </is>
+      </c>
+      <c r="J1682" t="inlineStr"/>
+      <c r="K1682" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1682" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Cuiabá</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>https://www.clinicafisiomt.com.br</t>
+        </is>
+      </c>
+      <c r="H1683" t="inlineStr"/>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>5565976013222</t>
+        </is>
+      </c>
+      <c r="J1683" t="inlineStr"/>
+      <c r="K1683" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1683" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>Médicos, Clínicas e Consultórios Medicos em Campo Grande</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>https://www.encontracampogrande.com.br</t>
+        </is>
+      </c>
+      <c r="H1684" t="inlineStr"/>
+      <c r="I1684" t="inlineStr"/>
+      <c r="J1684" t="inlineStr"/>
+      <c r="K1684" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1684" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>Dr. Guilherme Maldonado Filho</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>https://drguilhermemaldonado.com.br</t>
+        </is>
+      </c>
+      <c r="H1685" t="inlineStr"/>
+      <c r="I1685" t="inlineStr"/>
+      <c r="J1685" t="inlineStr"/>
+      <c r="K1685" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1685" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>Dra Grassiele Magalhaes I Dentista I Campo Grande MS</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>https://www.dragrassielemagalhaes.com</t>
+        </is>
+      </c>
+      <c r="H1686" t="inlineStr"/>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>5567991861012</t>
+        </is>
+      </c>
+      <c r="J1686" t="inlineStr"/>
+      <c r="K1686" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1686" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>Dentista em Campo Grande MS</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>https://drlucasfigueiredo.com</t>
+        </is>
+      </c>
+      <c r="H1687" t="inlineStr"/>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>5567991219812</t>
+        </is>
+      </c>
+      <c r="J1687" t="inlineStr"/>
+      <c r="K1687" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1687" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>Eximium Odontologia</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>https://www.eximiumodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1688" t="inlineStr"/>
+      <c r="I1688" t="inlineStr"/>
+      <c r="J1688" t="inlineStr"/>
+      <c r="K1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1688" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>Terapeuta Andrea Salomão</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>https://terapeutaandreasalomao.com.br</t>
+        </is>
+      </c>
+      <c r="H1689" t="inlineStr"/>
+      <c r="I1689" t="inlineStr">
+        <is>
+          <t>5567996072855</t>
+        </is>
+      </c>
+      <c r="J1689" t="inlineStr"/>
+      <c r="K1689" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1689" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>Psicólogo em Campo Grande MS</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>https://www.marcosmartinezgeorges.com.br</t>
+        </is>
+      </c>
+      <c r="H1690" t="inlineStr"/>
+      <c r="I1690" t="inlineStr">
+        <is>
+          <t>5567981099528</t>
+        </is>
+      </c>
+      <c r="J1690" t="inlineStr"/>
+      <c r="K1690" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1690" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>Psicologa Cláudia Carraro</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>https://www.claudiacarraropsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1691" t="inlineStr"/>
+      <c r="I1691" t="inlineStr"/>
+      <c r="J1691" t="inlineStr"/>
+      <c r="K1691" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1691" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Campo Grande</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>https://rodrigueseortiz.adv.br</t>
+        </is>
+      </c>
+      <c r="H1692" t="inlineStr"/>
+      <c r="I1692" t="inlineStr">
+        <is>
+          <t>5567981314652</t>
+        </is>
+      </c>
+      <c r="J1692" t="inlineStr"/>
+      <c r="K1692" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1692" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>Oliveira &amp; Godoi Advogados</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>https://oliveiraegodoi.com</t>
+        </is>
+      </c>
+      <c r="H1693" t="inlineStr"/>
+      <c r="I1693" t="inlineStr">
+        <is>
+          <t>5567949421338</t>
+        </is>
+      </c>
+      <c r="J1693" t="inlineStr"/>
+      <c r="K1693" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1693" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>Alessandro Henrique Nardoni</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>https://alessandronardoniadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1694" t="inlineStr"/>
+      <c r="I1694" t="inlineStr"/>
+      <c r="J1694" t="inlineStr"/>
+      <c r="K1694" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1694" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>Márcio Sandim Advogados</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>https://www.marciosandim.com</t>
+        </is>
+      </c>
+      <c r="H1695" t="inlineStr"/>
+      <c r="I1695" t="inlineStr">
+        <is>
+          <t>5567991672000</t>
+        </is>
+      </c>
+      <c r="J1695" t="inlineStr"/>
+      <c r="K1695" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1695" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>Pollak Advogados: Escritório de Advocacia</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>https://www.pollakadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1696" t="inlineStr"/>
+      <c r="I1696" t="inlineStr"/>
+      <c r="J1696" t="inlineStr"/>
+      <c r="K1696" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1696" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1696"/>
+  <dimension ref="A1:L1703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82217,10 +82217,8 @@
         </is>
       </c>
       <c r="H1676" t="inlineStr"/>
-      <c r="I1676" t="inlineStr">
-        <is>
-          <t>5565981548226</t>
-        </is>
+      <c r="I1676" t="n">
+        <v>5565981548226</v>
       </c>
       <c r="J1676" t="inlineStr"/>
       <c r="K1676" t="n">
@@ -82269,10 +82267,8 @@
         </is>
       </c>
       <c r="H1677" t="inlineStr"/>
-      <c r="I1677" t="inlineStr">
-        <is>
-          <t>5565999324612</t>
-        </is>
+      <c r="I1677" t="n">
+        <v>5565999324612</v>
       </c>
       <c r="J1677" t="inlineStr"/>
       <c r="K1677" t="n">
@@ -82321,10 +82317,8 @@
         </is>
       </c>
       <c r="H1678" t="inlineStr"/>
-      <c r="I1678" t="inlineStr">
-        <is>
-          <t>5565992060683</t>
-        </is>
+      <c r="I1678" t="n">
+        <v>5565992060683</v>
       </c>
       <c r="J1678" t="inlineStr"/>
       <c r="K1678" t="n">
@@ -82373,10 +82367,8 @@
         </is>
       </c>
       <c r="H1679" t="inlineStr"/>
-      <c r="I1679" t="inlineStr">
-        <is>
-          <t>5565996701321</t>
-        </is>
+      <c r="I1679" t="n">
+        <v>5565996701321</v>
       </c>
       <c r="J1679" t="inlineStr"/>
       <c r="K1679" t="n">
@@ -82425,10 +82417,8 @@
         </is>
       </c>
       <c r="H1680" t="inlineStr"/>
-      <c r="I1680" t="inlineStr">
-        <is>
-          <t>5517997368799</t>
-        </is>
+      <c r="I1680" t="n">
+        <v>5517997368799</v>
       </c>
       <c r="J1680" t="inlineStr"/>
       <c r="K1680" t="n">
@@ -82525,10 +82515,8 @@
         </is>
       </c>
       <c r="H1682" t="inlineStr"/>
-      <c r="I1682" t="inlineStr">
-        <is>
-          <t>5565992455033</t>
-        </is>
+      <c r="I1682" t="n">
+        <v>5565992455033</v>
       </c>
       <c r="J1682" t="inlineStr"/>
       <c r="K1682" t="n">
@@ -82577,10 +82565,8 @@
         </is>
       </c>
       <c r="H1683" t="inlineStr"/>
-      <c r="I1683" t="inlineStr">
-        <is>
-          <t>5565976013222</t>
-        </is>
+      <c r="I1683" t="n">
+        <v>5565976013222</v>
       </c>
       <c r="J1683" t="inlineStr"/>
       <c r="K1683" t="n">
@@ -82725,10 +82711,8 @@
         </is>
       </c>
       <c r="H1686" t="inlineStr"/>
-      <c r="I1686" t="inlineStr">
-        <is>
-          <t>5567991861012</t>
-        </is>
+      <c r="I1686" t="n">
+        <v>5567991861012</v>
       </c>
       <c r="J1686" t="inlineStr"/>
       <c r="K1686" t="n">
@@ -82777,10 +82761,8 @@
         </is>
       </c>
       <c r="H1687" t="inlineStr"/>
-      <c r="I1687" t="inlineStr">
-        <is>
-          <t>5567991219812</t>
-        </is>
+      <c r="I1687" t="n">
+        <v>5567991219812</v>
       </c>
       <c r="J1687" t="inlineStr"/>
       <c r="K1687" t="n">
@@ -82877,10 +82859,8 @@
         </is>
       </c>
       <c r="H1689" t="inlineStr"/>
-      <c r="I1689" t="inlineStr">
-        <is>
-          <t>5567996072855</t>
-        </is>
+      <c r="I1689" t="n">
+        <v>5567996072855</v>
       </c>
       <c r="J1689" t="inlineStr"/>
       <c r="K1689" t="n">
@@ -82929,10 +82909,8 @@
         </is>
       </c>
       <c r="H1690" t="inlineStr"/>
-      <c r="I1690" t="inlineStr">
-        <is>
-          <t>5567981099528</t>
-        </is>
+      <c r="I1690" t="n">
+        <v>5567981099528</v>
       </c>
       <c r="J1690" t="inlineStr"/>
       <c r="K1690" t="n">
@@ -83029,10 +83007,8 @@
         </is>
       </c>
       <c r="H1692" t="inlineStr"/>
-      <c r="I1692" t="inlineStr">
-        <is>
-          <t>5567981314652</t>
-        </is>
+      <c r="I1692" t="n">
+        <v>5567981314652</v>
       </c>
       <c r="J1692" t="inlineStr"/>
       <c r="K1692" t="n">
@@ -83081,10 +83057,8 @@
         </is>
       </c>
       <c r="H1693" t="inlineStr"/>
-      <c r="I1693" t="inlineStr">
-        <is>
-          <t>5567949421338</t>
-        </is>
+      <c r="I1693" t="n">
+        <v>5567949421338</v>
       </c>
       <c r="J1693" t="inlineStr"/>
       <c r="K1693" t="n">
@@ -83181,10 +83155,8 @@
         </is>
       </c>
       <c r="H1695" t="inlineStr"/>
-      <c r="I1695" t="inlineStr">
-        <is>
-          <t>5567991672000</t>
-        </is>
+      <c r="I1695" t="n">
+        <v>5567991672000</v>
       </c>
       <c r="J1695" t="inlineStr"/>
       <c r="K1695" t="n">
@@ -83244,6 +83216,358 @@
         </is>
       </c>
     </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>Dr. Henrique Totola</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>https://www.henriquetotola.com.br</t>
+        </is>
+      </c>
+      <c r="H1697" t="inlineStr"/>
+      <c r="I1697" t="inlineStr"/>
+      <c r="J1697" t="inlineStr"/>
+      <c r="K1697" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1697" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>Dr. Alberto V. Gomes</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>https://endocrinoalbertogomes.com.br</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr"/>
+      <c r="I1698" t="inlineStr"/>
+      <c r="J1698" t="inlineStr"/>
+      <c r="K1698" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1698" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>Giacomelli &amp; Giacomelli Advogados</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>https://www.giacomelliadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1699" t="inlineStr"/>
+      <c r="I1699" t="inlineStr">
+        <is>
+          <t>552733243368</t>
+        </is>
+      </c>
+      <c r="J1699" t="inlineStr"/>
+      <c r="K1699" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1699" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>https://guiamassagembrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr"/>
+      <c r="I1700" t="inlineStr">
+        <is>
+          <t>5511943909759</t>
+        </is>
+      </c>
+      <c r="J1700" t="inlineStr"/>
+      <c r="K1700" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1700" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>Terapeutas em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>https://www.kayaterapias.com</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr"/>
+      <c r="I1701" t="inlineStr">
+        <is>
+          <t>553135679990</t>
+        </is>
+      </c>
+      <c r="J1701" t="inlineStr"/>
+      <c r="K1701" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1701" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>Dra Gessica Mendes</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>https://www.dragessicamendes.com.br</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr"/>
+      <c r="I1702" t="inlineStr">
+        <is>
+          <t>5531984572473</t>
+        </is>
+      </c>
+      <c r="J1702" t="inlineStr"/>
+      <c r="K1702" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1702" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>https://landing.unibh.br</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr"/>
+      <c r="I1703" t="inlineStr"/>
+      <c r="J1703" t="inlineStr"/>
+      <c r="K1703" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1703" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1703"/>
+  <dimension ref="A1:L1731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83349,10 +83349,8 @@
         </is>
       </c>
       <c r="H1699" t="inlineStr"/>
-      <c r="I1699" t="inlineStr">
-        <is>
-          <t>552733243368</t>
-        </is>
+      <c r="I1699" t="n">
+        <v>552733243368</v>
       </c>
       <c r="J1699" t="inlineStr"/>
       <c r="K1699" t="n">
@@ -83401,10 +83399,8 @@
         </is>
       </c>
       <c r="H1700" t="inlineStr"/>
-      <c r="I1700" t="inlineStr">
-        <is>
-          <t>5511943909759</t>
-        </is>
+      <c r="I1700" t="n">
+        <v>5511943909759</v>
       </c>
       <c r="J1700" t="inlineStr"/>
       <c r="K1700" t="n">
@@ -83453,10 +83449,8 @@
         </is>
       </c>
       <c r="H1701" t="inlineStr"/>
-      <c r="I1701" t="inlineStr">
-        <is>
-          <t>553135679990</t>
-        </is>
+      <c r="I1701" t="n">
+        <v>553135679990</v>
       </c>
       <c r="J1701" t="inlineStr"/>
       <c r="K1701" t="n">
@@ -83505,10 +83499,8 @@
         </is>
       </c>
       <c r="H1702" t="inlineStr"/>
-      <c r="I1702" t="inlineStr">
-        <is>
-          <t>5531984572473</t>
-        </is>
+      <c r="I1702" t="n">
+        <v>5531984572473</v>
       </c>
       <c r="J1702" t="inlineStr"/>
       <c r="K1702" t="n">
@@ -83568,6 +83560,1414 @@
         </is>
       </c>
     </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>Constelação Familiar</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>https://www.monicabarreto.com</t>
+        </is>
+      </c>
+      <c r="H1704" t="inlineStr"/>
+      <c r="I1704" t="inlineStr"/>
+      <c r="J1704" t="inlineStr"/>
+      <c r="K1704" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1704" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>Dr Walter Schumacher</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>https://www.drwalterschumacher.com.br</t>
+        </is>
+      </c>
+      <c r="H1705" t="inlineStr"/>
+      <c r="I1705" t="inlineStr"/>
+      <c r="J1705" t="inlineStr"/>
+      <c r="K1705" t="n">
+        <v>71</v>
+      </c>
+      <c r="L1705" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>Dr. David Gusmão</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>https://davidgusmao.com</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr"/>
+      <c r="I1706" t="inlineStr">
+        <is>
+          <t>5551992438753</t>
+        </is>
+      </c>
+      <c r="J1706" t="inlineStr"/>
+      <c r="K1706" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1706" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>Forward Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>https://forwardfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr"/>
+      <c r="I1707" t="inlineStr">
+        <is>
+          <t>5551996902160</t>
+        </is>
+      </c>
+      <c r="J1707" t="inlineStr"/>
+      <c r="K1707" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1707" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>Ricardo Rebolho</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>https://www.ricardorebolho.com.br</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr"/>
+      <c r="I1708" t="inlineStr">
+        <is>
+          <t>5548988741970</t>
+        </is>
+      </c>
+      <c r="J1708" t="inlineStr"/>
+      <c r="K1708" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1708" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>Dr. Daniel Maffasioli Gonçalves</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>https://danielgoncalvespsiquiatra.com</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr"/>
+      <c r="I1709" t="inlineStr"/>
+      <c r="J1709" t="inlineStr"/>
+      <c r="K1709" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1709" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>Thiago Meira Odontologia</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>https://www.thiagomeira.com.br</t>
+        </is>
+      </c>
+      <c r="H1710" t="inlineStr"/>
+      <c r="I1710" t="inlineStr">
+        <is>
+          <t>554888454554</t>
+        </is>
+      </c>
+      <c r="J1710" t="inlineStr"/>
+      <c r="K1710" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1710" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>Dr. Allan Rabello Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>https://www.drallanrabello.com</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr"/>
+      <c r="I1711" t="inlineStr">
+        <is>
+          <t>5548984143116</t>
+        </is>
+      </c>
+      <c r="J1711" t="inlineStr"/>
+      <c r="K1711" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1711" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>Dr. Jatir</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>https://www.dentistajatir.com.br</t>
+        </is>
+      </c>
+      <c r="H1712" t="inlineStr"/>
+      <c r="I1712" t="inlineStr">
+        <is>
+          <t>5548999607669</t>
+        </is>
+      </c>
+      <c r="J1712" t="inlineStr"/>
+      <c r="K1712" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1712" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>Blanc Odontologia</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>https://blancodontosc.codental.site</t>
+        </is>
+      </c>
+      <c r="H1713" t="inlineStr"/>
+      <c r="I1713" t="inlineStr">
+        <is>
+          <t>5548991316946</t>
+        </is>
+      </c>
+      <c r="J1713" t="inlineStr"/>
+      <c r="K1713" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1713" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>Camila M Santos</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>https://www.psicocamilasantos.com.br</t>
+        </is>
+      </c>
+      <c r="H1714" t="inlineStr"/>
+      <c r="I1714" t="inlineStr">
+        <is>
+          <t>5548996263880</t>
+        </is>
+      </c>
+      <c r="J1714" t="inlineStr"/>
+      <c r="K1714" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1714" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>Fábio Bisol Brum Psicólogo e Psicanalista</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>https://www.fabiobrumpsi.com</t>
+        </is>
+      </c>
+      <c r="H1715" t="inlineStr"/>
+      <c r="I1715" t="inlineStr"/>
+      <c r="J1715" t="inlineStr"/>
+      <c r="K1715" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1715" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>Daniel Schmidt</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>https://danielschmidt.com.br</t>
+        </is>
+      </c>
+      <c r="H1716" t="inlineStr"/>
+      <c r="I1716" t="inlineStr"/>
+      <c r="J1716" t="inlineStr"/>
+      <c r="K1716" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1716" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>Leonardo Lima Psicólogo</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>https://leonardolimapsicologo.com</t>
+        </is>
+      </c>
+      <c r="H1717" t="inlineStr"/>
+      <c r="I1717" t="inlineStr"/>
+      <c r="J1717" t="inlineStr"/>
+      <c r="K1717" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1717" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>Vitor Paese</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>https://vitorpaese.com.br</t>
+        </is>
+      </c>
+      <c r="H1718" t="inlineStr"/>
+      <c r="I1718" t="inlineStr"/>
+      <c r="J1718" t="inlineStr"/>
+      <c r="K1718" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1718" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>Luciane Raupp</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>https://www.lucianeraupp.com</t>
+        </is>
+      </c>
+      <c r="H1719" t="inlineStr"/>
+      <c r="I1719" t="inlineStr">
+        <is>
+          <t>5548984215498</t>
+        </is>
+      </c>
+      <c r="J1719" t="inlineStr"/>
+      <c r="K1719" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1719" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>Francisco Bissoli</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>https://franciscobissoli.com</t>
+        </is>
+      </c>
+      <c r="H1720" t="inlineStr"/>
+      <c r="I1720" t="inlineStr">
+        <is>
+          <t>5548999970427</t>
+        </is>
+      </c>
+      <c r="J1720" t="inlineStr"/>
+      <c r="K1720" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1720" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>RC Advogados</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>https://rcadvogado.adv.br</t>
+        </is>
+      </c>
+      <c r="H1721" t="inlineStr"/>
+      <c r="I1721" t="inlineStr">
+        <is>
+          <t>5548999713376</t>
+        </is>
+      </c>
+      <c r="J1721" t="inlineStr"/>
+      <c r="K1721" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1721" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>Pereira Lima Advogados &amp; Consultores</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>https://www.advocaciapl.com</t>
+        </is>
+      </c>
+      <c r="H1722" t="inlineStr"/>
+      <c r="I1722" t="inlineStr">
+        <is>
+          <t>554891241385</t>
+        </is>
+      </c>
+      <c r="J1722" t="inlineStr"/>
+      <c r="K1722" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1722" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>KFS Sociedade de Advogados</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>https://kfsadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1723" t="inlineStr"/>
+      <c r="I1723" t="inlineStr">
+        <is>
+          <t>5548933818578</t>
+        </is>
+      </c>
+      <c r="J1723" t="inlineStr"/>
+      <c r="K1723" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1723" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>Advogado Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>https://vivianeadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1724" t="inlineStr"/>
+      <c r="I1724" t="inlineStr"/>
+      <c r="J1724" t="inlineStr"/>
+      <c r="K1724" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1724" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>Universidades</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>https://crefsc.org.br</t>
+        </is>
+      </c>
+      <c r="H1725" t="inlineStr"/>
+      <c r="I1725" t="inlineStr">
+        <is>
+          <t>5548996162644</t>
+        </is>
+      </c>
+      <c r="J1725" t="inlineStr"/>
+      <c r="K1725" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1725" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>https://www.ies.edu.br</t>
+        </is>
+      </c>
+      <c r="H1726" t="inlineStr"/>
+      <c r="I1726" t="inlineStr"/>
+      <c r="J1726" t="inlineStr"/>
+      <c r="K1726" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1726" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>Academia Ellite</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>https://www.academiaellite.com.br</t>
+        </is>
+      </c>
+      <c r="H1727" t="inlineStr"/>
+      <c r="I1727" t="inlineStr">
+        <is>
+          <t>554833340020</t>
+        </is>
+      </c>
+      <c r="J1727" t="inlineStr"/>
+      <c r="K1727" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1727" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>Academia em Florianópolis Centro</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>https://www.academiaprojetofit.com.br</t>
+        </is>
+      </c>
+      <c r="H1728" t="inlineStr"/>
+      <c r="I1728" t="inlineStr">
+        <is>
+          <t>5548991840053</t>
+        </is>
+      </c>
+      <c r="J1728" t="inlineStr"/>
+      <c r="K1728" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1728" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>FLORIANÓPOLIS</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>https://academiaad3.com.br</t>
+        </is>
+      </c>
+      <c r="H1729" t="inlineStr"/>
+      <c r="I1729" t="inlineStr"/>
+      <c r="J1729" t="inlineStr"/>
+      <c r="K1729" t="n">
+        <v>30</v>
+      </c>
+      <c r="L1729" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>Giovana Castelli - Florianópolis</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>https://www.giovanacastelli.com</t>
+        </is>
+      </c>
+      <c r="H1730" t="inlineStr"/>
+      <c r="I1730" t="inlineStr"/>
+      <c r="J1730" t="inlineStr"/>
+      <c r="K1730" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1730" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Florianópolis - SC: orçamento grátis</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>https://loqal.com.br</t>
+        </is>
+      </c>
+      <c r="H1731" t="inlineStr"/>
+      <c r="I1731" t="inlineStr"/>
+      <c r="J1731" t="inlineStr"/>
+      <c r="K1731" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1731" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1731"/>
+  <dimension ref="A1:L1739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83693,10 +83693,8 @@
         </is>
       </c>
       <c r="H1706" t="inlineStr"/>
-      <c r="I1706" t="inlineStr">
-        <is>
-          <t>5551992438753</t>
-        </is>
+      <c r="I1706" t="n">
+        <v>5551992438753</v>
       </c>
       <c r="J1706" t="inlineStr"/>
       <c r="K1706" t="n">
@@ -83745,10 +83743,8 @@
         </is>
       </c>
       <c r="H1707" t="inlineStr"/>
-      <c r="I1707" t="inlineStr">
-        <is>
-          <t>5551996902160</t>
-        </is>
+      <c r="I1707" t="n">
+        <v>5551996902160</v>
       </c>
       <c r="J1707" t="inlineStr"/>
       <c r="K1707" t="n">
@@ -83797,10 +83793,8 @@
         </is>
       </c>
       <c r="H1708" t="inlineStr"/>
-      <c r="I1708" t="inlineStr">
-        <is>
-          <t>5548988741970</t>
-        </is>
+      <c r="I1708" t="n">
+        <v>5548988741970</v>
       </c>
       <c r="J1708" t="inlineStr"/>
       <c r="K1708" t="n">
@@ -83897,10 +83891,8 @@
         </is>
       </c>
       <c r="H1710" t="inlineStr"/>
-      <c r="I1710" t="inlineStr">
-        <is>
-          <t>554888454554</t>
-        </is>
+      <c r="I1710" t="n">
+        <v>554888454554</v>
       </c>
       <c r="J1710" t="inlineStr"/>
       <c r="K1710" t="n">
@@ -83949,10 +83941,8 @@
         </is>
       </c>
       <c r="H1711" t="inlineStr"/>
-      <c r="I1711" t="inlineStr">
-        <is>
-          <t>5548984143116</t>
-        </is>
+      <c r="I1711" t="n">
+        <v>5548984143116</v>
       </c>
       <c r="J1711" t="inlineStr"/>
       <c r="K1711" t="n">
@@ -84001,10 +83991,8 @@
         </is>
       </c>
       <c r="H1712" t="inlineStr"/>
-      <c r="I1712" t="inlineStr">
-        <is>
-          <t>5548999607669</t>
-        </is>
+      <c r="I1712" t="n">
+        <v>5548999607669</v>
       </c>
       <c r="J1712" t="inlineStr"/>
       <c r="K1712" t="n">
@@ -84053,10 +84041,8 @@
         </is>
       </c>
       <c r="H1713" t="inlineStr"/>
-      <c r="I1713" t="inlineStr">
-        <is>
-          <t>5548991316946</t>
-        </is>
+      <c r="I1713" t="n">
+        <v>5548991316946</v>
       </c>
       <c r="J1713" t="inlineStr"/>
       <c r="K1713" t="n">
@@ -84105,10 +84091,8 @@
         </is>
       </c>
       <c r="H1714" t="inlineStr"/>
-      <c r="I1714" t="inlineStr">
-        <is>
-          <t>5548996263880</t>
-        </is>
+      <c r="I1714" t="n">
+        <v>5548996263880</v>
       </c>
       <c r="J1714" t="inlineStr"/>
       <c r="K1714" t="n">
@@ -84349,10 +84333,8 @@
         </is>
       </c>
       <c r="H1719" t="inlineStr"/>
-      <c r="I1719" t="inlineStr">
-        <is>
-          <t>5548984215498</t>
-        </is>
+      <c r="I1719" t="n">
+        <v>5548984215498</v>
       </c>
       <c r="J1719" t="inlineStr"/>
       <c r="K1719" t="n">
@@ -84401,10 +84383,8 @@
         </is>
       </c>
       <c r="H1720" t="inlineStr"/>
-      <c r="I1720" t="inlineStr">
-        <is>
-          <t>5548999970427</t>
-        </is>
+      <c r="I1720" t="n">
+        <v>5548999970427</v>
       </c>
       <c r="J1720" t="inlineStr"/>
       <c r="K1720" t="n">
@@ -84453,10 +84433,8 @@
         </is>
       </c>
       <c r="H1721" t="inlineStr"/>
-      <c r="I1721" t="inlineStr">
-        <is>
-          <t>5548999713376</t>
-        </is>
+      <c r="I1721" t="n">
+        <v>5548999713376</v>
       </c>
       <c r="J1721" t="inlineStr"/>
       <c r="K1721" t="n">
@@ -84505,10 +84483,8 @@
         </is>
       </c>
       <c r="H1722" t="inlineStr"/>
-      <c r="I1722" t="inlineStr">
-        <is>
-          <t>554891241385</t>
-        </is>
+      <c r="I1722" t="n">
+        <v>554891241385</v>
       </c>
       <c r="J1722" t="inlineStr"/>
       <c r="K1722" t="n">
@@ -84557,10 +84533,8 @@
         </is>
       </c>
       <c r="H1723" t="inlineStr"/>
-      <c r="I1723" t="inlineStr">
-        <is>
-          <t>5548933818578</t>
-        </is>
+      <c r="I1723" t="n">
+        <v>5548933818578</v>
       </c>
       <c r="J1723" t="inlineStr"/>
       <c r="K1723" t="n">
@@ -84657,10 +84631,8 @@
         </is>
       </c>
       <c r="H1725" t="inlineStr"/>
-      <c r="I1725" t="inlineStr">
-        <is>
-          <t>5548996162644</t>
-        </is>
+      <c r="I1725" t="n">
+        <v>5548996162644</v>
       </c>
       <c r="J1725" t="inlineStr"/>
       <c r="K1725" t="n">
@@ -84757,10 +84729,8 @@
         </is>
       </c>
       <c r="H1727" t="inlineStr"/>
-      <c r="I1727" t="inlineStr">
-        <is>
-          <t>554833340020</t>
-        </is>
+      <c r="I1727" t="n">
+        <v>554833340020</v>
       </c>
       <c r="J1727" t="inlineStr"/>
       <c r="K1727" t="n">
@@ -84809,10 +84779,8 @@
         </is>
       </c>
       <c r="H1728" t="inlineStr"/>
-      <c r="I1728" t="inlineStr">
-        <is>
-          <t>5548991840053</t>
-        </is>
+      <c r="I1728" t="n">
+        <v>5548991840053</v>
       </c>
       <c r="J1728" t="inlineStr"/>
       <c r="K1728" t="n">
@@ -84968,6 +84936,414 @@
         </is>
       </c>
     </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>Dra Yana Paiva</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>https://drayanapaiva.com.br</t>
+        </is>
+      </c>
+      <c r="H1732" t="inlineStr"/>
+      <c r="I1732" t="inlineStr">
+        <is>
+          <t>556899972353</t>
+        </is>
+      </c>
+      <c r="J1732" t="inlineStr"/>
+      <c r="K1732" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1732" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>Tatyana Cardoso — Psicólogo em Rio Branco - AC</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>https://www.acheclinicas.com.br</t>
+        </is>
+      </c>
+      <c r="H1733" t="inlineStr"/>
+      <c r="I1733" t="inlineStr">
+        <is>
+          <t>558005911390</t>
+        </is>
+      </c>
+      <c r="J1733" t="inlineStr"/>
+      <c r="K1733" t="n">
+        <v>94</v>
+      </c>
+      <c r="L1733" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>veralucialehnenpsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>https://veralucialehnenpsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1734" t="inlineStr"/>
+      <c r="I1734" t="inlineStr">
+        <is>
+          <t>5596991260935</t>
+        </is>
+      </c>
+      <c r="J1734" t="inlineStr"/>
+      <c r="K1734" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1734" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>Consultórios Psicanalistas e Psicólogos de Manaus</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>https://www.psicanaliseclinica.com</t>
+        </is>
+      </c>
+      <c r="H1735" t="inlineStr"/>
+      <c r="I1735" t="inlineStr"/>
+      <c r="J1735" t="inlineStr"/>
+      <c r="K1735" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1735" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>Psicólogo Tulio Peixoto</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>https://www.tuliopeixoto.com.br</t>
+        </is>
+      </c>
+      <c r="H1736" t="inlineStr"/>
+      <c r="I1736" t="inlineStr"/>
+      <c r="J1736" t="inlineStr"/>
+      <c r="K1736" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1736" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>Armando Antony &amp; Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>https://www.armandoantony.adv.br</t>
+        </is>
+      </c>
+      <c r="H1737" t="inlineStr"/>
+      <c r="I1737" t="inlineStr">
+        <is>
+          <t>5592984668546</t>
+        </is>
+      </c>
+      <c r="J1737" t="inlineStr"/>
+      <c r="K1737" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1737" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>Dr. Ronaldo Macena · Fisioterapeuta Especialista em Dores Crônicas</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>https://drronaldomacena.com.br</t>
+        </is>
+      </c>
+      <c r="H1738" t="inlineStr"/>
+      <c r="I1738" t="inlineStr">
+        <is>
+          <t>559281931738</t>
+        </is>
+      </c>
+      <c r="J1738" t="inlineStr"/>
+      <c r="K1738" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1738" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>Dentista em Belém PA</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>https://sorridiodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H1739" t="inlineStr"/>
+      <c r="I1739" t="inlineStr">
+        <is>
+          <t>559191820775</t>
+        </is>
+      </c>
+      <c r="J1739" t="inlineStr"/>
+      <c r="K1739" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1739" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1739"/>
+  <dimension ref="A1:L1748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84973,10 +84973,8 @@
         </is>
       </c>
       <c r="H1732" t="inlineStr"/>
-      <c r="I1732" t="inlineStr">
-        <is>
-          <t>556899972353</t>
-        </is>
+      <c r="I1732" t="n">
+        <v>556899972353</v>
       </c>
       <c r="J1732" t="inlineStr"/>
       <c r="K1732" t="n">
@@ -85025,10 +85023,8 @@
         </is>
       </c>
       <c r="H1733" t="inlineStr"/>
-      <c r="I1733" t="inlineStr">
-        <is>
-          <t>558005911390</t>
-        </is>
+      <c r="I1733" t="n">
+        <v>558005911390</v>
       </c>
       <c r="J1733" t="inlineStr"/>
       <c r="K1733" t="n">
@@ -85077,10 +85073,8 @@
         </is>
       </c>
       <c r="H1734" t="inlineStr"/>
-      <c r="I1734" t="inlineStr">
-        <is>
-          <t>5596991260935</t>
-        </is>
+      <c r="I1734" t="n">
+        <v>5596991260935</v>
       </c>
       <c r="J1734" t="inlineStr"/>
       <c r="K1734" t="n">
@@ -85225,10 +85219,8 @@
         </is>
       </c>
       <c r="H1737" t="inlineStr"/>
-      <c r="I1737" t="inlineStr">
-        <is>
-          <t>5592984668546</t>
-        </is>
+      <c r="I1737" t="n">
+        <v>5592984668546</v>
       </c>
       <c r="J1737" t="inlineStr"/>
       <c r="K1737" t="n">
@@ -85277,10 +85269,8 @@
         </is>
       </c>
       <c r="H1738" t="inlineStr"/>
-      <c r="I1738" t="inlineStr">
-        <is>
-          <t>559281931738</t>
-        </is>
+      <c r="I1738" t="n">
+        <v>559281931738</v>
       </c>
       <c r="J1738" t="inlineStr"/>
       <c r="K1738" t="n">
@@ -85329,16 +85319,466 @@
         </is>
       </c>
       <c r="H1739" t="inlineStr"/>
-      <c r="I1739" t="inlineStr">
-        <is>
-          <t>559191820775</t>
-        </is>
+      <c r="I1739" t="n">
+        <v>559191820775</v>
       </c>
       <c r="J1739" t="inlineStr"/>
       <c r="K1739" t="n">
         <v>67</v>
       </c>
       <c r="L1739" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>Dr. Fabio de Carvalho Barros</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>https://www.drfabiobarros.com</t>
+        </is>
+      </c>
+      <c r="H1740" t="inlineStr"/>
+      <c r="I1740" t="inlineStr"/>
+      <c r="J1740" t="inlineStr"/>
+      <c r="K1740" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1740" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>Dr. Márcio Medeiros</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>https://marciomedeiros-al.com.br</t>
+        </is>
+      </c>
+      <c r="H1741" t="inlineStr"/>
+      <c r="I1741" t="inlineStr">
+        <is>
+          <t>5582991066615</t>
+        </is>
+      </c>
+      <c r="J1741" t="inlineStr"/>
+      <c r="K1741" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1741" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>Dolf Advogados</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>https://www.dolf.adv.br</t>
+        </is>
+      </c>
+      <c r="H1742" t="inlineStr"/>
+      <c r="I1742" t="inlineStr">
+        <is>
+          <t>558299949472</t>
+        </is>
+      </c>
+      <c r="J1742" t="inlineStr"/>
+      <c r="K1742" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1742" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Salvador (BA) — Agendar consulta</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>https://meudoctor.com</t>
+        </is>
+      </c>
+      <c r="H1743" t="inlineStr"/>
+      <c r="I1743" t="inlineStr"/>
+      <c r="J1743" t="inlineStr"/>
+      <c r="K1743" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1743" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>Bianca Braga</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>https://biancabragapsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1744" t="inlineStr"/>
+      <c r="I1744" t="inlineStr">
+        <is>
+          <t>5571996961908</t>
+        </is>
+      </c>
+      <c r="J1744" t="inlineStr"/>
+      <c r="K1744" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1744" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>Psicólogos em Salvador, BA</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>https://psicologosemsalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H1745" t="inlineStr"/>
+      <c r="I1745" t="inlineStr"/>
+      <c r="J1745" t="inlineStr"/>
+      <c r="K1745" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1745" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>Pereira Borges</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>https://pereiraborgesadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1746" t="inlineStr"/>
+      <c r="I1746" t="inlineStr">
+        <is>
+          <t>5571999032305</t>
+        </is>
+      </c>
+      <c r="J1746" t="inlineStr"/>
+      <c r="K1746" t="n">
+        <v>100</v>
+      </c>
+      <c r="L1746" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>Magalhães Neto: Escritório de advocacia especialista em ...</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>https://magalhaesnetoadv.com.br</t>
+        </is>
+      </c>
+      <c r="H1747" t="inlineStr"/>
+      <c r="I1747" t="inlineStr">
+        <is>
+          <t>557181902229</t>
+        </is>
+      </c>
+      <c r="J1747" t="inlineStr"/>
+      <c r="K1747" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1747" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>Terapia</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>https://www.priscillacostapsicologa.com</t>
+        </is>
+      </c>
+      <c r="H1748" t="inlineStr"/>
+      <c r="I1748" t="inlineStr"/>
+      <c r="J1748" t="inlineStr"/>
+      <c r="K1748" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1748" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1748"/>
+  <dimension ref="A1:L1755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85417,10 +85417,8 @@
         </is>
       </c>
       <c r="H1741" t="inlineStr"/>
-      <c r="I1741" t="inlineStr">
-        <is>
-          <t>5582991066615</t>
-        </is>
+      <c r="I1741" t="n">
+        <v>5582991066615</v>
       </c>
       <c r="J1741" t="inlineStr"/>
       <c r="K1741" t="n">
@@ -85469,10 +85467,8 @@
         </is>
       </c>
       <c r="H1742" t="inlineStr"/>
-      <c r="I1742" t="inlineStr">
-        <is>
-          <t>558299949472</t>
-        </is>
+      <c r="I1742" t="n">
+        <v>558299949472</v>
       </c>
       <c r="J1742" t="inlineStr"/>
       <c r="K1742" t="n">
@@ -85569,10 +85565,8 @@
         </is>
       </c>
       <c r="H1744" t="inlineStr"/>
-      <c r="I1744" t="inlineStr">
-        <is>
-          <t>5571996961908</t>
-        </is>
+      <c r="I1744" t="n">
+        <v>5571996961908</v>
       </c>
       <c r="J1744" t="inlineStr"/>
       <c r="K1744" t="n">
@@ -85669,10 +85663,8 @@
         </is>
       </c>
       <c r="H1746" t="inlineStr"/>
-      <c r="I1746" t="inlineStr">
-        <is>
-          <t>5571999032305</t>
-        </is>
+      <c r="I1746" t="n">
+        <v>5571999032305</v>
       </c>
       <c r="J1746" t="inlineStr"/>
       <c r="K1746" t="n">
@@ -85721,10 +85713,8 @@
         </is>
       </c>
       <c r="H1747" t="inlineStr"/>
-      <c r="I1747" t="inlineStr">
-        <is>
-          <t>557181902229</t>
-        </is>
+      <c r="I1747" t="n">
+        <v>557181902229</v>
       </c>
       <c r="J1747" t="inlineStr"/>
       <c r="K1747" t="n">
@@ -85784,6 +85774,354 @@
         </is>
       </c>
     </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>Cmre Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>https://hospitais.med.br</t>
+        </is>
+      </c>
+      <c r="H1749" t="inlineStr"/>
+      <c r="I1749" t="inlineStr"/>
+      <c r="J1749" t="inlineStr"/>
+      <c r="K1749" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1749" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>Implantes Dentários em Brasília - DF</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>https://www.drfernandobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1750" t="inlineStr"/>
+      <c r="I1750" t="inlineStr">
+        <is>
+          <t>5561996750795</t>
+        </is>
+      </c>
+      <c r="J1750" t="inlineStr"/>
+      <c r="K1750" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1750" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>Academias em Brasília (DF) — 132 unidades</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>https://fitclick.com.br</t>
+        </is>
+      </c>
+      <c r="H1751" t="inlineStr"/>
+      <c r="I1751" t="inlineStr"/>
+      <c r="J1751" t="inlineStr"/>
+      <c r="K1751" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1751" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Brasília</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>https://fisioterapiaembrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1752" t="inlineStr"/>
+      <c r="I1752" t="inlineStr">
+        <is>
+          <t>5561935005357</t>
+        </is>
+      </c>
+      <c r="J1752" t="inlineStr"/>
+      <c r="K1752" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1752" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>Médicos e Clínicas no Centro de Goiânia</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>https://www.encontracentrodegoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H1753" t="inlineStr"/>
+      <c r="I1753" t="inlineStr"/>
+      <c r="J1753" t="inlineStr"/>
+      <c r="K1753" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1753" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>Psicólogo em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>https://www.psicologojacksonbandeira.com</t>
+        </is>
+      </c>
+      <c r="H1754" t="inlineStr"/>
+      <c r="I1754" t="inlineStr">
+        <is>
+          <t>556283286939</t>
+        </is>
+      </c>
+      <c r="J1754" t="inlineStr"/>
+      <c r="K1754" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1754" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>Advogado Especialista</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>https://gutembergamorim.com.br</t>
+        </is>
+      </c>
+      <c r="H1755" t="inlineStr"/>
+      <c r="I1755" t="inlineStr"/>
+      <c r="J1755" t="inlineStr"/>
+      <c r="K1755" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1755" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1755"/>
+  <dimension ref="A1:L1764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85859,10 +85859,8 @@
         </is>
       </c>
       <c r="H1750" t="inlineStr"/>
-      <c r="I1750" t="inlineStr">
-        <is>
-          <t>5561996750795</t>
-        </is>
+      <c r="I1750" t="n">
+        <v>5561996750795</v>
       </c>
       <c r="J1750" t="inlineStr"/>
       <c r="K1750" t="n">
@@ -85959,10 +85957,8 @@
         </is>
       </c>
       <c r="H1752" t="inlineStr"/>
-      <c r="I1752" t="inlineStr">
-        <is>
-          <t>5561935005357</t>
-        </is>
+      <c r="I1752" t="n">
+        <v>5561935005357</v>
       </c>
       <c r="J1752" t="inlineStr"/>
       <c r="K1752" t="n">
@@ -86059,10 +86055,8 @@
         </is>
       </c>
       <c r="H1754" t="inlineStr"/>
-      <c r="I1754" t="inlineStr">
-        <is>
-          <t>556283286939</t>
-        </is>
+      <c r="I1754" t="n">
+        <v>556283286939</v>
       </c>
       <c r="J1754" t="inlineStr"/>
       <c r="K1754" t="n">
@@ -86122,6 +86116,446 @@
         </is>
       </c>
     </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>Ferreira Alcântara</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>https://ferreiraalcantara.adv.br</t>
+        </is>
+      </c>
+      <c r="H1756" t="inlineStr"/>
+      <c r="I1756" t="inlineStr"/>
+      <c r="J1756" t="inlineStr"/>
+      <c r="K1756" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1756" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>Centro de Educação Física e Desportos</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>https://turismo.vitoria.net.br</t>
+        </is>
+      </c>
+      <c r="H1757" t="inlineStr"/>
+      <c r="I1757" t="inlineStr"/>
+      <c r="J1757" t="inlineStr"/>
+      <c r="K1757" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1757" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>Terapeuta em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>https://cissatavares.com.br</t>
+        </is>
+      </c>
+      <c r="H1758" t="inlineStr"/>
+      <c r="I1758" t="inlineStr"/>
+      <c r="J1758" t="inlineStr"/>
+      <c r="K1758" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1758" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>GGS ADV</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>https://www.ggsadv.com</t>
+        </is>
+      </c>
+      <c r="H1759" t="inlineStr"/>
+      <c r="I1759" t="inlineStr"/>
+      <c r="J1759" t="inlineStr"/>
+      <c r="K1759" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1759" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>Advogados de Família e Previdenciário</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>https://xavierteixeiraadvogados.com</t>
+        </is>
+      </c>
+      <c r="H1760" t="inlineStr"/>
+      <c r="I1760" t="inlineStr">
+        <is>
+          <t>5531992749195</t>
+        </is>
+      </c>
+      <c r="J1760" t="inlineStr"/>
+      <c r="K1760" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1760" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>RAJ ODONTOLOGIA</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>https://www.rajodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1761" t="inlineStr"/>
+      <c r="I1761" t="inlineStr">
+        <is>
+          <t>5521969372624</t>
+        </is>
+      </c>
+      <c r="J1761" t="inlineStr"/>
+      <c r="K1761" t="n">
+        <v>93</v>
+      </c>
+      <c r="L1761" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>Psicólogo Rio de Janeiro — Agendar Consulta</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>https://www.psidoctor.com.br</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr"/>
+      <c r="I1762" t="inlineStr"/>
+      <c r="J1762" t="inlineStr"/>
+      <c r="K1762" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1762" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>Encontre a terapia perfeita para voce</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>https://www.terapiascarioca.com.br</t>
+        </is>
+      </c>
+      <c r="H1763" t="inlineStr"/>
+      <c r="I1763" t="inlineStr"/>
+      <c r="J1763" t="inlineStr"/>
+      <c r="K1763" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1763" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>Escola de Educação Física e Desportos</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>https://eefd.ufrj.br</t>
+        </is>
+      </c>
+      <c r="H1764" t="inlineStr"/>
+      <c r="I1764" t="inlineStr"/>
+      <c r="J1764" t="inlineStr"/>
+      <c r="K1764" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1764" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1764"/>
+  <dimension ref="A1:L1771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86345,10 +86345,8 @@
         </is>
       </c>
       <c r="H1760" t="inlineStr"/>
-      <c r="I1760" t="inlineStr">
-        <is>
-          <t>5531992749195</t>
-        </is>
+      <c r="I1760" t="n">
+        <v>5531992749195</v>
       </c>
       <c r="J1760" t="inlineStr"/>
       <c r="K1760" t="n">
@@ -86397,10 +86395,8 @@
         </is>
       </c>
       <c r="H1761" t="inlineStr"/>
-      <c r="I1761" t="inlineStr">
-        <is>
-          <t>5521969372624</t>
-        </is>
+      <c r="I1761" t="n">
+        <v>5521969372624</v>
       </c>
       <c r="J1761" t="inlineStr"/>
       <c r="K1761" t="n">
@@ -86556,6 +86552,358 @@
         </is>
       </c>
     </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>Dra. Marcia Zonatto</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>https://dramarciazonatto.com.br</t>
+        </is>
+      </c>
+      <c r="H1765" t="inlineStr"/>
+      <c r="I1765" t="inlineStr">
+        <is>
+          <t>5541987031818</t>
+        </is>
+      </c>
+      <c r="J1765" t="inlineStr"/>
+      <c r="K1765" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1765" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>Morales Psicologia</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>https://moralespsicologia.com</t>
+        </is>
+      </c>
+      <c r="H1766" t="inlineStr"/>
+      <c r="I1766" t="inlineStr">
+        <is>
+          <t>5511936185569</t>
+        </is>
+      </c>
+      <c r="J1766" t="inlineStr"/>
+      <c r="K1766" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1766" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>Dr. Luiz Antônio Marchioni</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>https://www.luizantoniomarchioni.com</t>
+        </is>
+      </c>
+      <c r="H1767" t="inlineStr"/>
+      <c r="I1767" t="inlineStr"/>
+      <c r="J1767" t="inlineStr"/>
+      <c r="K1767" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1767" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>Marta Novelo</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>https://psicologamartanovelo.com.br</t>
+        </is>
+      </c>
+      <c r="H1768" t="inlineStr"/>
+      <c r="I1768" t="inlineStr">
+        <is>
+          <t>5551997167180</t>
+        </is>
+      </c>
+      <c r="J1768" t="inlineStr"/>
+      <c r="K1768" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1768" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>Bandeira Pereira Advogados</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>https://www.bandeirapereira.com</t>
+        </is>
+      </c>
+      <c r="H1769" t="inlineStr"/>
+      <c r="I1769" t="inlineStr"/>
+      <c r="J1769" t="inlineStr"/>
+      <c r="K1769" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1769" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>Dra. Célia Mendes Médica Psiquiatra e Gestalt ...</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>https://www.draceliamendes.com</t>
+        </is>
+      </c>
+      <c r="H1770" t="inlineStr"/>
+      <c r="I1770" t="inlineStr">
+        <is>
+          <t>5548996294505</t>
+        </is>
+      </c>
+      <c r="J1770" t="inlineStr"/>
+      <c r="K1770" t="n">
+        <v>94</v>
+      </c>
+      <c r="L1770" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>Graduação</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>https://www.udesc.br</t>
+        </is>
+      </c>
+      <c r="H1771" t="inlineStr"/>
+      <c r="I1771" t="inlineStr"/>
+      <c r="J1771" t="inlineStr"/>
+      <c r="K1771" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1771" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1771"/>
+  <dimension ref="A1:L1798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86589,10 +86589,8 @@
         </is>
       </c>
       <c r="H1765" t="inlineStr"/>
-      <c r="I1765" t="inlineStr">
-        <is>
-          <t>5541987031818</t>
-        </is>
+      <c r="I1765" t="n">
+        <v>5541987031818</v>
       </c>
       <c r="J1765" t="inlineStr"/>
       <c r="K1765" t="n">
@@ -86641,10 +86639,8 @@
         </is>
       </c>
       <c r="H1766" t="inlineStr"/>
-      <c r="I1766" t="inlineStr">
-        <is>
-          <t>5511936185569</t>
-        </is>
+      <c r="I1766" t="n">
+        <v>5511936185569</v>
       </c>
       <c r="J1766" t="inlineStr"/>
       <c r="K1766" t="n">
@@ -86741,10 +86737,8 @@
         </is>
       </c>
       <c r="H1768" t="inlineStr"/>
-      <c r="I1768" t="inlineStr">
-        <is>
-          <t>5551997167180</t>
-        </is>
+      <c r="I1768" t="n">
+        <v>5551997167180</v>
       </c>
       <c r="J1768" t="inlineStr"/>
       <c r="K1768" t="n">
@@ -86841,10 +86835,8 @@
         </is>
       </c>
       <c r="H1770" t="inlineStr"/>
-      <c r="I1770" t="inlineStr">
-        <is>
-          <t>5548996294505</t>
-        </is>
+      <c r="I1770" t="n">
+        <v>5548996294505</v>
       </c>
       <c r="J1770" t="inlineStr"/>
       <c r="K1770" t="n">
@@ -86904,6 +86896,1330 @@
         </is>
       </c>
     </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>Psicólogo em Rio Branco, AC: 10 Opções e Preços</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>https://www.santoguia.com.br</t>
+        </is>
+      </c>
+      <c r="H1772" t="inlineStr"/>
+      <c r="I1772" t="inlineStr"/>
+      <c r="J1772" t="inlineStr"/>
+      <c r="K1772" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1772" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>Hospitais e clínicas em Macapá/AP</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>https://crm.com.br</t>
+        </is>
+      </c>
+      <c r="H1773" t="inlineStr"/>
+      <c r="I1773" t="inlineStr"/>
+      <c r="J1773" t="inlineStr"/>
+      <c r="K1773" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1773" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>Manaós Odontologia</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>https://manaosodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1774" t="inlineStr"/>
+      <c r="I1774" t="inlineStr">
+        <is>
+          <t>5592994563374</t>
+        </is>
+      </c>
+      <c r="J1774" t="inlineStr"/>
+      <c r="K1774" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1774" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>https://brunocoluna.site.med.br</t>
+        </is>
+      </c>
+      <c r="H1775" t="inlineStr"/>
+      <c r="I1775" t="inlineStr"/>
+      <c r="J1775" t="inlineStr"/>
+      <c r="K1775" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1775" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>Psicóloga Roberta Bandeira</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>http://robertabandeira.com</t>
+        </is>
+      </c>
+      <c r="H1776" t="inlineStr"/>
+      <c r="I1776" t="inlineStr">
+        <is>
+          <t>5591986137544</t>
+        </is>
+      </c>
+      <c r="J1776" t="inlineStr"/>
+      <c r="K1776" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1776" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>Faculdade de Educação Física (Belém)</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>https://ufpa.br</t>
+        </is>
+      </c>
+      <c r="H1777" t="inlineStr"/>
+      <c r="I1777" t="inlineStr"/>
+      <c r="J1777" t="inlineStr"/>
+      <c r="K1777" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1777" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>Educação Física - Campus III</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>https://www.uepa.br</t>
+        </is>
+      </c>
+      <c r="H1778" t="inlineStr"/>
+      <c r="I1778" t="inlineStr"/>
+      <c r="J1778" t="inlineStr"/>
+      <c r="K1778" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1778" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>Sobre o Curso</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>https://fefbelem.ufpa.br</t>
+        </is>
+      </c>
+      <c r="H1779" t="inlineStr"/>
+      <c r="I1779" t="inlineStr"/>
+      <c r="J1779" t="inlineStr"/>
+      <c r="K1779" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1779" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>Homepage V2</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>https://companhiabelem.com.br</t>
+        </is>
+      </c>
+      <c r="H1780" t="inlineStr"/>
+      <c r="I1780" t="inlineStr">
+        <is>
+          <t>5591992206591</t>
+        </is>
+      </c>
+      <c r="J1780" t="inlineStr"/>
+      <c r="K1780" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1780" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>Dr. Angelo Scotta</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>https://www.scottafisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1781" t="inlineStr"/>
+      <c r="I1781" t="inlineStr"/>
+      <c r="J1781" t="inlineStr"/>
+      <c r="K1781" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1781" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>Clínica Dra. Andréia</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>https://site.clinicadraandreia.com.br</t>
+        </is>
+      </c>
+      <c r="H1782" t="inlineStr"/>
+      <c r="I1782" t="inlineStr"/>
+      <c r="J1782" t="inlineStr"/>
+      <c r="K1782" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1782" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>Clínica Popular Porto Velho</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>https://clinicapopularpvh.com.br</t>
+        </is>
+      </c>
+      <c r="H1783" t="inlineStr"/>
+      <c r="I1783" t="inlineStr"/>
+      <c r="J1783" t="inlineStr"/>
+      <c r="K1783" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1783" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>Dentista em Porto Velho</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>https://drapatricianogueira.com.br</t>
+        </is>
+      </c>
+      <c r="H1784" t="inlineStr"/>
+      <c r="I1784" t="inlineStr">
+        <is>
+          <t>5569992027233</t>
+        </is>
+      </c>
+      <c r="J1784" t="inlineStr"/>
+      <c r="K1784" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1784" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>Dra Magna Bezerra</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>https://www.dramagnabezerra.com.br</t>
+        </is>
+      </c>
+      <c r="H1785" t="inlineStr"/>
+      <c r="I1785" t="inlineStr">
+        <is>
+          <t>556992435963</t>
+        </is>
+      </c>
+      <c r="J1785" t="inlineStr"/>
+      <c r="K1785" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1785" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>Dente Feliz</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>https://www.dentistaportovelho.com.br</t>
+        </is>
+      </c>
+      <c r="H1786" t="inlineStr"/>
+      <c r="I1786" t="inlineStr">
+        <is>
+          <t>5569992251288</t>
+        </is>
+      </c>
+      <c r="J1786" t="inlineStr"/>
+      <c r="K1786" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1786" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>Dra. Daniele Medeiros</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>https://www.psidanielemedeiros.com</t>
+        </is>
+      </c>
+      <c r="H1787" t="inlineStr"/>
+      <c r="I1787" t="inlineStr"/>
+      <c r="J1787" t="inlineStr"/>
+      <c r="K1787" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1787" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>Afya Porto Velho</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>https://portovelho.afya.com.br</t>
+        </is>
+      </c>
+      <c r="H1788" t="inlineStr"/>
+      <c r="I1788" t="inlineStr"/>
+      <c r="J1788" t="inlineStr"/>
+      <c r="K1788" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1788" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>https://faculdadesapiens.edu.br</t>
+        </is>
+      </c>
+      <c r="H1789" t="inlineStr"/>
+      <c r="I1789" t="inlineStr"/>
+      <c r="J1789" t="inlineStr"/>
+      <c r="K1789" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1789" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>Academias em Porto Velho</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>https://www.encontraportovelho.com.br</t>
+        </is>
+      </c>
+      <c r="H1790" t="inlineStr"/>
+      <c r="I1790" t="inlineStr"/>
+      <c r="J1790" t="inlineStr"/>
+      <c r="K1790" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1790" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>D'Sena Academia</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>https://dsenaacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1791" t="inlineStr"/>
+      <c r="I1791" t="inlineStr"/>
+      <c r="J1791" t="inlineStr"/>
+      <c r="K1791" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1791" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>MA Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>https://www.mafisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1792" t="inlineStr"/>
+      <c r="I1792" t="inlineStr">
+        <is>
+          <t>5569999382001</t>
+        </is>
+      </c>
+      <c r="J1792" t="inlineStr"/>
+      <c r="K1792" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1792" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>FisioCordis</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>http://www.fisiocordisro.com.br</t>
+        </is>
+      </c>
+      <c r="H1793" t="inlineStr"/>
+      <c r="I1793" t="inlineStr"/>
+      <c r="J1793" t="inlineStr"/>
+      <c r="K1793" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1793" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>Psicólogas, Clínicas de Psicologia, Psicólogos em Boa Vista ...</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>https://www.encontraboavistarr.com.br</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr"/>
+      <c r="I1794" t="inlineStr"/>
+      <c r="J1794" t="inlineStr"/>
+      <c r="K1794" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1794" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>Clínica Palmas</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>http://clinicapalmas.com.br</t>
+        </is>
+      </c>
+      <c r="H1795" t="inlineStr"/>
+      <c r="I1795" t="inlineStr"/>
+      <c r="J1795" t="inlineStr"/>
+      <c r="K1795" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1795" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>Hospital Palmas Medical</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>https://hospitalpalmasmedical.com.br</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr"/>
+      <c r="I1796" t="inlineStr"/>
+      <c r="J1796" t="inlineStr"/>
+      <c r="K1796" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1796" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>Medical Center Palmas: Hospital, Estrutura, Especialidades ...</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>https://www.encontrapalmas.com.br</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr"/>
+      <c r="I1797" t="inlineStr"/>
+      <c r="J1797" t="inlineStr"/>
+      <c r="K1797" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1797" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>Psicóloga em Palmas e Luzimangues</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>https://penidopsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr"/>
+      <c r="I1798" t="inlineStr"/>
+      <c r="J1798" t="inlineStr"/>
+      <c r="K1798" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1798" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1798"/>
+  <dimension ref="A1:L1804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87029,10 +87029,8 @@
         </is>
       </c>
       <c r="H1774" t="inlineStr"/>
-      <c r="I1774" t="inlineStr">
-        <is>
-          <t>5592994563374</t>
-        </is>
+      <c r="I1774" t="n">
+        <v>5592994563374</v>
       </c>
       <c r="J1774" t="inlineStr"/>
       <c r="K1774" t="n">
@@ -87129,10 +87127,8 @@
         </is>
       </c>
       <c r="H1776" t="inlineStr"/>
-      <c r="I1776" t="inlineStr">
-        <is>
-          <t>5591986137544</t>
-        </is>
+      <c r="I1776" t="n">
+        <v>5591986137544</v>
       </c>
       <c r="J1776" t="inlineStr"/>
       <c r="K1776" t="n">
@@ -87325,10 +87321,8 @@
         </is>
       </c>
       <c r="H1780" t="inlineStr"/>
-      <c r="I1780" t="inlineStr">
-        <is>
-          <t>5591992206591</t>
-        </is>
+      <c r="I1780" t="n">
+        <v>5591992206591</v>
       </c>
       <c r="J1780" t="inlineStr"/>
       <c r="K1780" t="n">
@@ -87521,10 +87515,8 @@
         </is>
       </c>
       <c r="H1784" t="inlineStr"/>
-      <c r="I1784" t="inlineStr">
-        <is>
-          <t>5569992027233</t>
-        </is>
+      <c r="I1784" t="n">
+        <v>5569992027233</v>
       </c>
       <c r="J1784" t="inlineStr"/>
       <c r="K1784" t="n">
@@ -87573,10 +87565,8 @@
         </is>
       </c>
       <c r="H1785" t="inlineStr"/>
-      <c r="I1785" t="inlineStr">
-        <is>
-          <t>556992435963</t>
-        </is>
+      <c r="I1785" t="n">
+        <v>556992435963</v>
       </c>
       <c r="J1785" t="inlineStr"/>
       <c r="K1785" t="n">
@@ -87625,10 +87615,8 @@
         </is>
       </c>
       <c r="H1786" t="inlineStr"/>
-      <c r="I1786" t="inlineStr">
-        <is>
-          <t>5569992251288</t>
-        </is>
+      <c r="I1786" t="n">
+        <v>5569992251288</v>
       </c>
       <c r="J1786" t="inlineStr"/>
       <c r="K1786" t="n">
@@ -87917,10 +87905,8 @@
         </is>
       </c>
       <c r="H1792" t="inlineStr"/>
-      <c r="I1792" t="inlineStr">
-        <is>
-          <t>5569999382001</t>
-        </is>
+      <c r="I1792" t="n">
+        <v>5569999382001</v>
       </c>
       <c r="J1792" t="inlineStr"/>
       <c r="K1792" t="n">
@@ -88220,6 +88206,302 @@
         </is>
       </c>
     </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>Bruno Queiroz Psicólogo</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>https://brunoqueirozpsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr"/>
+      <c r="I1799" t="inlineStr"/>
+      <c r="J1799" t="inlineStr"/>
+      <c r="K1799" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1799" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>Juan Bastos</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>https://www.juanbastos.adv.br</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr"/>
+      <c r="I1800" t="inlineStr">
+        <is>
+          <t>5561995633861</t>
+        </is>
+      </c>
+      <c r="J1800" t="inlineStr"/>
+      <c r="K1800" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1800" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>Clínica CAM em Salvador e Lauro de Freitas</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>https://www.clinicacam.com.br</t>
+        </is>
+      </c>
+      <c r="H1801" t="inlineStr"/>
+      <c r="I1801" t="inlineStr">
+        <is>
+          <t>551140048030</t>
+        </is>
+      </c>
+      <c r="J1801" t="inlineStr"/>
+      <c r="K1801" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1801" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>Ft. Leonardo R. Bezerra I Fisioterapeuta Cred. Mckenzie</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>https://www.leonardobezerra.com.br</t>
+        </is>
+      </c>
+      <c r="H1802" t="inlineStr"/>
+      <c r="I1802" t="inlineStr"/>
+      <c r="J1802" t="inlineStr"/>
+      <c r="K1802" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1802" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>São Luís</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>Clínica da Família São Luís</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>https://www.encontrasaoluisma.com.br</t>
+        </is>
+      </c>
+      <c r="H1803" t="inlineStr"/>
+      <c r="I1803" t="inlineStr"/>
+      <c r="J1803" t="inlineStr"/>
+      <c r="K1803" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1803" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>São Luís</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>Clínica São Luis</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>https://www2.hapvida.com.br</t>
+        </is>
+      </c>
+      <c r="H1804" t="inlineStr"/>
+      <c r="I1804" t="inlineStr"/>
+      <c r="J1804" t="inlineStr"/>
+      <c r="K1804" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1804" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1804"/>
+  <dimension ref="A1:L1813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88291,10 +88291,8 @@
         </is>
       </c>
       <c r="H1800" t="inlineStr"/>
-      <c r="I1800" t="inlineStr">
-        <is>
-          <t>5561995633861</t>
-        </is>
+      <c r="I1800" t="n">
+        <v>5561995633861</v>
       </c>
       <c r="J1800" t="inlineStr"/>
       <c r="K1800" t="n">
@@ -88343,10 +88341,8 @@
         </is>
       </c>
       <c r="H1801" t="inlineStr"/>
-      <c r="I1801" t="inlineStr">
-        <is>
-          <t>551140048030</t>
-        </is>
+      <c r="I1801" t="n">
+        <v>551140048030</v>
       </c>
       <c r="J1801" t="inlineStr"/>
       <c r="K1801" t="n">
@@ -88502,6 +88498,450 @@
         </is>
       </c>
     </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>Fisiotrauma · Fazemos o que te faz bem</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>https://fisiotrauma.com.br</t>
+        </is>
+      </c>
+      <c r="H1805" t="inlineStr"/>
+      <c r="I1805" t="inlineStr"/>
+      <c r="J1805" t="inlineStr"/>
+      <c r="K1805" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1805" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>Lilian Normanha » Psicóloga e terapeuta comportamental em ...</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>https://liliannormanha.com.br</t>
+        </is>
+      </c>
+      <c r="H1806" t="inlineStr"/>
+      <c r="I1806" t="inlineStr">
+        <is>
+          <t>556281771170</t>
+        </is>
+      </c>
+      <c r="J1806" t="inlineStr"/>
+      <c r="K1806" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1806" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>Site deMarco Alves Sociedade de Advocacia</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr">
+        <is>
+          <t>https://www.marcoadv.com</t>
+        </is>
+      </c>
+      <c r="H1807" t="inlineStr"/>
+      <c r="I1807" t="inlineStr"/>
+      <c r="J1807" t="inlineStr"/>
+      <c r="K1807" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1807" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>Clínicas Médicas em Cuiabá-MT</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr">
+        <is>
+          <t>https://regionalize.com.br</t>
+        </is>
+      </c>
+      <c r="H1808" t="inlineStr"/>
+      <c r="I1808" t="inlineStr">
+        <is>
+          <t>5566984418324</t>
+        </is>
+      </c>
+      <c r="J1808" t="inlineStr"/>
+      <c r="K1808" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1808" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>Dr. Marcelo Tramontana — Cirurgião-Dentista</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>https://www.drmarcelotramontana.com.br</t>
+        </is>
+      </c>
+      <c r="H1809" t="inlineStr"/>
+      <c r="I1809" t="inlineStr">
+        <is>
+          <t>556593436309</t>
+        </is>
+      </c>
+      <c r="J1809" t="inlineStr"/>
+      <c r="K1809" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1809" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>Dra. Yara Lorenzetti</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr">
+        <is>
+          <t>https://yaralorenzetti.com.br</t>
+        </is>
+      </c>
+      <c r="H1810" t="inlineStr"/>
+      <c r="I1810" t="inlineStr"/>
+      <c r="J1810" t="inlineStr"/>
+      <c r="K1810" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1810" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>EncontreiPSI</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>https://www.encontreipsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1811" t="inlineStr"/>
+      <c r="I1811" t="inlineStr"/>
+      <c r="J1811" t="inlineStr"/>
+      <c r="K1811" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1811" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>Conselho Regional de Educação Física da 17ª Região do Estado ...</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>https://www.cref17.org.br</t>
+        </is>
+      </c>
+      <c r="H1812" t="inlineStr"/>
+      <c r="I1812" t="inlineStr"/>
+      <c r="J1812" t="inlineStr"/>
+      <c r="K1812" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1812" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>Sesc Fitness tem vagas abertas para diversas atividades em ...</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>https://www.sescmt.com.br</t>
+        </is>
+      </c>
+      <c r="H1813" t="inlineStr"/>
+      <c r="I1813" t="inlineStr"/>
+      <c r="J1813" t="inlineStr"/>
+      <c r="K1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1813" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
